--- a/RM.xlsx
+++ b/RM.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29530"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\MPCI QC\Desktop\FG &amp; RMPM LIST\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7DA978BE-91FB-4371-8E0C-2A27C1DFF3D9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{21759D3C-DC17-4F84-9815-5B393A21BFFC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="45" yWindow="15" windowWidth="20445" windowHeight="10905" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4708" uniqueCount="2443">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4723" uniqueCount="2452">
   <si>
     <t>ID</t>
   </si>
@@ -5396,7 +5396,7 @@
     <t>RM085.3</t>
   </si>
   <si>
-    <t>Screw 28mm BMW Green Cap H=21.10, OD=33.7, W=3.4</t>
+    <t>Screw 28mm BMW Green Cap H=22.4, OD=32.5, W=3.4</t>
   </si>
   <si>
     <t>Screw 28mm BMW Green Cap</t>
@@ -5471,10 +5471,15 @@
     <t>RM085.2</t>
   </si>
   <si>
-    <t>Screw 28mm BMW Milky White Cap H=21.10, OD=33.7, W=3.4</t>
+    <t>Screw 28mm BMW Milky White Cap H=22.4, OD=32.5, W=3.4</t>
   </si>
   <si>
     <t>Screw 28mm BMW Milky White Cap</t>
+  </si>
+  <si>
+    <t>Total Height: 22.40 mm
+OD: 32.50 mm
+Weight: 3.40 gm</t>
   </si>
   <si>
     <t>RM083.3</t>
@@ -7804,6 +7809,32 @@
   </si>
   <si>
     <t>Rah Mid-Night Blue MB (DN-09082022)</t>
+  </si>
+  <si>
+    <t>RM234.2</t>
+  </si>
+  <si>
+    <t>Soap Dispenser Pump 24mm Black LP</t>
+  </si>
+  <si>
+    <t>(((Codification done for COA purpose)))</t>
+  </si>
+  <si>
+    <t>RM202.4</t>
+  </si>
+  <si>
+    <t>PET Resin Recycled RUPET084 - 1125Kgs</t>
+  </si>
+  <si>
+    <t>Recycled PET Chips RUPET084</t>
+  </si>
+  <si>
+    <t>Rungta Eco Extrusions Private Limited</t>
+  </si>
+  <si>
+    <t>Billed to: Dabur
+Shipped to: MPCI
+Trial not done yet</t>
   </si>
 </sst>
 </file>
@@ -7983,11 +8014,13 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -8241,8 +8274,6 @@
       </border>
     </dxf>
     <dxf>
-      <numFmt numFmtId="30" formatCode="@"/>
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <border diagonalUp="0" diagonalDown="0">
         <left style="thin">
           <color indexed="64"/>
@@ -8332,20 +8363,20 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{9F1E8D76-5862-4302-A167-1CD59370D110}" name="Table1" displayName="Table1" ref="A1:K530" totalsRowShown="0" headerRowDxfId="0" dataDxfId="15" headerRowBorderDxfId="13" tableBorderDxfId="14" totalsRowBorderDxfId="12">
-  <autoFilter ref="A1:K530" xr:uid="{9F1E8D76-5862-4302-A167-1CD59370D110}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{1F039EC9-6C81-44BF-BDD8-BD030429FA22}" name="Table1" displayName="Table1" ref="A1:K532" totalsRowShown="0" headerRowDxfId="0" dataDxfId="15" headerRowBorderDxfId="13" tableBorderDxfId="14" totalsRowBorderDxfId="12">
+  <autoFilter ref="A1:K532" xr:uid="{1F039EC9-6C81-44BF-BDD8-BD030429FA22}"/>
   <tableColumns count="11">
-    <tableColumn id="1" xr3:uid="{1EEF98EB-F390-47C1-BD7E-4AD8C8B490D4}" name="ID" dataDxfId="11"/>
-    <tableColumn id="2" xr3:uid="{09F334CE-05C1-47F0-B710-89113DA8CE89}" name="Status" dataDxfId="10"/>
-    <tableColumn id="3" xr3:uid="{07D6BCFC-9A24-435E-A82F-CA4DFFDAE8C1}" name="Material List::Material_Detail" dataDxfId="9"/>
-    <tableColumn id="4" xr3:uid="{CEFAACBD-9153-40F9-A365-E9B70C6724BA}" name="Product_Code" dataDxfId="8"/>
-    <tableColumn id="5" xr3:uid="{D641327B-EAFC-4155-9C2F-6573EC4A9F16}" name="RM PM Product List 2::Product_Detail" dataDxfId="7"/>
-    <tableColumn id="6" xr3:uid="{77105DE7-D92B-4F3E-A189-5C1C1E9B8384}" name="Item_Code" dataDxfId="6"/>
-    <tableColumn id="7" xr3:uid="{C51144A7-F25A-4500-B72E-65D8DA098A7D}" name="Old_Item_Code" dataDxfId="5"/>
-    <tableColumn id="8" xr3:uid="{643CA6CC-E1ED-4DF5-9C0A-F91AB85F086B}" name="Item_Name" dataDxfId="4"/>
-    <tableColumn id="9" xr3:uid="{9AE69C0D-0329-4D09-995C-505C4894F7AB}" name="Item_Detail_by_Vendor" dataDxfId="3"/>
-    <tableColumn id="10" xr3:uid="{EBC82A8A-951D-4B35-870C-8EC56ED2CA43}" name="Vendor List 2::Vendor_Name" dataDxfId="2"/>
-    <tableColumn id="11" xr3:uid="{25FF612D-672B-4F86-853D-8FA5048F2736}" name="Remarks" dataDxfId="1"/>
+    <tableColumn id="1" xr3:uid="{43BA8B2C-B61B-49ED-BA93-161E3E1035A8}" name="ID" dataDxfId="11"/>
+    <tableColumn id="2" xr3:uid="{9A3FF523-352E-426D-8D5D-F42138B81F77}" name="Status" dataDxfId="10"/>
+    <tableColumn id="3" xr3:uid="{5BFA5739-57D6-4002-8ACE-AD5C74E58B24}" name="Material List::Material_Detail" dataDxfId="9"/>
+    <tableColumn id="4" xr3:uid="{2ED2B048-9943-499F-BA4F-AEACF77A4585}" name="Product_Code" dataDxfId="8"/>
+    <tableColumn id="5" xr3:uid="{2D1987A0-21E0-4788-A8D1-B539DBE80A15}" name="RM PM Product List 2::Product_Detail" dataDxfId="7"/>
+    <tableColumn id="6" xr3:uid="{66D4A25C-A235-477C-B076-4DBCF1DE4BEE}" name="Item_Code" dataDxfId="6"/>
+    <tableColumn id="7" xr3:uid="{AA9E07D4-BB89-4C4D-95A7-1B2F020E5B6C}" name="Old_Item_Code" dataDxfId="5"/>
+    <tableColumn id="8" xr3:uid="{643E3A94-3A50-4C27-A96C-7D799DA3CEA5}" name="Item_Name" dataDxfId="4"/>
+    <tableColumn id="9" xr3:uid="{AF523473-BCF4-47DF-9B1E-9038856C6061}" name="Item_Detail_by_Vendor" dataDxfId="3"/>
+    <tableColumn id="10" xr3:uid="{FDC3D2FC-88BF-41F0-B6E1-A4CA470807F0}" name="Vendor List 2::Vendor_Name" dataDxfId="2"/>
+    <tableColumn id="11" xr3:uid="{BBD06216-3437-4CB7-B10D-B81BF109BDB1}" name="Remarks" dataDxfId="1"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -8648,7 +8679,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:K530"/>
+  <dimension ref="A1:K532"/>
   <sheetFormatPr defaultColWidth="21.7109375" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.140625" bestFit="1" customWidth="1"/>
@@ -21162,7 +21193,9 @@
       <c r="J378" s="5" t="s">
         <v>1524</v>
       </c>
-      <c r="K378" s="6"/>
+      <c r="K378" s="8" t="s">
+        <v>1800</v>
+      </c>
     </row>
     <row r="379" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A379" s="4">
@@ -21181,14 +21214,14 @@
         <v>1570</v>
       </c>
       <c r="F379" s="5" t="s">
-        <v>1800</v>
+        <v>1801</v>
       </c>
       <c r="G379" s="7"/>
       <c r="H379" s="5" t="s">
-        <v>1801</v>
+        <v>1802</v>
       </c>
       <c r="I379" s="5" t="s">
-        <v>1802</v>
+        <v>1803</v>
       </c>
       <c r="J379" s="5" t="s">
         <v>1786</v>
@@ -21212,20 +21245,20 @@
         <v>1576</v>
       </c>
       <c r="F380" s="5" t="s">
-        <v>1803</v>
+        <v>1804</v>
       </c>
       <c r="G380" s="7"/>
       <c r="H380" s="5" t="s">
-        <v>1804</v>
+        <v>1805</v>
       </c>
       <c r="I380" s="5" t="s">
-        <v>1805</v>
+        <v>1806</v>
       </c>
       <c r="J380" s="5" t="s">
         <v>1479</v>
       </c>
       <c r="K380" s="8" t="s">
-        <v>1806</v>
+        <v>1807</v>
       </c>
     </row>
     <row r="381" spans="1:11" x14ac:dyDescent="0.2">
@@ -21245,14 +21278,14 @@
         <v>1570</v>
       </c>
       <c r="F381" s="5" t="s">
-        <v>1807</v>
+        <v>1808</v>
       </c>
       <c r="G381" s="7"/>
       <c r="H381" s="5" t="s">
-        <v>1808</v>
+        <v>1809</v>
       </c>
       <c r="I381" s="5" t="s">
-        <v>1809</v>
+        <v>1810</v>
       </c>
       <c r="J381" s="5" t="s">
         <v>1786</v>
@@ -21276,20 +21309,20 @@
         <v>1033</v>
       </c>
       <c r="F382" s="5" t="s">
-        <v>1810</v>
+        <v>1811</v>
       </c>
       <c r="G382" s="7"/>
       <c r="H382" s="5" t="s">
-        <v>1811</v>
+        <v>1812</v>
       </c>
       <c r="I382" s="5" t="s">
-        <v>1811</v>
+        <v>1812</v>
       </c>
       <c r="J382" s="5" t="s">
         <v>1013</v>
       </c>
       <c r="K382" s="8" t="s">
-        <v>1812</v>
+        <v>1813</v>
       </c>
     </row>
     <row r="383" spans="1:11" x14ac:dyDescent="0.2">
@@ -21309,20 +21342,20 @@
         <v>122</v>
       </c>
       <c r="F383" s="5" t="s">
-        <v>1813</v>
+        <v>1814</v>
       </c>
       <c r="G383" s="7"/>
       <c r="H383" s="5" t="s">
-        <v>1814</v>
+        <v>1815</v>
       </c>
       <c r="I383" s="5" t="s">
-        <v>1814</v>
+        <v>1815</v>
       </c>
       <c r="J383" s="5" t="s">
         <v>104</v>
       </c>
       <c r="K383" s="8" t="s">
-        <v>1815</v>
+        <v>1816</v>
       </c>
     </row>
     <row r="384" spans="1:11" x14ac:dyDescent="0.2">
@@ -21336,20 +21369,20 @@
         <v>1287</v>
       </c>
       <c r="D384" s="5" t="s">
-        <v>1816</v>
+        <v>1817</v>
       </c>
       <c r="E384" s="5" t="s">
-        <v>1817</v>
+        <v>1818</v>
       </c>
       <c r="F384" s="5" t="s">
-        <v>1818</v>
+        <v>1819</v>
       </c>
       <c r="G384" s="7"/>
       <c r="H384" s="5" t="s">
-        <v>1819</v>
+        <v>1820</v>
       </c>
       <c r="I384" s="5" t="s">
-        <v>1819</v>
+        <v>1820</v>
       </c>
       <c r="J384" s="5" t="s">
         <v>1005</v>
@@ -21373,20 +21406,20 @@
         <v>1570</v>
       </c>
       <c r="F385" s="5" t="s">
-        <v>1820</v>
+        <v>1821</v>
       </c>
       <c r="G385" s="7"/>
       <c r="H385" s="5" t="s">
-        <v>1821</v>
+        <v>1822</v>
       </c>
       <c r="I385" s="5" t="s">
-        <v>1821</v>
+        <v>1822</v>
       </c>
       <c r="J385" s="5" t="s">
         <v>1786</v>
       </c>
       <c r="K385" s="8" t="s">
-        <v>1822</v>
+        <v>1823</v>
       </c>
     </row>
     <row r="386" spans="1:11" x14ac:dyDescent="0.2">
@@ -21406,14 +21439,14 @@
         <v>122</v>
       </c>
       <c r="F386" s="5" t="s">
-        <v>1823</v>
+        <v>1824</v>
       </c>
       <c r="G386" s="7"/>
       <c r="H386" s="5" t="s">
-        <v>1824</v>
+        <v>1825</v>
       </c>
       <c r="I386" s="5" t="s">
-        <v>1825</v>
+        <v>1826</v>
       </c>
       <c r="J386" s="5" t="s">
         <v>104</v>
@@ -21431,20 +21464,20 @@
         <v>12</v>
       </c>
       <c r="D387" s="5" t="s">
-        <v>1826</v>
+        <v>1827</v>
       </c>
       <c r="E387" s="5" t="s">
-        <v>1827</v>
+        <v>1828</v>
       </c>
       <c r="F387" s="5" t="s">
-        <v>1828</v>
+        <v>1829</v>
       </c>
       <c r="G387" s="7"/>
       <c r="H387" s="5" t="s">
-        <v>1829</v>
+        <v>1830</v>
       </c>
       <c r="I387" s="5" t="s">
-        <v>1830</v>
+        <v>1831</v>
       </c>
       <c r="J387" s="5" t="s">
         <v>19</v>
@@ -21459,29 +21492,29 @@
         <v>11</v>
       </c>
       <c r="C388" s="5" t="s">
-        <v>1831</v>
+        <v>1832</v>
       </c>
       <c r="D388" s="5" t="s">
-        <v>1832</v>
+        <v>1833</v>
       </c>
       <c r="E388" s="5" t="s">
-        <v>1833</v>
+        <v>1834</v>
       </c>
       <c r="F388" s="5" t="s">
-        <v>1834</v>
+        <v>1835</v>
       </c>
       <c r="G388" s="7"/>
       <c r="H388" s="5" t="s">
-        <v>1835</v>
+        <v>1836</v>
       </c>
       <c r="I388" s="5" t="s">
-        <v>1835</v>
+        <v>1836</v>
       </c>
       <c r="J388" s="5" t="s">
-        <v>1836</v>
+        <v>1837</v>
       </c>
       <c r="K388" s="8" t="s">
-        <v>1837</v>
+        <v>1838</v>
       </c>
     </row>
     <row r="389" spans="1:11" x14ac:dyDescent="0.2">
@@ -21495,20 +21528,20 @@
         <v>67</v>
       </c>
       <c r="D389" s="5" t="s">
-        <v>1838</v>
+        <v>1839</v>
       </c>
       <c r="E389" s="5" t="s">
-        <v>1839</v>
+        <v>1840</v>
       </c>
       <c r="F389" s="5" t="s">
-        <v>1840</v>
+        <v>1841</v>
       </c>
       <c r="G389" s="7"/>
       <c r="H389" s="5" t="s">
-        <v>1841</v>
+        <v>1842</v>
       </c>
       <c r="I389" s="5" t="s">
-        <v>1842</v>
+        <v>1843</v>
       </c>
       <c r="J389" s="5" t="s">
         <v>223</v>
@@ -21532,14 +21565,14 @@
         <v>1570</v>
       </c>
       <c r="F390" s="5" t="s">
-        <v>1843</v>
+        <v>1844</v>
       </c>
       <c r="G390" s="7"/>
       <c r="H390" s="5" t="s">
-        <v>1844</v>
+        <v>1845</v>
       </c>
       <c r="I390" s="5" t="s">
-        <v>1844</v>
+        <v>1845</v>
       </c>
       <c r="J390" s="5" t="s">
         <v>1786</v>
@@ -21563,14 +21596,14 @@
         <v>1737</v>
       </c>
       <c r="F391" s="5" t="s">
-        <v>1845</v>
+        <v>1846</v>
       </c>
       <c r="G391" s="7"/>
       <c r="H391" s="5" t="s">
-        <v>1846</v>
+        <v>1847</v>
       </c>
       <c r="I391" s="5" t="s">
-        <v>1846</v>
+        <v>1847</v>
       </c>
       <c r="J391" s="5" t="s">
         <v>1524</v>
@@ -21594,20 +21627,20 @@
         <v>1648</v>
       </c>
       <c r="F392" s="5" t="s">
-        <v>1847</v>
+        <v>1848</v>
       </c>
       <c r="G392" s="7"/>
       <c r="H392" s="5" t="s">
-        <v>1848</v>
+        <v>1849</v>
       </c>
       <c r="I392" s="5" t="s">
-        <v>1848</v>
+        <v>1849</v>
       </c>
       <c r="J392" s="5" t="s">
         <v>1524</v>
       </c>
       <c r="K392" s="8" t="s">
-        <v>1849</v>
+        <v>1850</v>
       </c>
     </row>
     <row r="393" spans="1:11" x14ac:dyDescent="0.2">
@@ -21621,26 +21654,26 @@
         <v>1472</v>
       </c>
       <c r="D393" s="5" t="s">
-        <v>1850</v>
+        <v>1851</v>
       </c>
       <c r="E393" s="5" t="s">
-        <v>1851</v>
+        <v>1852</v>
       </c>
       <c r="F393" s="5" t="s">
-        <v>1852</v>
+        <v>1853</v>
       </c>
       <c r="G393" s="7"/>
       <c r="H393" s="5" t="s">
-        <v>1853</v>
+        <v>1854</v>
       </c>
       <c r="I393" s="5" t="s">
-        <v>1854</v>
+        <v>1855</v>
       </c>
       <c r="J393" s="5" t="s">
         <v>1524</v>
       </c>
       <c r="K393" s="8" t="s">
-        <v>1855</v>
+        <v>1856</v>
       </c>
     </row>
     <row r="394" spans="1:11" x14ac:dyDescent="0.2">
@@ -21660,20 +21693,20 @@
         <v>1533</v>
       </c>
       <c r="F394" s="5" t="s">
-        <v>1856</v>
+        <v>1857</v>
       </c>
       <c r="G394" s="7"/>
       <c r="H394" s="5" t="s">
-        <v>1857</v>
+        <v>1858</v>
       </c>
       <c r="I394" s="5" t="s">
-        <v>1858</v>
+        <v>1859</v>
       </c>
       <c r="J394" s="5" t="s">
         <v>1524</v>
       </c>
       <c r="K394" s="8" t="s">
-        <v>1859</v>
+        <v>1860</v>
       </c>
     </row>
     <row r="395" spans="1:11" x14ac:dyDescent="0.2">
@@ -21693,14 +21726,14 @@
         <v>1779</v>
       </c>
       <c r="F395" s="5" t="s">
-        <v>1860</v>
+        <v>1861</v>
       </c>
       <c r="G395" s="7"/>
       <c r="H395" s="5" t="s">
-        <v>1861</v>
+        <v>1862</v>
       </c>
       <c r="I395" s="5" t="s">
-        <v>1862</v>
+        <v>1863</v>
       </c>
       <c r="J395" s="5" t="s">
         <v>1524</v>
@@ -21718,20 +21751,20 @@
         <v>1472</v>
       </c>
       <c r="D396" s="5" t="s">
-        <v>1863</v>
+        <v>1864</v>
       </c>
       <c r="E396" s="5" t="s">
-        <v>1864</v>
+        <v>1865</v>
       </c>
       <c r="F396" s="5" t="s">
-        <v>1865</v>
+        <v>1866</v>
       </c>
       <c r="G396" s="7"/>
       <c r="H396" s="5" t="s">
-        <v>1866</v>
+        <v>1867</v>
       </c>
       <c r="I396" s="5" t="s">
-        <v>1867</v>
+        <v>1868</v>
       </c>
       <c r="J396" s="5" t="s">
         <v>1524</v>
@@ -21746,29 +21779,29 @@
         <v>11</v>
       </c>
       <c r="C397" s="5" t="s">
-        <v>1831</v>
+        <v>1832</v>
       </c>
       <c r="D397" s="5" t="s">
-        <v>1868</v>
+        <v>1869</v>
       </c>
       <c r="E397" s="5" t="s">
-        <v>1869</v>
+        <v>1870</v>
       </c>
       <c r="F397" s="5" t="s">
-        <v>1870</v>
+        <v>1871</v>
       </c>
       <c r="G397" s="7"/>
       <c r="H397" s="5" t="s">
-        <v>1871</v>
+        <v>1872</v>
       </c>
       <c r="I397" s="5" t="s">
-        <v>1871</v>
+        <v>1872</v>
       </c>
       <c r="J397" s="5" t="s">
-        <v>1836</v>
+        <v>1837</v>
       </c>
       <c r="K397" s="8" t="s">
-        <v>1872</v>
+        <v>1873</v>
       </c>
     </row>
     <row r="398" spans="1:11" x14ac:dyDescent="0.2">
@@ -21782,26 +21815,26 @@
         <v>277</v>
       </c>
       <c r="D398" s="5" t="s">
-        <v>1873</v>
+        <v>1874</v>
       </c>
       <c r="E398" s="5" t="s">
-        <v>1874</v>
+        <v>1875</v>
       </c>
       <c r="F398" s="5" t="s">
-        <v>1875</v>
+        <v>1876</v>
       </c>
       <c r="G398" s="7"/>
       <c r="H398" s="5" t="s">
-        <v>1876</v>
+        <v>1877</v>
       </c>
       <c r="I398" s="5" t="s">
-        <v>1876</v>
+        <v>1877</v>
       </c>
       <c r="J398" s="5" t="s">
         <v>283</v>
       </c>
       <c r="K398" s="8" t="s">
-        <v>1877</v>
+        <v>1878</v>
       </c>
     </row>
     <row r="399" spans="1:11" x14ac:dyDescent="0.2">
@@ -21821,7 +21854,7 @@
         <v>1352</v>
       </c>
       <c r="F399" s="5" t="s">
-        <v>1878</v>
+        <v>1879</v>
       </c>
       <c r="G399" s="7"/>
       <c r="H399" s="5" t="s">
@@ -21852,20 +21885,20 @@
         <v>1637</v>
       </c>
       <c r="F400" s="5" t="s">
-        <v>1879</v>
+        <v>1880</v>
       </c>
       <c r="G400" s="7"/>
       <c r="H400" s="5" t="s">
-        <v>1880</v>
+        <v>1881</v>
       </c>
       <c r="I400" s="5" t="s">
-        <v>1880</v>
+        <v>1881</v>
       </c>
       <c r="J400" s="5" t="s">
         <v>1669</v>
       </c>
       <c r="K400" s="8" t="s">
-        <v>1881</v>
+        <v>1882</v>
       </c>
     </row>
     <row r="401" spans="1:11" x14ac:dyDescent="0.2">
@@ -21885,20 +21918,20 @@
         <v>1637</v>
       </c>
       <c r="F401" s="5" t="s">
-        <v>1882</v>
+        <v>1883</v>
       </c>
       <c r="G401" s="7"/>
       <c r="H401" s="5" t="s">
-        <v>1883</v>
+        <v>1884</v>
       </c>
       <c r="I401" s="5" t="s">
-        <v>1883</v>
+        <v>1884</v>
       </c>
       <c r="J401" s="5" t="s">
         <v>1669</v>
       </c>
       <c r="K401" s="8" t="s">
-        <v>1884</v>
+        <v>1885</v>
       </c>
     </row>
     <row r="402" spans="1:11" x14ac:dyDescent="0.2">
@@ -21918,20 +21951,20 @@
         <v>1648</v>
       </c>
       <c r="F402" s="5" t="s">
-        <v>1885</v>
+        <v>1886</v>
       </c>
       <c r="G402" s="7"/>
       <c r="H402" s="5" t="s">
-        <v>1886</v>
+        <v>1887</v>
       </c>
       <c r="I402" s="5" t="s">
-        <v>1887</v>
+        <v>1888</v>
       </c>
       <c r="J402" s="5" t="s">
         <v>1669</v>
       </c>
       <c r="K402" s="8" t="s">
-        <v>1888</v>
+        <v>1889</v>
       </c>
     </row>
     <row r="403" spans="1:11" x14ac:dyDescent="0.2">
@@ -21951,20 +21984,20 @@
         <v>1648</v>
       </c>
       <c r="F403" s="5" t="s">
-        <v>1889</v>
+        <v>1890</v>
       </c>
       <c r="G403" s="7"/>
       <c r="H403" s="5" t="s">
-        <v>1890</v>
+        <v>1891</v>
       </c>
       <c r="I403" s="5" t="s">
-        <v>1891</v>
+        <v>1892</v>
       </c>
       <c r="J403" s="5" t="s">
         <v>1669</v>
       </c>
       <c r="K403" s="8" t="s">
-        <v>1892</v>
+        <v>1893</v>
       </c>
     </row>
     <row r="404" spans="1:11" x14ac:dyDescent="0.2">
@@ -21984,14 +22017,14 @@
         <v>1519</v>
       </c>
       <c r="F404" s="5" t="s">
-        <v>1893</v>
+        <v>1894</v>
       </c>
       <c r="G404" s="7"/>
       <c r="H404" s="5" t="s">
-        <v>1894</v>
+        <v>1895</v>
       </c>
       <c r="I404" s="5" t="s">
-        <v>1895</v>
+        <v>1896</v>
       </c>
       <c r="J404" s="5" t="s">
         <v>1524</v>
@@ -22009,26 +22042,26 @@
         <v>588</v>
       </c>
       <c r="D405" s="5" t="s">
-        <v>1896</v>
+        <v>1897</v>
       </c>
       <c r="E405" s="5" t="s">
-        <v>1897</v>
+        <v>1898</v>
       </c>
       <c r="F405" s="5" t="s">
-        <v>1898</v>
+        <v>1899</v>
       </c>
       <c r="G405" s="7"/>
       <c r="H405" s="5" t="s">
-        <v>1899</v>
+        <v>1900</v>
       </c>
       <c r="I405" s="5" t="s">
-        <v>1900</v>
+        <v>1901</v>
       </c>
       <c r="J405" s="5" t="s">
         <v>619</v>
       </c>
       <c r="K405" s="8" t="s">
-        <v>1901</v>
+        <v>1902</v>
       </c>
     </row>
     <row r="406" spans="1:11" x14ac:dyDescent="0.2">
@@ -22042,20 +22075,20 @@
         <v>1472</v>
       </c>
       <c r="D406" s="5" t="s">
-        <v>1902</v>
+        <v>1903</v>
       </c>
       <c r="E406" s="5" t="s">
-        <v>1903</v>
+        <v>1904</v>
       </c>
       <c r="F406" s="5" t="s">
-        <v>1904</v>
+        <v>1905</v>
       </c>
       <c r="G406" s="7"/>
       <c r="H406" s="5" t="s">
-        <v>1905</v>
+        <v>1906</v>
       </c>
       <c r="I406" s="5" t="s">
-        <v>1905</v>
+        <v>1906</v>
       </c>
       <c r="J406" s="5" t="s">
         <v>619</v>
@@ -22073,26 +22106,26 @@
         <v>1287</v>
       </c>
       <c r="D407" s="5" t="s">
-        <v>1906</v>
+        <v>1907</v>
       </c>
       <c r="E407" s="5" t="s">
-        <v>1907</v>
+        <v>1908</v>
       </c>
       <c r="F407" s="5" t="s">
-        <v>1908</v>
+        <v>1909</v>
       </c>
       <c r="G407" s="7"/>
       <c r="H407" s="5" t="s">
-        <v>1907</v>
+        <v>1908</v>
       </c>
       <c r="I407" s="5" t="s">
-        <v>1907</v>
+        <v>1908</v>
       </c>
       <c r="J407" s="5" t="s">
-        <v>1909</v>
+        <v>1910</v>
       </c>
       <c r="K407" s="8" t="s">
-        <v>1910</v>
+        <v>1911</v>
       </c>
     </row>
     <row r="408" spans="1:11" x14ac:dyDescent="0.2">
@@ -22112,14 +22145,14 @@
         <v>760</v>
       </c>
       <c r="F408" s="5" t="s">
-        <v>1911</v>
+        <v>1912</v>
       </c>
       <c r="G408" s="7"/>
       <c r="H408" s="5" t="s">
-        <v>1912</v>
+        <v>1913</v>
       </c>
       <c r="I408" s="5" t="s">
-        <v>1913</v>
+        <v>1914</v>
       </c>
       <c r="J408" s="5" t="s">
         <v>619</v>
@@ -22137,26 +22170,26 @@
         <v>67</v>
       </c>
       <c r="D409" s="5" t="s">
-        <v>1838</v>
+        <v>1839</v>
       </c>
       <c r="E409" s="5" t="s">
-        <v>1839</v>
+        <v>1840</v>
       </c>
       <c r="F409" s="5" t="s">
-        <v>1914</v>
+        <v>1915</v>
       </c>
       <c r="G409" s="7"/>
       <c r="H409" s="5" t="s">
-        <v>1915</v>
+        <v>1916</v>
       </c>
       <c r="I409" s="5" t="s">
-        <v>1915</v>
+        <v>1916</v>
       </c>
       <c r="J409" s="5" t="s">
         <v>177</v>
       </c>
       <c r="K409" s="8" t="s">
-        <v>1916</v>
+        <v>1917</v>
       </c>
     </row>
     <row r="410" spans="1:11" x14ac:dyDescent="0.2">
@@ -22170,26 +22203,26 @@
         <v>1472</v>
       </c>
       <c r="D410" s="5" t="s">
-        <v>1917</v>
+        <v>1918</v>
       </c>
       <c r="E410" s="5" t="s">
-        <v>1918</v>
+        <v>1919</v>
       </c>
       <c r="F410" s="5" t="s">
-        <v>1919</v>
+        <v>1920</v>
       </c>
       <c r="G410" s="7"/>
       <c r="H410" s="5" t="s">
-        <v>1920</v>
+        <v>1921</v>
       </c>
       <c r="I410" s="5" t="s">
-        <v>1921</v>
+        <v>1922</v>
       </c>
       <c r="J410" s="5" t="s">
         <v>1524</v>
       </c>
       <c r="K410" s="8" t="s">
-        <v>1922</v>
+        <v>1923</v>
       </c>
     </row>
     <row r="411" spans="1:11" x14ac:dyDescent="0.2">
@@ -22203,26 +22236,26 @@
         <v>277</v>
       </c>
       <c r="D411" s="5" t="s">
-        <v>1923</v>
+        <v>1924</v>
       </c>
       <c r="E411" s="5" t="s">
-        <v>1924</v>
+        <v>1925</v>
       </c>
       <c r="F411" s="5" t="s">
-        <v>1925</v>
+        <v>1926</v>
       </c>
       <c r="G411" s="7"/>
       <c r="H411" s="5" t="s">
-        <v>1926</v>
+        <v>1927</v>
       </c>
       <c r="I411" s="5" t="s">
-        <v>1927</v>
+        <v>1928</v>
       </c>
       <c r="J411" s="5" t="s">
         <v>283</v>
       </c>
       <c r="K411" s="8" t="s">
-        <v>1928</v>
+        <v>1929</v>
       </c>
     </row>
     <row r="412" spans="1:11" x14ac:dyDescent="0.2">
@@ -22236,24 +22269,24 @@
         <v>1472</v>
       </c>
       <c r="D412" s="5" t="s">
-        <v>1929</v>
+        <v>1930</v>
       </c>
       <c r="E412" s="5" t="s">
-        <v>1930</v>
+        <v>1931</v>
       </c>
       <c r="F412" s="5" t="s">
-        <v>1931</v>
+        <v>1932</v>
       </c>
       <c r="G412" s="7"/>
       <c r="H412" s="5" t="s">
-        <v>1932</v>
+        <v>1933</v>
       </c>
       <c r="I412" s="7"/>
       <c r="J412" s="5" t="s">
         <v>1524</v>
       </c>
       <c r="K412" s="8" t="s">
-        <v>1933</v>
+        <v>1934</v>
       </c>
     </row>
     <row r="413" spans="1:11" x14ac:dyDescent="0.2">
@@ -22267,26 +22300,26 @@
         <v>1287</v>
       </c>
       <c r="D413" s="5" t="s">
-        <v>1934</v>
+        <v>1935</v>
       </c>
       <c r="E413" s="5" t="s">
-        <v>1935</v>
+        <v>1936</v>
       </c>
       <c r="F413" s="5" t="s">
-        <v>1936</v>
+        <v>1937</v>
       </c>
       <c r="G413" s="7"/>
       <c r="H413" s="5" t="s">
-        <v>1937</v>
+        <v>1938</v>
       </c>
       <c r="I413" s="5" t="s">
-        <v>1938</v>
+        <v>1939</v>
       </c>
       <c r="J413" s="5" t="s">
-        <v>1909</v>
+        <v>1910</v>
       </c>
       <c r="K413" s="8" t="s">
-        <v>1939</v>
+        <v>1940</v>
       </c>
     </row>
     <row r="414" spans="1:11" x14ac:dyDescent="0.2">
@@ -22306,20 +22339,20 @@
         <v>627</v>
       </c>
       <c r="F414" s="5" t="s">
-        <v>1940</v>
+        <v>1941</v>
       </c>
       <c r="G414" s="7"/>
       <c r="H414" s="5" t="s">
-        <v>1941</v>
+        <v>1942</v>
       </c>
       <c r="I414" s="5" t="s">
-        <v>1942</v>
+        <v>1943</v>
       </c>
       <c r="J414" s="5" t="s">
         <v>619</v>
       </c>
       <c r="K414" s="8" t="s">
-        <v>1943</v>
+        <v>1944</v>
       </c>
     </row>
     <row r="415" spans="1:11" x14ac:dyDescent="0.2">
@@ -22339,20 +22372,20 @@
         <v>46</v>
       </c>
       <c r="F415" s="5" t="s">
-        <v>1944</v>
+        <v>1945</v>
       </c>
       <c r="G415" s="7"/>
       <c r="H415" s="5" t="s">
-        <v>1945</v>
+        <v>1946</v>
       </c>
       <c r="I415" s="5" t="s">
-        <v>1946</v>
+        <v>1947</v>
       </c>
       <c r="J415" s="5" t="s">
         <v>51</v>
       </c>
       <c r="K415" s="8" t="s">
-        <v>1947</v>
+        <v>1948</v>
       </c>
     </row>
     <row r="416" spans="1:11" x14ac:dyDescent="0.2">
@@ -22372,20 +22405,20 @@
         <v>1637</v>
       </c>
       <c r="F416" s="5" t="s">
-        <v>1948</v>
+        <v>1949</v>
       </c>
       <c r="G416" s="7"/>
       <c r="H416" s="5" t="s">
-        <v>1949</v>
+        <v>1950</v>
       </c>
       <c r="I416" s="5" t="s">
-        <v>1950</v>
+        <v>1951</v>
       </c>
       <c r="J416" s="5" t="s">
         <v>1524</v>
       </c>
       <c r="K416" s="8" t="s">
-        <v>1951</v>
+        <v>1952</v>
       </c>
     </row>
     <row r="417" spans="1:11" x14ac:dyDescent="0.2">
@@ -22399,26 +22432,26 @@
         <v>1287</v>
       </c>
       <c r="D417" s="5" t="s">
-        <v>1952</v>
+        <v>1953</v>
       </c>
       <c r="E417" s="5" t="s">
-        <v>1953</v>
+        <v>1954</v>
       </c>
       <c r="F417" s="5" t="s">
-        <v>1954</v>
+        <v>1955</v>
       </c>
       <c r="G417" s="7"/>
       <c r="H417" s="5" t="s">
-        <v>1955</v>
+        <v>1956</v>
       </c>
       <c r="I417" s="5" t="s">
-        <v>1955</v>
+        <v>1956</v>
       </c>
       <c r="J417" s="5" t="s">
         <v>851</v>
       </c>
       <c r="K417" s="8" t="s">
-        <v>1956</v>
+        <v>1957</v>
       </c>
     </row>
     <row r="418" spans="1:11" x14ac:dyDescent="0.2">
@@ -22438,20 +22471,20 @@
         <v>25</v>
       </c>
       <c r="F418" s="5" t="s">
-        <v>1957</v>
+        <v>1958</v>
       </c>
       <c r="G418" s="7"/>
       <c r="H418" s="5" t="s">
-        <v>1958</v>
+        <v>1959</v>
       </c>
       <c r="I418" s="5" t="s">
-        <v>1959</v>
+        <v>1960</v>
       </c>
       <c r="J418" s="5" t="s">
         <v>34</v>
       </c>
       <c r="K418" s="8" t="s">
-        <v>1960</v>
+        <v>1961</v>
       </c>
     </row>
     <row r="419" spans="1:11" x14ac:dyDescent="0.2">
@@ -22471,20 +22504,20 @@
         <v>627</v>
       </c>
       <c r="F419" s="5" t="s">
-        <v>1961</v>
+        <v>1962</v>
       </c>
       <c r="G419" s="7"/>
       <c r="H419" s="5" t="s">
-        <v>1962</v>
+        <v>1963</v>
       </c>
       <c r="I419" s="5" t="s">
-        <v>1963</v>
+        <v>1964</v>
       </c>
       <c r="J419" s="5" t="s">
         <v>619</v>
       </c>
       <c r="K419" s="8" t="s">
-        <v>1964</v>
+        <v>1965</v>
       </c>
     </row>
     <row r="420" spans="1:11" x14ac:dyDescent="0.2">
@@ -22504,20 +22537,20 @@
         <v>627</v>
       </c>
       <c r="F420" s="5" t="s">
-        <v>1965</v>
+        <v>1966</v>
       </c>
       <c r="G420" s="7"/>
       <c r="H420" s="5" t="s">
-        <v>1966</v>
+        <v>1967</v>
       </c>
       <c r="I420" s="5" t="s">
-        <v>1967</v>
+        <v>1968</v>
       </c>
       <c r="J420" s="5" t="s">
         <v>619</v>
       </c>
       <c r="K420" s="8" t="s">
-        <v>1968</v>
+        <v>1969</v>
       </c>
     </row>
     <row r="421" spans="1:11" x14ac:dyDescent="0.2">
@@ -22531,26 +22564,26 @@
         <v>1287</v>
       </c>
       <c r="D421" s="5" t="s">
-        <v>1816</v>
+        <v>1817</v>
       </c>
       <c r="E421" s="5" t="s">
-        <v>1817</v>
+        <v>1818</v>
       </c>
       <c r="F421" s="5" t="s">
-        <v>1969</v>
+        <v>1970</v>
       </c>
       <c r="G421" s="7"/>
       <c r="H421" s="5" t="s">
-        <v>1819</v>
+        <v>1820</v>
       </c>
       <c r="I421" s="5" t="s">
-        <v>1970</v>
+        <v>1971</v>
       </c>
       <c r="J421" s="5" t="s">
         <v>1444</v>
       </c>
       <c r="K421" s="8" t="s">
-        <v>1971</v>
+        <v>1972</v>
       </c>
     </row>
     <row r="422" spans="1:11" x14ac:dyDescent="0.2">
@@ -22564,24 +22597,24 @@
         <v>1287</v>
       </c>
       <c r="D422" s="5" t="s">
-        <v>1952</v>
+        <v>1953</v>
       </c>
       <c r="E422" s="5" t="s">
-        <v>1953</v>
+        <v>1954</v>
       </c>
       <c r="F422" s="5" t="s">
-        <v>1972</v>
+        <v>1973</v>
       </c>
       <c r="G422" s="7"/>
       <c r="H422" s="5" t="s">
-        <v>1955</v>
+        <v>1956</v>
       </c>
       <c r="I422" s="7"/>
       <c r="J422" s="5" t="s">
         <v>1444</v>
       </c>
       <c r="K422" s="8" t="s">
-        <v>1973</v>
+        <v>1974</v>
       </c>
     </row>
     <row r="423" spans="1:11" x14ac:dyDescent="0.2">
@@ -22601,20 +22634,20 @@
         <v>25</v>
       </c>
       <c r="F423" s="5" t="s">
-        <v>1974</v>
+        <v>1975</v>
       </c>
       <c r="G423" s="7"/>
       <c r="H423" s="5" t="s">
-        <v>1975</v>
+        <v>1976</v>
       </c>
       <c r="I423" s="5" t="s">
-        <v>1976</v>
+        <v>1977</v>
       </c>
       <c r="J423" s="5" t="s">
         <v>34</v>
       </c>
       <c r="K423" s="8" t="s">
-        <v>1977</v>
+        <v>1978</v>
       </c>
     </row>
     <row r="424" spans="1:11" x14ac:dyDescent="0.2">
@@ -22628,17 +22661,17 @@
         <v>1472</v>
       </c>
       <c r="D424" s="5" t="s">
-        <v>1978</v>
+        <v>1979</v>
       </c>
       <c r="E424" s="5" t="s">
-        <v>1979</v>
+        <v>1980</v>
       </c>
       <c r="F424" s="5" t="s">
-        <v>1980</v>
+        <v>1981</v>
       </c>
       <c r="G424" s="7"/>
       <c r="H424" s="5" t="s">
-        <v>1981</v>
+        <v>1982</v>
       </c>
       <c r="I424" s="5" t="s">
         <v>1551</v>
@@ -22647,7 +22680,7 @@
         <v>1552</v>
       </c>
       <c r="K424" s="8" t="s">
-        <v>1982</v>
+        <v>1983</v>
       </c>
     </row>
     <row r="425" spans="1:11" x14ac:dyDescent="0.2">
@@ -22661,13 +22694,13 @@
         <v>1472</v>
       </c>
       <c r="D425" s="5" t="s">
-        <v>1983</v>
+        <v>1984</v>
       </c>
       <c r="E425" s="5" t="s">
-        <v>1984</v>
+        <v>1985</v>
       </c>
       <c r="F425" s="5" t="s">
-        <v>1985</v>
+        <v>1986</v>
       </c>
       <c r="G425" s="7"/>
       <c r="H425" s="5" t="s">
@@ -22692,23 +22725,23 @@
         <v>1472</v>
       </c>
       <c r="D426" s="5" t="s">
-        <v>1983</v>
+        <v>1984</v>
       </c>
       <c r="E426" s="5" t="s">
-        <v>1984</v>
+        <v>1985</v>
       </c>
       <c r="F426" s="5" t="s">
-        <v>1986</v>
+        <v>1987</v>
       </c>
       <c r="G426" s="7"/>
       <c r="H426" s="5" t="s">
-        <v>1987</v>
+        <v>1988</v>
       </c>
       <c r="I426" s="5" t="s">
-        <v>1988</v>
+        <v>1989</v>
       </c>
       <c r="J426" s="5" t="s">
-        <v>1989</v>
+        <v>1990</v>
       </c>
       <c r="K426" s="6"/>
     </row>
@@ -22729,7 +22762,7 @@
         <v>1294</v>
       </c>
       <c r="F427" s="5" t="s">
-        <v>1990</v>
+        <v>1991</v>
       </c>
       <c r="G427" s="7"/>
       <c r="H427" s="5" t="s">
@@ -22758,11 +22791,11 @@
         <v>1289</v>
       </c>
       <c r="F428" s="5" t="s">
-        <v>1991</v>
+        <v>1992</v>
       </c>
       <c r="G428" s="7"/>
       <c r="H428" s="5" t="s">
-        <v>1992</v>
+        <v>1993</v>
       </c>
       <c r="I428" s="7"/>
       <c r="J428" s="5" t="s">
@@ -22787,7 +22820,7 @@
         <v>1294</v>
       </c>
       <c r="F429" s="5" t="s">
-        <v>1993</v>
+        <v>1994</v>
       </c>
       <c r="G429" s="7"/>
       <c r="H429" s="5" t="s">
@@ -22816,7 +22849,7 @@
         <v>1299</v>
       </c>
       <c r="F430" s="5" t="s">
-        <v>1994</v>
+        <v>1995</v>
       </c>
       <c r="G430" s="7"/>
       <c r="H430" s="5" t="s">
@@ -22827,7 +22860,7 @@
         <v>851</v>
       </c>
       <c r="K430" s="8" t="s">
-        <v>1995</v>
+        <v>1996</v>
       </c>
     </row>
     <row r="431" spans="1:11" x14ac:dyDescent="0.2">
@@ -22847,11 +22880,11 @@
         <v>1299</v>
       </c>
       <c r="F431" s="5" t="s">
-        <v>1996</v>
+        <v>1997</v>
       </c>
       <c r="G431" s="7"/>
       <c r="H431" s="5" t="s">
-        <v>1997</v>
+        <v>1998</v>
       </c>
       <c r="I431" s="7"/>
       <c r="J431" s="5" t="s">
@@ -22870,26 +22903,26 @@
         <v>588</v>
       </c>
       <c r="D432" s="5" t="s">
-        <v>1998</v>
+        <v>1999</v>
       </c>
       <c r="E432" s="5" t="s">
-        <v>1999</v>
+        <v>2000</v>
       </c>
       <c r="F432" s="5" t="s">
-        <v>2000</v>
+        <v>2001</v>
       </c>
       <c r="G432" s="7"/>
       <c r="H432" s="5" t="s">
-        <v>2001</v>
+        <v>2002</v>
       </c>
       <c r="I432" s="5" t="s">
-        <v>2002</v>
+        <v>2003</v>
       </c>
       <c r="J432" s="5" t="s">
         <v>641</v>
       </c>
       <c r="K432" s="8" t="s">
-        <v>2003</v>
+        <v>2004</v>
       </c>
     </row>
     <row r="433" spans="1:11" x14ac:dyDescent="0.2">
@@ -22900,29 +22933,29 @@
         <v>11</v>
       </c>
       <c r="C433" s="5" t="s">
-        <v>1831</v>
+        <v>1832</v>
       </c>
       <c r="D433" s="5" t="s">
-        <v>2004</v>
+        <v>2005</v>
       </c>
       <c r="E433" s="5" t="s">
-        <v>2005</v>
+        <v>2006</v>
       </c>
       <c r="F433" s="5" t="s">
-        <v>2006</v>
+        <v>2007</v>
       </c>
       <c r="G433" s="7"/>
       <c r="H433" s="5" t="s">
-        <v>2007</v>
+        <v>2008</v>
       </c>
       <c r="I433" s="5" t="s">
-        <v>2008</v>
+        <v>2009</v>
       </c>
       <c r="J433" s="5" t="s">
         <v>1786</v>
       </c>
       <c r="K433" s="8" t="s">
-        <v>2009</v>
+        <v>2010</v>
       </c>
     </row>
     <row r="434" spans="1:11" x14ac:dyDescent="0.2">
@@ -22936,26 +22969,26 @@
         <v>588</v>
       </c>
       <c r="D434" s="5" t="s">
-        <v>2010</v>
+        <v>2011</v>
       </c>
       <c r="E434" s="5" t="s">
-        <v>2011</v>
+        <v>2012</v>
       </c>
       <c r="F434" s="5" t="s">
-        <v>2012</v>
+        <v>2013</v>
       </c>
       <c r="G434" s="7"/>
       <c r="H434" s="5" t="s">
-        <v>2013</v>
+        <v>2014</v>
       </c>
       <c r="I434" s="5" t="s">
-        <v>2014</v>
+        <v>2015</v>
       </c>
       <c r="J434" s="5" t="s">
-        <v>2015</v>
+        <v>2016</v>
       </c>
       <c r="K434" s="8" t="s">
-        <v>2016</v>
+        <v>2017</v>
       </c>
     </row>
     <row r="435" spans="1:11" x14ac:dyDescent="0.2">
@@ -22975,20 +23008,20 @@
         <v>25</v>
       </c>
       <c r="F435" s="5" t="s">
-        <v>2017</v>
+        <v>2018</v>
       </c>
       <c r="G435" s="7"/>
       <c r="H435" s="5" t="s">
-        <v>2018</v>
+        <v>2019</v>
       </c>
       <c r="I435" s="5" t="s">
-        <v>2019</v>
+        <v>2020</v>
       </c>
       <c r="J435" s="5" t="s">
         <v>34</v>
       </c>
       <c r="K435" s="8" t="s">
-        <v>2020</v>
+        <v>2021</v>
       </c>
     </row>
     <row r="436" spans="1:11" x14ac:dyDescent="0.2">
@@ -23002,26 +23035,26 @@
         <v>765</v>
       </c>
       <c r="D436" s="5" t="s">
-        <v>2021</v>
+        <v>2022</v>
       </c>
       <c r="E436" s="5" t="s">
-        <v>2022</v>
+        <v>2023</v>
       </c>
       <c r="F436" s="5" t="s">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="G436" s="7"/>
       <c r="H436" s="5" t="s">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="I436" s="5" t="s">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="J436" s="5" t="s">
         <v>797</v>
       </c>
       <c r="K436" s="8" t="s">
-        <v>2026</v>
+        <v>2027</v>
       </c>
     </row>
     <row r="437" spans="1:11" x14ac:dyDescent="0.2">
@@ -23041,20 +23074,20 @@
         <v>1715</v>
       </c>
       <c r="F437" s="5" t="s">
-        <v>2027</v>
+        <v>2028</v>
       </c>
       <c r="G437" s="7"/>
       <c r="H437" s="5" t="s">
-        <v>2028</v>
+        <v>2029</v>
       </c>
       <c r="I437" s="5" t="s">
-        <v>2029</v>
+        <v>2030</v>
       </c>
       <c r="J437" s="5" t="s">
         <v>1524</v>
       </c>
       <c r="K437" s="8" t="s">
-        <v>2030</v>
+        <v>2031</v>
       </c>
     </row>
     <row r="438" spans="1:11" x14ac:dyDescent="0.2">
@@ -23074,20 +23107,20 @@
         <v>1737</v>
       </c>
       <c r="F438" s="5" t="s">
-        <v>2031</v>
+        <v>2032</v>
       </c>
       <c r="G438" s="7"/>
       <c r="H438" s="5" t="s">
-        <v>2032</v>
+        <v>2033</v>
       </c>
       <c r="I438" s="5" t="s">
-        <v>2033</v>
+        <v>2034</v>
       </c>
       <c r="J438" s="5" t="s">
         <v>1524</v>
       </c>
       <c r="K438" s="8" t="s">
-        <v>2034</v>
+        <v>2035</v>
       </c>
     </row>
     <row r="439" spans="1:11" x14ac:dyDescent="0.2">
@@ -23107,20 +23140,20 @@
         <v>1327</v>
       </c>
       <c r="F439" s="5" t="s">
-        <v>2035</v>
+        <v>2036</v>
       </c>
       <c r="G439" s="7"/>
       <c r="H439" s="5" t="s">
-        <v>2036</v>
+        <v>2037</v>
       </c>
       <c r="I439" s="5" t="s">
-        <v>2037</v>
+        <v>2038</v>
       </c>
       <c r="J439" s="5" t="s">
         <v>851</v>
       </c>
       <c r="K439" s="8" t="s">
-        <v>2038</v>
+        <v>2039</v>
       </c>
     </row>
     <row r="440" spans="1:11" x14ac:dyDescent="0.2">
@@ -23134,26 +23167,26 @@
         <v>1472</v>
       </c>
       <c r="D440" s="5" t="s">
-        <v>2039</v>
+        <v>2040</v>
       </c>
       <c r="E440" s="5" t="s">
-        <v>2040</v>
+        <v>2041</v>
       </c>
       <c r="F440" s="5" t="s">
-        <v>2041</v>
+        <v>2042</v>
       </c>
       <c r="G440" s="7"/>
       <c r="H440" s="5" t="s">
-        <v>2042</v>
+        <v>2043</v>
       </c>
       <c r="I440" s="5" t="s">
-        <v>2043</v>
+        <v>2044</v>
       </c>
       <c r="J440" s="5" t="s">
         <v>1479</v>
       </c>
       <c r="K440" s="8" t="s">
-        <v>2044</v>
+        <v>2045</v>
       </c>
     </row>
     <row r="441" spans="1:11" x14ac:dyDescent="0.2">
@@ -23167,26 +23200,26 @@
         <v>588</v>
       </c>
       <c r="D441" s="5" t="s">
-        <v>2045</v>
+        <v>2046</v>
       </c>
       <c r="E441" s="5" t="s">
-        <v>2046</v>
+        <v>2047</v>
       </c>
       <c r="F441" s="5" t="s">
-        <v>2047</v>
+        <v>2048</v>
       </c>
       <c r="G441" s="7"/>
       <c r="H441" s="5" t="s">
-        <v>2048</v>
+        <v>2049</v>
       </c>
       <c r="I441" s="5" t="s">
-        <v>2049</v>
+        <v>2050</v>
       </c>
       <c r="J441" s="5" t="s">
         <v>619</v>
       </c>
       <c r="K441" s="8" t="s">
-        <v>2050</v>
+        <v>2051</v>
       </c>
     </row>
     <row r="442" spans="1:11" x14ac:dyDescent="0.2">
@@ -23206,20 +23239,20 @@
         <v>1474</v>
       </c>
       <c r="F442" s="5" t="s">
-        <v>2051</v>
+        <v>2052</v>
       </c>
       <c r="G442" s="7"/>
       <c r="H442" s="5" t="s">
-        <v>2052</v>
+        <v>2053</v>
       </c>
       <c r="I442" s="5" t="s">
-        <v>2053</v>
+        <v>2054</v>
       </c>
       <c r="J442" s="5" t="s">
         <v>1524</v>
       </c>
       <c r="K442" s="8" t="s">
-        <v>2054</v>
+        <v>2055</v>
       </c>
     </row>
     <row r="443" spans="1:11" x14ac:dyDescent="0.2">
@@ -23233,26 +23266,26 @@
         <v>1472</v>
       </c>
       <c r="D443" s="5" t="s">
-        <v>2055</v>
+        <v>2056</v>
       </c>
       <c r="E443" s="5" t="s">
-        <v>2056</v>
+        <v>2057</v>
       </c>
       <c r="F443" s="5" t="s">
-        <v>2057</v>
+        <v>2058</v>
       </c>
       <c r="G443" s="7"/>
       <c r="H443" s="5" t="s">
-        <v>2058</v>
+        <v>2059</v>
       </c>
       <c r="I443" s="5" t="s">
-        <v>2059</v>
+        <v>2060</v>
       </c>
       <c r="J443" s="5" t="s">
         <v>1524</v>
       </c>
       <c r="K443" s="8" t="s">
-        <v>2060</v>
+        <v>2061</v>
       </c>
     </row>
     <row r="444" spans="1:11" x14ac:dyDescent="0.2">
@@ -23266,26 +23299,26 @@
         <v>765</v>
       </c>
       <c r="D444" s="5" t="s">
-        <v>2061</v>
+        <v>2062</v>
       </c>
       <c r="E444" s="5" t="s">
-        <v>2062</v>
+        <v>2063</v>
       </c>
       <c r="F444" s="5" t="s">
-        <v>2063</v>
+        <v>2064</v>
       </c>
       <c r="G444" s="7"/>
       <c r="H444" s="5" t="s">
-        <v>2064</v>
+        <v>2065</v>
       </c>
       <c r="I444" s="5" t="s">
-        <v>2065</v>
+        <v>2066</v>
       </c>
       <c r="J444" s="5" t="s">
         <v>797</v>
       </c>
       <c r="K444" s="8" t="s">
-        <v>2066</v>
+        <v>2067</v>
       </c>
     </row>
     <row r="445" spans="1:11" x14ac:dyDescent="0.2">
@@ -23299,26 +23332,26 @@
         <v>969</v>
       </c>
       <c r="D445" s="5" t="s">
-        <v>2067</v>
+        <v>2068</v>
       </c>
       <c r="E445" s="5" t="s">
-        <v>2068</v>
+        <v>2069</v>
       </c>
       <c r="F445" s="5" t="s">
-        <v>2069</v>
+        <v>2070</v>
       </c>
       <c r="G445" s="7"/>
       <c r="H445" s="5" t="s">
-        <v>2070</v>
+        <v>2071</v>
       </c>
       <c r="I445" s="5" t="s">
-        <v>2071</v>
+        <v>2072</v>
       </c>
       <c r="J445" s="5" t="s">
         <v>1005</v>
       </c>
       <c r="K445" s="8" t="s">
-        <v>2072</v>
+        <v>2073</v>
       </c>
     </row>
     <row r="446" spans="1:11" x14ac:dyDescent="0.2">
@@ -23338,18 +23371,18 @@
         <v>1519</v>
       </c>
       <c r="F446" s="5" t="s">
-        <v>2073</v>
+        <v>2074</v>
       </c>
       <c r="G446" s="7"/>
       <c r="H446" s="5" t="s">
-        <v>2074</v>
+        <v>2075</v>
       </c>
       <c r="I446" s="7"/>
       <c r="J446" s="5" t="s">
         <v>1524</v>
       </c>
       <c r="K446" s="8" t="s">
-        <v>2075</v>
+        <v>2076</v>
       </c>
     </row>
     <row r="447" spans="1:11" x14ac:dyDescent="0.2">
@@ -23369,20 +23402,20 @@
         <v>1637</v>
       </c>
       <c r="F447" s="5" t="s">
-        <v>2076</v>
+        <v>2077</v>
       </c>
       <c r="G447" s="7"/>
       <c r="H447" s="5" t="s">
-        <v>2077</v>
+        <v>2078</v>
       </c>
       <c r="I447" s="5" t="s">
-        <v>2078</v>
+        <v>2079</v>
       </c>
       <c r="J447" s="5" t="s">
         <v>1669</v>
       </c>
       <c r="K447" s="8" t="s">
-        <v>2079</v>
+        <v>2080</v>
       </c>
     </row>
     <row r="448" spans="1:11" x14ac:dyDescent="0.2">
@@ -23402,20 +23435,20 @@
         <v>1498</v>
       </c>
       <c r="F448" s="5" t="s">
-        <v>2080</v>
+        <v>2081</v>
       </c>
       <c r="G448" s="7"/>
       <c r="H448" s="5" t="s">
-        <v>2081</v>
+        <v>2082</v>
       </c>
       <c r="I448" s="5" t="s">
-        <v>2082</v>
+        <v>2083</v>
       </c>
       <c r="J448" s="5" t="s">
         <v>1669</v>
       </c>
       <c r="K448" s="8" t="s">
-        <v>2083</v>
+        <v>2084</v>
       </c>
     </row>
     <row r="449" spans="1:11" x14ac:dyDescent="0.2">
@@ -23429,26 +23462,26 @@
         <v>588</v>
       </c>
       <c r="D449" s="5" t="s">
-        <v>2084</v>
+        <v>2085</v>
       </c>
       <c r="E449" s="5" t="s">
-        <v>2085</v>
+        <v>2086</v>
       </c>
       <c r="F449" s="5" t="s">
-        <v>2086</v>
+        <v>2087</v>
       </c>
       <c r="G449" s="7"/>
       <c r="H449" s="5" t="s">
-        <v>2087</v>
+        <v>2088</v>
       </c>
       <c r="I449" s="5" t="s">
-        <v>2088</v>
+        <v>2089</v>
       </c>
       <c r="J449" s="5" t="s">
         <v>619</v>
       </c>
       <c r="K449" s="8" t="s">
-        <v>2089</v>
+        <v>2090</v>
       </c>
     </row>
     <row r="450" spans="1:11" x14ac:dyDescent="0.2">
@@ -23468,20 +23501,20 @@
         <v>62</v>
       </c>
       <c r="F450" s="5" t="s">
-        <v>2090</v>
+        <v>2091</v>
       </c>
       <c r="G450" s="7"/>
       <c r="H450" s="5" t="s">
-        <v>2091</v>
+        <v>2092</v>
       </c>
       <c r="I450" s="5" t="s">
-        <v>2092</v>
+        <v>2093</v>
       </c>
       <c r="J450" s="5" t="s">
-        <v>2093</v>
+        <v>2094</v>
       </c>
       <c r="K450" s="8" t="s">
-        <v>2094</v>
+        <v>2095</v>
       </c>
     </row>
     <row r="451" spans="1:11" x14ac:dyDescent="0.2">
@@ -23495,26 +23528,26 @@
         <v>1472</v>
       </c>
       <c r="D451" s="5" t="s">
-        <v>2095</v>
+        <v>2096</v>
       </c>
       <c r="E451" s="5" t="s">
-        <v>2096</v>
+        <v>2097</v>
       </c>
       <c r="F451" s="5" t="s">
-        <v>2097</v>
+        <v>2098</v>
       </c>
       <c r="G451" s="7"/>
       <c r="H451" s="5" t="s">
-        <v>2098</v>
+        <v>2099</v>
       </c>
       <c r="I451" s="5" t="s">
-        <v>2099</v>
+        <v>2100</v>
       </c>
       <c r="J451" s="5" t="s">
         <v>1524</v>
       </c>
       <c r="K451" s="8" t="s">
-        <v>2100</v>
+        <v>2101</v>
       </c>
     </row>
     <row r="452" spans="1:11" x14ac:dyDescent="0.2">
@@ -23526,24 +23559,24 @@
         <v>1472</v>
       </c>
       <c r="D452" s="5" t="s">
-        <v>2095</v>
+        <v>2096</v>
       </c>
       <c r="E452" s="5" t="s">
-        <v>2096</v>
+        <v>2097</v>
       </c>
       <c r="F452" s="5" t="s">
-        <v>2101</v>
+        <v>2102</v>
       </c>
       <c r="G452" s="7"/>
       <c r="H452" s="5" t="s">
-        <v>2102</v>
+        <v>2103</v>
       </c>
       <c r="I452" s="7"/>
       <c r="J452" s="5" t="s">
         <v>1524</v>
       </c>
       <c r="K452" s="8" t="s">
-        <v>2103</v>
+        <v>2104</v>
       </c>
     </row>
     <row r="453" spans="1:11" x14ac:dyDescent="0.2">
@@ -23555,24 +23588,24 @@
         <v>1472</v>
       </c>
       <c r="D453" s="5" t="s">
-        <v>2104</v>
+        <v>2105</v>
       </c>
       <c r="E453" s="5" t="s">
-        <v>2105</v>
+        <v>2106</v>
       </c>
       <c r="F453" s="5" t="s">
-        <v>2106</v>
+        <v>2107</v>
       </c>
       <c r="G453" s="7"/>
       <c r="H453" s="5" t="s">
-        <v>2107</v>
+        <v>2108</v>
       </c>
       <c r="I453" s="7"/>
       <c r="J453" s="5" t="s">
         <v>1524</v>
       </c>
       <c r="K453" s="8" t="s">
-        <v>2103</v>
+        <v>2104</v>
       </c>
     </row>
     <row r="454" spans="1:11" x14ac:dyDescent="0.2">
@@ -23584,24 +23617,24 @@
         <v>1472</v>
       </c>
       <c r="D454" s="5" t="s">
-        <v>2104</v>
+        <v>2105</v>
       </c>
       <c r="E454" s="5" t="s">
-        <v>2105</v>
+        <v>2106</v>
       </c>
       <c r="F454" s="5" t="s">
-        <v>2108</v>
+        <v>2109</v>
       </c>
       <c r="G454" s="7"/>
       <c r="H454" s="5" t="s">
-        <v>2109</v>
+        <v>2110</v>
       </c>
       <c r="I454" s="7"/>
       <c r="J454" s="5" t="s">
         <v>1524</v>
       </c>
       <c r="K454" s="8" t="s">
-        <v>2110</v>
+        <v>2111</v>
       </c>
     </row>
     <row r="455" spans="1:11" x14ac:dyDescent="0.2">
@@ -23613,24 +23646,24 @@
         <v>1472</v>
       </c>
       <c r="D455" s="5" t="s">
-        <v>2104</v>
+        <v>2105</v>
       </c>
       <c r="E455" s="5" t="s">
-        <v>2105</v>
+        <v>2106</v>
       </c>
       <c r="F455" s="5" t="s">
-        <v>2111</v>
+        <v>2112</v>
       </c>
       <c r="G455" s="7"/>
       <c r="H455" s="5" t="s">
-        <v>2112</v>
+        <v>2113</v>
       </c>
       <c r="I455" s="7"/>
       <c r="J455" s="5" t="s">
         <v>1524</v>
       </c>
       <c r="K455" s="8" t="s">
-        <v>2103</v>
+        <v>2104</v>
       </c>
     </row>
     <row r="456" spans="1:11" x14ac:dyDescent="0.2">
@@ -23642,24 +23675,24 @@
         <v>1472</v>
       </c>
       <c r="D456" s="5" t="s">
-        <v>2113</v>
+        <v>2114</v>
       </c>
       <c r="E456" s="5" t="s">
-        <v>2114</v>
+        <v>2115</v>
       </c>
       <c r="F456" s="5" t="s">
-        <v>2115</v>
+        <v>2116</v>
       </c>
       <c r="G456" s="7"/>
       <c r="H456" s="5" t="s">
-        <v>2116</v>
+        <v>2117</v>
       </c>
       <c r="I456" s="7"/>
       <c r="J456" s="5" t="s">
         <v>1524</v>
       </c>
       <c r="K456" s="8" t="s">
-        <v>2103</v>
+        <v>2104</v>
       </c>
     </row>
     <row r="457" spans="1:11" x14ac:dyDescent="0.2">
@@ -23673,26 +23706,26 @@
         <v>1472</v>
       </c>
       <c r="D457" s="5" t="s">
-        <v>2117</v>
+        <v>2118</v>
       </c>
       <c r="E457" s="5" t="s">
-        <v>2118</v>
+        <v>2119</v>
       </c>
       <c r="F457" s="5" t="s">
-        <v>2119</v>
+        <v>2120</v>
       </c>
       <c r="G457" s="7"/>
       <c r="H457" s="5" t="s">
-        <v>2120</v>
+        <v>2121</v>
       </c>
       <c r="I457" s="5" t="s">
-        <v>2121</v>
+        <v>2122</v>
       </c>
       <c r="J457" s="5" t="s">
         <v>1524</v>
       </c>
       <c r="K457" s="8" t="s">
-        <v>2122</v>
+        <v>2123</v>
       </c>
     </row>
     <row r="458" spans="1:11" x14ac:dyDescent="0.2">
@@ -23712,20 +23745,20 @@
         <v>62</v>
       </c>
       <c r="F458" s="5" t="s">
-        <v>2123</v>
+        <v>2124</v>
       </c>
       <c r="G458" s="7"/>
       <c r="H458" s="5" t="s">
-        <v>2124</v>
+        <v>2125</v>
       </c>
       <c r="I458" s="5" t="s">
-        <v>2125</v>
+        <v>2126</v>
       </c>
       <c r="J458" s="5" t="s">
         <v>485</v>
       </c>
       <c r="K458" s="8" t="s">
-        <v>2126</v>
+        <v>2127</v>
       </c>
     </row>
     <row r="459" spans="1:11" x14ac:dyDescent="0.2">
@@ -23745,20 +23778,20 @@
         <v>669</v>
       </c>
       <c r="F459" s="5" t="s">
-        <v>2127</v>
+        <v>2128</v>
       </c>
       <c r="G459" s="7"/>
       <c r="H459" s="5" t="s">
-        <v>2128</v>
+        <v>2129</v>
       </c>
       <c r="I459" s="5" t="s">
-        <v>2129</v>
+        <v>2130</v>
       </c>
       <c r="J459" s="5" t="s">
-        <v>2130</v>
+        <v>2131</v>
       </c>
       <c r="K459" s="8" t="s">
-        <v>2131</v>
+        <v>2132</v>
       </c>
     </row>
     <row r="460" spans="1:11" x14ac:dyDescent="0.2">
@@ -23772,26 +23805,26 @@
         <v>588</v>
       </c>
       <c r="D460" s="5" t="s">
-        <v>2132</v>
+        <v>2133</v>
       </c>
       <c r="E460" s="5" t="s">
-        <v>2133</v>
+        <v>2134</v>
       </c>
       <c r="F460" s="5" t="s">
-        <v>2134</v>
+        <v>2135</v>
       </c>
       <c r="G460" s="7"/>
       <c r="H460" s="5" t="s">
-        <v>2135</v>
+        <v>2136</v>
       </c>
       <c r="I460" s="5" t="s">
-        <v>2136</v>
+        <v>2137</v>
       </c>
       <c r="J460" s="5" t="s">
-        <v>2130</v>
+        <v>2131</v>
       </c>
       <c r="K460" s="8" t="s">
-        <v>2137</v>
+        <v>2138</v>
       </c>
     </row>
     <row r="461" spans="1:11" x14ac:dyDescent="0.2">
@@ -23805,26 +23838,26 @@
         <v>588</v>
       </c>
       <c r="D461" s="5" t="s">
-        <v>1896</v>
+        <v>1897</v>
       </c>
       <c r="E461" s="5" t="s">
-        <v>1897</v>
+        <v>1898</v>
       </c>
       <c r="F461" s="5" t="s">
-        <v>2138</v>
+        <v>2139</v>
       </c>
       <c r="G461" s="7"/>
       <c r="H461" s="5" t="s">
-        <v>2139</v>
+        <v>2140</v>
       </c>
       <c r="I461" s="5" t="s">
-        <v>2140</v>
+        <v>2141</v>
       </c>
       <c r="J461" s="5" t="s">
-        <v>2130</v>
+        <v>2131</v>
       </c>
       <c r="K461" s="8" t="s">
-        <v>2141</v>
+        <v>2142</v>
       </c>
     </row>
     <row r="462" spans="1:11" x14ac:dyDescent="0.2">
@@ -23838,24 +23871,24 @@
         <v>1472</v>
       </c>
       <c r="D462" s="5" t="s">
-        <v>2142</v>
+        <v>2143</v>
       </c>
       <c r="E462" s="5" t="s">
-        <v>2143</v>
+        <v>2144</v>
       </c>
       <c r="F462" s="5" t="s">
-        <v>2144</v>
+        <v>2145</v>
       </c>
       <c r="G462" s="7"/>
       <c r="H462" s="5" t="s">
-        <v>2145</v>
+        <v>2146</v>
       </c>
       <c r="I462" s="7"/>
       <c r="J462" s="5" t="s">
         <v>1524</v>
       </c>
       <c r="K462" s="8" t="s">
-        <v>2146</v>
+        <v>2147</v>
       </c>
     </row>
     <row r="463" spans="1:11" x14ac:dyDescent="0.2">
@@ -23869,20 +23902,20 @@
         <v>1472</v>
       </c>
       <c r="D463" s="5" t="s">
-        <v>2147</v>
+        <v>2148</v>
       </c>
       <c r="E463" s="5" t="s">
-        <v>2148</v>
+        <v>2149</v>
       </c>
       <c r="F463" s="5" t="s">
-        <v>2149</v>
+        <v>2150</v>
       </c>
       <c r="G463" s="7"/>
       <c r="H463" s="5" t="s">
-        <v>2150</v>
+        <v>2151</v>
       </c>
       <c r="I463" s="5" t="s">
-        <v>2151</v>
+        <v>2152</v>
       </c>
       <c r="J463" s="5" t="s">
         <v>1524</v>
@@ -23900,26 +23933,26 @@
         <v>588</v>
       </c>
       <c r="D464" s="5" t="s">
-        <v>2152</v>
+        <v>2153</v>
       </c>
       <c r="E464" s="5" t="s">
-        <v>2153</v>
+        <v>2154</v>
       </c>
       <c r="F464" s="5" t="s">
-        <v>2154</v>
+        <v>2155</v>
       </c>
       <c r="G464" s="7"/>
       <c r="H464" s="5" t="s">
-        <v>2155</v>
+        <v>2156</v>
       </c>
       <c r="I464" s="5" t="s">
-        <v>2156</v>
+        <v>2157</v>
       </c>
       <c r="J464" s="5" t="s">
-        <v>2157</v>
+        <v>2158</v>
       </c>
       <c r="K464" s="8" t="s">
-        <v>2158</v>
+        <v>2159</v>
       </c>
     </row>
     <row r="465" spans="1:11" x14ac:dyDescent="0.2">
@@ -23933,20 +23966,20 @@
         <v>1472</v>
       </c>
       <c r="D465" s="5" t="s">
-        <v>1929</v>
+        <v>1930</v>
       </c>
       <c r="E465" s="5" t="s">
-        <v>1930</v>
+        <v>1931</v>
       </c>
       <c r="F465" s="5" t="s">
-        <v>2159</v>
+        <v>2160</v>
       </c>
       <c r="G465" s="7"/>
       <c r="H465" s="5" t="s">
-        <v>2160</v>
+        <v>2161</v>
       </c>
       <c r="I465" s="5" t="s">
-        <v>2161</v>
+        <v>2162</v>
       </c>
       <c r="J465" s="5" t="s">
         <v>1669</v>
@@ -23964,26 +23997,26 @@
         <v>1472</v>
       </c>
       <c r="D466" s="5" t="s">
-        <v>2104</v>
+        <v>2105</v>
       </c>
       <c r="E466" s="5" t="s">
-        <v>2105</v>
+        <v>2106</v>
       </c>
       <c r="F466" s="5" t="s">
-        <v>2162</v>
+        <v>2163</v>
       </c>
       <c r="G466" s="7"/>
       <c r="H466" s="5" t="s">
-        <v>2163</v>
+        <v>2164</v>
       </c>
       <c r="I466" s="5" t="s">
-        <v>2164</v>
+        <v>2165</v>
       </c>
       <c r="J466" s="5" t="s">
-        <v>2165</v>
+        <v>2166</v>
       </c>
       <c r="K466" s="8" t="s">
-        <v>2166</v>
+        <v>2167</v>
       </c>
     </row>
     <row r="467" spans="1:11" x14ac:dyDescent="0.2">
@@ -24003,17 +24036,17 @@
         <v>14</v>
       </c>
       <c r="F467" s="5" t="s">
-        <v>2167</v>
+        <v>2168</v>
       </c>
       <c r="G467" s="7"/>
       <c r="H467" s="5" t="s">
-        <v>2168</v>
+        <v>2169</v>
       </c>
       <c r="I467" s="5" t="s">
-        <v>2169</v>
+        <v>2170</v>
       </c>
       <c r="J467" s="5" t="s">
-        <v>2170</v>
+        <v>2171</v>
       </c>
       <c r="K467" s="6"/>
     </row>
@@ -24028,26 +24061,26 @@
         <v>1472</v>
       </c>
       <c r="D468" s="5" t="s">
-        <v>2171</v>
+        <v>2172</v>
       </c>
       <c r="E468" s="5" t="s">
-        <v>2172</v>
+        <v>2173</v>
       </c>
       <c r="F468" s="5" t="s">
-        <v>2173</v>
+        <v>2174</v>
       </c>
       <c r="G468" s="7"/>
       <c r="H468" s="5" t="s">
-        <v>2174</v>
+        <v>2175</v>
       </c>
       <c r="I468" s="5" t="s">
-        <v>2175</v>
+        <v>2176</v>
       </c>
       <c r="J468" s="5" t="s">
         <v>1669</v>
       </c>
       <c r="K468" s="8" t="s">
-        <v>2176</v>
+        <v>2177</v>
       </c>
     </row>
     <row r="469" spans="1:11" x14ac:dyDescent="0.2">
@@ -24061,26 +24094,26 @@
         <v>1472</v>
       </c>
       <c r="D469" s="5" t="s">
-        <v>2171</v>
+        <v>2172</v>
       </c>
       <c r="E469" s="5" t="s">
-        <v>2172</v>
+        <v>2173</v>
       </c>
       <c r="F469" s="5" t="s">
-        <v>2177</v>
+        <v>2178</v>
       </c>
       <c r="G469" s="7"/>
       <c r="H469" s="5" t="s">
-        <v>2178</v>
+        <v>2179</v>
       </c>
       <c r="I469" s="5" t="s">
-        <v>2179</v>
+        <v>2180</v>
       </c>
       <c r="J469" s="5" t="s">
         <v>1669</v>
       </c>
       <c r="K469" s="8" t="s">
-        <v>2180</v>
+        <v>2181</v>
       </c>
     </row>
     <row r="470" spans="1:11" x14ac:dyDescent="0.2">
@@ -24094,26 +24127,26 @@
         <v>765</v>
       </c>
       <c r="D470" s="5" t="s">
-        <v>2181</v>
+        <v>2182</v>
       </c>
       <c r="E470" s="5" t="s">
-        <v>2182</v>
+        <v>2183</v>
       </c>
       <c r="F470" s="5" t="s">
-        <v>2183</v>
+        <v>2184</v>
       </c>
       <c r="G470" s="7"/>
       <c r="H470" s="5" t="s">
-        <v>2184</v>
+        <v>2185</v>
       </c>
       <c r="I470" s="5" t="s">
-        <v>2185</v>
+        <v>2186</v>
       </c>
       <c r="J470" s="5" t="s">
         <v>797</v>
       </c>
       <c r="K470" s="8" t="s">
-        <v>2186</v>
+        <v>2187</v>
       </c>
     </row>
     <row r="471" spans="1:11" x14ac:dyDescent="0.2">
@@ -24133,11 +24166,11 @@
         <v>1322</v>
       </c>
       <c r="F471" s="5" t="s">
-        <v>2187</v>
+        <v>2188</v>
       </c>
       <c r="G471" s="7"/>
       <c r="H471" s="5" t="s">
-        <v>2188</v>
+        <v>2189</v>
       </c>
       <c r="I471" s="5" t="s">
         <v>1287</v>
@@ -24164,11 +24197,11 @@
         <v>1294</v>
       </c>
       <c r="F472" s="5" t="s">
-        <v>2189</v>
+        <v>2190</v>
       </c>
       <c r="G472" s="7"/>
       <c r="H472" s="5" t="s">
-        <v>2190</v>
+        <v>2191</v>
       </c>
       <c r="I472" s="5" t="s">
         <v>1287</v>
@@ -24195,11 +24228,11 @@
         <v>1299</v>
       </c>
       <c r="F473" s="5" t="s">
-        <v>2191</v>
+        <v>2192</v>
       </c>
       <c r="G473" s="7"/>
       <c r="H473" s="5" t="s">
-        <v>2192</v>
+        <v>2193</v>
       </c>
       <c r="I473" s="5" t="s">
         <v>1287</v>
@@ -24226,14 +24259,14 @@
         <v>736</v>
       </c>
       <c r="F474" s="5" t="s">
-        <v>2193</v>
+        <v>2194</v>
       </c>
       <c r="G474" s="7"/>
       <c r="H474" s="5" t="s">
-        <v>2194</v>
+        <v>2195</v>
       </c>
       <c r="I474" s="5" t="s">
-        <v>2195</v>
+        <v>2196</v>
       </c>
       <c r="J474" s="5" t="s">
         <v>619</v>
@@ -24251,26 +24284,26 @@
         <v>12</v>
       </c>
       <c r="D475" s="5" t="s">
-        <v>1826</v>
+        <v>1827</v>
       </c>
       <c r="E475" s="5" t="s">
-        <v>1827</v>
+        <v>1828</v>
       </c>
       <c r="F475" s="5" t="s">
-        <v>2196</v>
+        <v>2197</v>
       </c>
       <c r="G475" s="7"/>
       <c r="H475" s="5" t="s">
-        <v>2197</v>
+        <v>2198</v>
       </c>
       <c r="I475" s="5" t="s">
-        <v>2198</v>
+        <v>2199</v>
       </c>
       <c r="J475" s="5" t="s">
-        <v>2199</v>
+        <v>2200</v>
       </c>
       <c r="K475" s="8" t="s">
-        <v>2200</v>
+        <v>2201</v>
       </c>
     </row>
     <row r="476" spans="1:11" x14ac:dyDescent="0.2">
@@ -24284,26 +24317,26 @@
         <v>12</v>
       </c>
       <c r="D476" s="5" t="s">
-        <v>1826</v>
+        <v>1827</v>
       </c>
       <c r="E476" s="5" t="s">
-        <v>1827</v>
+        <v>1828</v>
       </c>
       <c r="F476" s="5" t="s">
-        <v>2201</v>
+        <v>2202</v>
       </c>
       <c r="G476" s="7"/>
       <c r="H476" s="5" t="s">
-        <v>2202</v>
+        <v>2203</v>
       </c>
       <c r="I476" s="5" t="s">
-        <v>2203</v>
+        <v>2204</v>
       </c>
       <c r="J476" s="5" t="s">
-        <v>2204</v>
+        <v>2205</v>
       </c>
       <c r="K476" s="8" t="s">
-        <v>2205</v>
+        <v>2206</v>
       </c>
     </row>
     <row r="477" spans="1:11" x14ac:dyDescent="0.2">
@@ -24317,26 +24350,26 @@
         <v>588</v>
       </c>
       <c r="D477" s="5" t="s">
-        <v>2206</v>
+        <v>2207</v>
       </c>
       <c r="E477" s="5" t="s">
-        <v>2207</v>
+        <v>2208</v>
       </c>
       <c r="F477" s="5" t="s">
-        <v>2208</v>
+        <v>2209</v>
       </c>
       <c r="G477" s="7"/>
       <c r="H477" s="5" t="s">
-        <v>2209</v>
+        <v>2210</v>
       </c>
       <c r="I477" s="5" t="s">
-        <v>2210</v>
+        <v>2211</v>
       </c>
       <c r="J477" s="5" t="s">
-        <v>2211</v>
+        <v>2212</v>
       </c>
       <c r="K477" s="8" t="s">
-        <v>2212</v>
+        <v>2213</v>
       </c>
     </row>
     <row r="478" spans="1:11" x14ac:dyDescent="0.2">
@@ -24350,20 +24383,20 @@
         <v>1472</v>
       </c>
       <c r="D478" s="5" t="s">
-        <v>2213</v>
+        <v>2214</v>
       </c>
       <c r="E478" s="5" t="s">
-        <v>2214</v>
+        <v>2215</v>
       </c>
       <c r="F478" s="5" t="s">
-        <v>2215</v>
+        <v>2216</v>
       </c>
       <c r="G478" s="7"/>
       <c r="H478" s="5" t="s">
-        <v>2216</v>
+        <v>2217</v>
       </c>
       <c r="I478" s="5" t="s">
-        <v>2217</v>
+        <v>2218</v>
       </c>
       <c r="J478" s="5" t="s">
         <v>1587</v>
@@ -24387,7 +24420,7 @@
         <v>1307</v>
       </c>
       <c r="F479" s="5" t="s">
-        <v>2218</v>
+        <v>2219</v>
       </c>
       <c r="G479" s="7"/>
       <c r="H479" s="5" t="s">
@@ -24398,7 +24431,7 @@
         <v>1005</v>
       </c>
       <c r="K479" s="8" t="s">
-        <v>2219</v>
+        <v>2220</v>
       </c>
     </row>
     <row r="480" spans="1:11" x14ac:dyDescent="0.2">
@@ -24418,20 +24451,20 @@
         <v>767</v>
       </c>
       <c r="F480" s="5" t="s">
-        <v>2220</v>
+        <v>2221</v>
       </c>
       <c r="G480" s="7"/>
       <c r="H480" s="5" t="s">
-        <v>2221</v>
+        <v>2222</v>
       </c>
       <c r="I480" s="5" t="s">
-        <v>2222</v>
+        <v>2223</v>
       </c>
       <c r="J480" s="5" t="s">
-        <v>2223</v>
+        <v>2224</v>
       </c>
       <c r="K480" s="8" t="s">
-        <v>2224</v>
+        <v>2225</v>
       </c>
     </row>
     <row r="481" spans="1:11" x14ac:dyDescent="0.2">
@@ -24451,20 +24484,20 @@
         <v>774</v>
       </c>
       <c r="F481" s="5" t="s">
-        <v>2225</v>
+        <v>2226</v>
       </c>
       <c r="G481" s="7"/>
       <c r="H481" s="5" t="s">
         <v>777</v>
       </c>
       <c r="I481" s="5" t="s">
-        <v>2226</v>
+        <v>2227</v>
       </c>
       <c r="J481" s="5" t="s">
-        <v>2223</v>
+        <v>2224</v>
       </c>
       <c r="K481" s="8" t="s">
-        <v>2227</v>
+        <v>2228</v>
       </c>
     </row>
     <row r="482" spans="1:11" x14ac:dyDescent="0.2">
@@ -24484,14 +24517,14 @@
         <v>1307</v>
       </c>
       <c r="F482" s="5" t="s">
-        <v>2228</v>
+        <v>2229</v>
       </c>
       <c r="G482" s="7"/>
       <c r="H482" s="5" t="s">
         <v>1449</v>
       </c>
       <c r="I482" s="5" t="s">
-        <v>2229</v>
+        <v>2230</v>
       </c>
       <c r="J482" s="5" t="s">
         <v>851</v>
@@ -24509,26 +24542,26 @@
         <v>1472</v>
       </c>
       <c r="D483" s="5" t="s">
-        <v>2230</v>
+        <v>2231</v>
       </c>
       <c r="E483" s="5" t="s">
-        <v>2231</v>
+        <v>2232</v>
       </c>
       <c r="F483" s="5" t="s">
-        <v>2232</v>
+        <v>2233</v>
       </c>
       <c r="G483" s="7"/>
       <c r="H483" s="5" t="s">
-        <v>2233</v>
+        <v>2234</v>
       </c>
       <c r="I483" s="5" t="s">
-        <v>2234</v>
+        <v>2235</v>
       </c>
       <c r="J483" s="5" t="s">
         <v>1524</v>
       </c>
       <c r="K483" s="8" t="s">
-        <v>2235</v>
+        <v>2236</v>
       </c>
     </row>
     <row r="484" spans="1:11" x14ac:dyDescent="0.2">
@@ -24542,26 +24575,26 @@
         <v>1472</v>
       </c>
       <c r="D484" s="5" t="s">
-        <v>2236</v>
+        <v>2237</v>
       </c>
       <c r="E484" s="5" t="s">
-        <v>2237</v>
+        <v>2238</v>
       </c>
       <c r="F484" s="5" t="s">
-        <v>2238</v>
+        <v>2239</v>
       </c>
       <c r="G484" s="7"/>
       <c r="H484" s="5" t="s">
-        <v>2239</v>
+        <v>2240</v>
       </c>
       <c r="I484" s="5" t="s">
-        <v>2240</v>
+        <v>2241</v>
       </c>
       <c r="J484" s="5" t="s">
         <v>1524</v>
       </c>
       <c r="K484" s="8" t="s">
-        <v>2241</v>
+        <v>2242</v>
       </c>
     </row>
     <row r="485" spans="1:11" x14ac:dyDescent="0.2">
@@ -24575,20 +24608,20 @@
         <v>1472</v>
       </c>
       <c r="D485" s="5" t="s">
-        <v>1929</v>
+        <v>1930</v>
       </c>
       <c r="E485" s="5" t="s">
-        <v>1930</v>
+        <v>1931</v>
       </c>
       <c r="F485" s="5" t="s">
-        <v>2242</v>
+        <v>2243</v>
       </c>
       <c r="G485" s="7"/>
       <c r="H485" s="5" t="s">
-        <v>2243</v>
+        <v>2244</v>
       </c>
       <c r="I485" s="5" t="s">
-        <v>2244</v>
+        <v>2245</v>
       </c>
       <c r="J485" s="5" t="s">
         <v>1669</v>
@@ -24606,20 +24639,20 @@
         <v>1472</v>
       </c>
       <c r="D486" s="5" t="s">
-        <v>1902</v>
+        <v>1903</v>
       </c>
       <c r="E486" s="5" t="s">
-        <v>1903</v>
+        <v>1904</v>
       </c>
       <c r="F486" s="5" t="s">
-        <v>2245</v>
+        <v>2246</v>
       </c>
       <c r="G486" s="7"/>
       <c r="H486" s="5" t="s">
-        <v>2246</v>
+        <v>2247</v>
       </c>
       <c r="I486" s="5" t="s">
-        <v>2247</v>
+        <v>2248</v>
       </c>
       <c r="J486" s="5" t="s">
         <v>619</v>
@@ -24643,11 +24676,11 @@
         <v>1554</v>
       </c>
       <c r="F487" s="5" t="s">
-        <v>2248</v>
+        <v>2249</v>
       </c>
       <c r="G487" s="7"/>
       <c r="H487" s="5" t="s">
-        <v>2249</v>
+        <v>2250</v>
       </c>
       <c r="I487" s="7"/>
       <c r="J487" s="5" t="s">
@@ -24672,14 +24705,14 @@
         <v>657</v>
       </c>
       <c r="F488" s="5" t="s">
-        <v>2250</v>
+        <v>2251</v>
       </c>
       <c r="G488" s="7"/>
       <c r="H488" s="5" t="s">
-        <v>2251</v>
+        <v>2252</v>
       </c>
       <c r="I488" s="5" t="s">
-        <v>2252</v>
+        <v>2253</v>
       </c>
       <c r="J488" s="5" t="s">
         <v>619</v>
@@ -24703,20 +24736,20 @@
         <v>1648</v>
       </c>
       <c r="F489" s="5" t="s">
-        <v>2253</v>
+        <v>2254</v>
       </c>
       <c r="G489" s="7"/>
       <c r="H489" s="5" t="s">
-        <v>2254</v>
+        <v>2255</v>
       </c>
       <c r="I489" s="5" t="s">
-        <v>2255</v>
+        <v>2256</v>
       </c>
       <c r="J489" s="5" t="s">
         <v>1524</v>
       </c>
       <c r="K489" s="8" t="s">
-        <v>2256</v>
+        <v>2257</v>
       </c>
     </row>
     <row r="490" spans="1:11" x14ac:dyDescent="0.2">
@@ -24730,26 +24763,26 @@
         <v>1472</v>
       </c>
       <c r="D490" s="5" t="s">
-        <v>2142</v>
+        <v>2143</v>
       </c>
       <c r="E490" s="5" t="s">
-        <v>2143</v>
+        <v>2144</v>
       </c>
       <c r="F490" s="5" t="s">
-        <v>2257</v>
+        <v>2258</v>
       </c>
       <c r="G490" s="7"/>
       <c r="H490" s="5" t="s">
-        <v>2258</v>
+        <v>2259</v>
       </c>
       <c r="I490" s="5" t="s">
-        <v>2259</v>
+        <v>2260</v>
       </c>
       <c r="J490" s="5" t="s">
-        <v>2165</v>
+        <v>2166</v>
       </c>
       <c r="K490" s="8" t="s">
-        <v>2260</v>
+        <v>2261</v>
       </c>
     </row>
     <row r="491" spans="1:11" x14ac:dyDescent="0.2">
@@ -24763,24 +24796,24 @@
         <v>1006</v>
       </c>
       <c r="D491" s="5" t="s">
-        <v>2261</v>
+        <v>2262</v>
       </c>
       <c r="E491" s="5" t="s">
-        <v>2262</v>
+        <v>2263</v>
       </c>
       <c r="F491" s="5" t="s">
-        <v>2263</v>
+        <v>2264</v>
       </c>
       <c r="G491" s="7"/>
       <c r="H491" s="5" t="s">
-        <v>2264</v>
+        <v>2265</v>
       </c>
       <c r="I491" s="7"/>
       <c r="J491" s="5" t="s">
         <v>1013</v>
       </c>
       <c r="K491" s="8" t="s">
-        <v>2265</v>
+        <v>2266</v>
       </c>
     </row>
     <row r="492" spans="1:11" x14ac:dyDescent="0.2">
@@ -24800,14 +24833,14 @@
         <v>14</v>
       </c>
       <c r="F492" s="5" t="s">
-        <v>2266</v>
+        <v>2267</v>
       </c>
       <c r="G492" s="7"/>
       <c r="H492" s="5" t="s">
-        <v>2267</v>
+        <v>2268</v>
       </c>
       <c r="I492" s="5" t="s">
-        <v>2268</v>
+        <v>2269</v>
       </c>
       <c r="J492" s="5" t="s">
         <v>34</v>
@@ -24825,26 +24858,26 @@
         <v>588</v>
       </c>
       <c r="D493" s="5" t="s">
-        <v>2269</v>
+        <v>2270</v>
       </c>
       <c r="E493" s="5" t="s">
-        <v>2270</v>
+        <v>2271</v>
       </c>
       <c r="F493" s="5" t="s">
-        <v>2271</v>
+        <v>2272</v>
       </c>
       <c r="G493" s="7"/>
       <c r="H493" s="5" t="s">
-        <v>2272</v>
+        <v>2273</v>
       </c>
       <c r="I493" s="5" t="s">
-        <v>2273</v>
+        <v>2274</v>
       </c>
       <c r="J493" s="5" t="s">
         <v>641</v>
       </c>
       <c r="K493" s="8" t="s">
-        <v>2274</v>
+        <v>2275</v>
       </c>
     </row>
     <row r="494" spans="1:11" x14ac:dyDescent="0.2">
@@ -24858,23 +24891,23 @@
         <v>277</v>
       </c>
       <c r="D494" s="5" t="s">
-        <v>2275</v>
+        <v>2276</v>
       </c>
       <c r="E494" s="5" t="s">
-        <v>2276</v>
+        <v>2277</v>
       </c>
       <c r="F494" s="5" t="s">
-        <v>2277</v>
+        <v>2278</v>
       </c>
       <c r="G494" s="7"/>
       <c r="H494" s="5" t="s">
-        <v>2278</v>
+        <v>2279</v>
       </c>
       <c r="I494" s="5" t="s">
-        <v>2279</v>
+        <v>2280</v>
       </c>
       <c r="J494" s="5" t="s">
-        <v>2280</v>
+        <v>2281</v>
       </c>
       <c r="K494" s="6"/>
     </row>
@@ -24889,23 +24922,23 @@
         <v>277</v>
       </c>
       <c r="D495" s="5" t="s">
-        <v>2281</v>
+        <v>2282</v>
       </c>
       <c r="E495" s="5" t="s">
-        <v>2282</v>
+        <v>2283</v>
       </c>
       <c r="F495" s="5" t="s">
-        <v>2283</v>
+        <v>2284</v>
       </c>
       <c r="G495" s="7"/>
       <c r="H495" s="5" t="s">
-        <v>2284</v>
+        <v>2285</v>
       </c>
       <c r="I495" s="5" t="s">
-        <v>2285</v>
+        <v>2286</v>
       </c>
       <c r="J495" s="5" t="s">
-        <v>2280</v>
+        <v>2281</v>
       </c>
       <c r="K495" s="6"/>
     </row>
@@ -24920,23 +24953,23 @@
         <v>277</v>
       </c>
       <c r="D496" s="5" t="s">
-        <v>2286</v>
+        <v>2287</v>
       </c>
       <c r="E496" s="5" t="s">
-        <v>2287</v>
+        <v>2288</v>
       </c>
       <c r="F496" s="5" t="s">
-        <v>2288</v>
+        <v>2289</v>
       </c>
       <c r="G496" s="7"/>
       <c r="H496" s="5" t="s">
-        <v>2289</v>
+        <v>2290</v>
       </c>
       <c r="I496" s="5" t="s">
-        <v>2290</v>
+        <v>2291</v>
       </c>
       <c r="J496" s="5" t="s">
-        <v>2280</v>
+        <v>2281</v>
       </c>
       <c r="K496" s="6"/>
     </row>
@@ -24951,23 +24984,23 @@
         <v>277</v>
       </c>
       <c r="D497" s="5" t="s">
-        <v>2291</v>
+        <v>2292</v>
       </c>
       <c r="E497" s="5" t="s">
-        <v>2292</v>
+        <v>2293</v>
       </c>
       <c r="F497" s="5" t="s">
-        <v>2293</v>
+        <v>2294</v>
       </c>
       <c r="G497" s="7"/>
       <c r="H497" s="5" t="s">
-        <v>2294</v>
+        <v>2295</v>
       </c>
       <c r="I497" s="5" t="s">
-        <v>2295</v>
+        <v>2296</v>
       </c>
       <c r="J497" s="5" t="s">
-        <v>2280</v>
+        <v>2281</v>
       </c>
       <c r="K497" s="6"/>
     </row>
@@ -24982,23 +25015,23 @@
         <v>277</v>
       </c>
       <c r="D498" s="5" t="s">
-        <v>2296</v>
+        <v>2297</v>
       </c>
       <c r="E498" s="5" t="s">
-        <v>2297</v>
+        <v>2298</v>
       </c>
       <c r="F498" s="5" t="s">
-        <v>2298</v>
+        <v>2299</v>
       </c>
       <c r="G498" s="7"/>
       <c r="H498" s="5" t="s">
-        <v>2299</v>
+        <v>2300</v>
       </c>
       <c r="I498" s="5" t="s">
-        <v>2300</v>
+        <v>2301</v>
       </c>
       <c r="J498" s="5" t="s">
-        <v>2280</v>
+        <v>2281</v>
       </c>
       <c r="K498" s="6"/>
     </row>
@@ -25013,23 +25046,23 @@
         <v>277</v>
       </c>
       <c r="D499" s="5" t="s">
-        <v>2301</v>
+        <v>2302</v>
       </c>
       <c r="E499" s="5" t="s">
-        <v>2302</v>
+        <v>2303</v>
       </c>
       <c r="F499" s="5" t="s">
-        <v>2303</v>
+        <v>2304</v>
       </c>
       <c r="G499" s="7"/>
       <c r="H499" s="5" t="s">
-        <v>2304</v>
+        <v>2305</v>
       </c>
       <c r="I499" s="5" t="s">
-        <v>2305</v>
+        <v>2306</v>
       </c>
       <c r="J499" s="5" t="s">
-        <v>2280</v>
+        <v>2281</v>
       </c>
       <c r="K499" s="6"/>
     </row>
@@ -25044,23 +25077,23 @@
         <v>277</v>
       </c>
       <c r="D500" s="5" t="s">
-        <v>2306</v>
+        <v>2307</v>
       </c>
       <c r="E500" s="5" t="s">
-        <v>2307</v>
+        <v>2308</v>
       </c>
       <c r="F500" s="5" t="s">
-        <v>2308</v>
+        <v>2309</v>
       </c>
       <c r="G500" s="7"/>
       <c r="H500" s="5" t="s">
-        <v>2309</v>
+        <v>2310</v>
       </c>
       <c r="I500" s="5" t="s">
-        <v>2310</v>
+        <v>2311</v>
       </c>
       <c r="J500" s="5" t="s">
-        <v>2280</v>
+        <v>2281</v>
       </c>
       <c r="K500" s="6"/>
     </row>
@@ -25075,23 +25108,23 @@
         <v>277</v>
       </c>
       <c r="D501" s="5" t="s">
-        <v>2311</v>
+        <v>2312</v>
       </c>
       <c r="E501" s="5" t="s">
-        <v>2312</v>
+        <v>2313</v>
       </c>
       <c r="F501" s="5" t="s">
-        <v>2313</v>
+        <v>2314</v>
       </c>
       <c r="G501" s="7"/>
       <c r="H501" s="5" t="s">
-        <v>2314</v>
+        <v>2315</v>
       </c>
       <c r="I501" s="5" t="s">
-        <v>2315</v>
+        <v>2316</v>
       </c>
       <c r="J501" s="5" t="s">
-        <v>2280</v>
+        <v>2281</v>
       </c>
       <c r="K501" s="6"/>
     </row>
@@ -25106,26 +25139,26 @@
         <v>588</v>
       </c>
       <c r="D502" s="5" t="s">
-        <v>2010</v>
+        <v>2011</v>
       </c>
       <c r="E502" s="5" t="s">
-        <v>2011</v>
+        <v>2012</v>
       </c>
       <c r="F502" s="5" t="s">
-        <v>2316</v>
+        <v>2317</v>
       </c>
       <c r="G502" s="7"/>
       <c r="H502" s="5" t="s">
-        <v>2317</v>
+        <v>2318</v>
       </c>
       <c r="I502" s="5" t="s">
-        <v>2318</v>
+        <v>2319</v>
       </c>
       <c r="J502" s="5" t="s">
         <v>619</v>
       </c>
       <c r="K502" s="8" t="s">
-        <v>2319</v>
+        <v>2320</v>
       </c>
     </row>
     <row r="503" spans="1:11" x14ac:dyDescent="0.2">
@@ -25145,20 +25178,20 @@
         <v>1498</v>
       </c>
       <c r="F503" s="5" t="s">
-        <v>2320</v>
+        <v>2321</v>
       </c>
       <c r="G503" s="7"/>
       <c r="H503" s="5" t="s">
-        <v>2321</v>
+        <v>2322</v>
       </c>
       <c r="I503" s="5" t="s">
-        <v>2322</v>
+        <v>2323</v>
       </c>
       <c r="J503" s="5" t="s">
         <v>1524</v>
       </c>
       <c r="K503" s="8" t="s">
-        <v>2323</v>
+        <v>2324</v>
       </c>
     </row>
     <row r="504" spans="1:11" x14ac:dyDescent="0.2">
@@ -25172,26 +25205,26 @@
         <v>588</v>
       </c>
       <c r="D504" s="5" t="s">
-        <v>2010</v>
+        <v>2011</v>
       </c>
       <c r="E504" s="5" t="s">
-        <v>2011</v>
+        <v>2012</v>
       </c>
       <c r="F504" s="5" t="s">
-        <v>2324</v>
+        <v>2325</v>
       </c>
       <c r="G504" s="7"/>
       <c r="H504" s="5" t="s">
-        <v>2013</v>
+        <v>2014</v>
       </c>
       <c r="I504" s="5" t="s">
-        <v>2325</v>
+        <v>2326</v>
       </c>
       <c r="J504" s="5" t="s">
         <v>619</v>
       </c>
       <c r="K504" s="8" t="s">
-        <v>2326</v>
+        <v>2327</v>
       </c>
     </row>
     <row r="505" spans="1:11" x14ac:dyDescent="0.2">
@@ -25205,26 +25238,26 @@
         <v>765</v>
       </c>
       <c r="D505" s="5" t="s">
-        <v>2327</v>
+        <v>2328</v>
       </c>
       <c r="E505" s="5" t="s">
-        <v>2328</v>
+        <v>2329</v>
       </c>
       <c r="F505" s="5" t="s">
-        <v>2329</v>
+        <v>2330</v>
       </c>
       <c r="G505" s="7"/>
       <c r="H505" s="5" t="s">
-        <v>2330</v>
+        <v>2331</v>
       </c>
       <c r="I505" s="5" t="s">
-        <v>2331</v>
+        <v>2332</v>
       </c>
       <c r="J505" s="5" t="s">
         <v>772</v>
       </c>
       <c r="K505" s="8" t="s">
-        <v>2332</v>
+        <v>2333</v>
       </c>
     </row>
     <row r="506" spans="1:11" x14ac:dyDescent="0.2">
@@ -25244,20 +25277,20 @@
         <v>1737</v>
       </c>
       <c r="F506" s="5" t="s">
-        <v>2333</v>
+        <v>2334</v>
       </c>
       <c r="G506" s="7"/>
       <c r="H506" s="5" t="s">
-        <v>2334</v>
+        <v>2335</v>
       </c>
       <c r="I506" s="5" t="s">
-        <v>2335</v>
+        <v>2336</v>
       </c>
       <c r="J506" s="5" t="s">
         <v>1524</v>
       </c>
       <c r="K506" s="8" t="s">
-        <v>2336</v>
+        <v>2337</v>
       </c>
     </row>
     <row r="507" spans="1:11" x14ac:dyDescent="0.2">
@@ -25277,18 +25310,18 @@
         <v>1779</v>
       </c>
       <c r="F507" s="5" t="s">
-        <v>2337</v>
+        <v>2338</v>
       </c>
       <c r="G507" s="7"/>
       <c r="H507" s="5" t="s">
-        <v>2338</v>
+        <v>2339</v>
       </c>
       <c r="I507" s="7"/>
       <c r="J507" s="5" t="s">
         <v>1524</v>
       </c>
       <c r="K507" s="8" t="s">
-        <v>2339</v>
+        <v>2340</v>
       </c>
     </row>
     <row r="508" spans="1:11" x14ac:dyDescent="0.2">
@@ -25302,26 +25335,26 @@
         <v>1472</v>
       </c>
       <c r="D508" s="5" t="s">
-        <v>2095</v>
+        <v>2096</v>
       </c>
       <c r="E508" s="5" t="s">
-        <v>2096</v>
+        <v>2097</v>
       </c>
       <c r="F508" s="5" t="s">
-        <v>2340</v>
+        <v>2341</v>
       </c>
       <c r="G508" s="7"/>
       <c r="H508" s="5" t="s">
-        <v>2341</v>
+        <v>2342</v>
       </c>
       <c r="I508" s="5" t="s">
-        <v>2342</v>
+        <v>2343</v>
       </c>
       <c r="J508" s="5" t="s">
         <v>1524</v>
       </c>
       <c r="K508" s="8" t="s">
-        <v>2343</v>
+        <v>2344</v>
       </c>
     </row>
     <row r="509" spans="1:11" x14ac:dyDescent="0.2">
@@ -25341,14 +25374,14 @@
         <v>1498</v>
       </c>
       <c r="F509" s="5" t="s">
-        <v>2344</v>
+        <v>2345</v>
       </c>
       <c r="G509" s="7"/>
       <c r="H509" s="5" t="s">
-        <v>2345</v>
+        <v>2346</v>
       </c>
       <c r="I509" s="5" t="s">
-        <v>2346</v>
+        <v>2347</v>
       </c>
       <c r="J509" s="5" t="s">
         <v>1524</v>
@@ -25366,26 +25399,26 @@
         <v>1472</v>
       </c>
       <c r="D510" s="5" t="s">
-        <v>2347</v>
+        <v>2348</v>
       </c>
       <c r="E510" s="5" t="s">
-        <v>2348</v>
+        <v>2349</v>
       </c>
       <c r="F510" s="5" t="s">
-        <v>2349</v>
+        <v>2350</v>
       </c>
       <c r="G510" s="7"/>
       <c r="H510" s="5" t="s">
-        <v>2350</v>
+        <v>2351</v>
       </c>
       <c r="I510" s="5" t="s">
-        <v>2351</v>
+        <v>2352</v>
       </c>
       <c r="J510" s="5" t="s">
         <v>1524</v>
       </c>
       <c r="K510" s="8" t="s">
-        <v>2352</v>
+        <v>2353</v>
       </c>
     </row>
     <row r="511" spans="1:11" x14ac:dyDescent="0.2">
@@ -25399,26 +25432,26 @@
         <v>1472</v>
       </c>
       <c r="D511" s="5" t="s">
-        <v>2353</v>
+        <v>2354</v>
       </c>
       <c r="E511" s="5" t="s">
-        <v>2354</v>
+        <v>2355</v>
       </c>
       <c r="F511" s="5" t="s">
-        <v>2355</v>
+        <v>2356</v>
       </c>
       <c r="G511" s="7"/>
       <c r="H511" s="5" t="s">
-        <v>2356</v>
+        <v>2357</v>
       </c>
       <c r="I511" s="5" t="s">
-        <v>2357</v>
+        <v>2358</v>
       </c>
       <c r="J511" s="5" t="s">
         <v>1669</v>
       </c>
       <c r="K511" s="8" t="s">
-        <v>2358</v>
+        <v>2359</v>
       </c>
     </row>
     <row r="512" spans="1:11" x14ac:dyDescent="0.2">
@@ -25438,14 +25471,14 @@
         <v>46</v>
       </c>
       <c r="F512" s="5" t="s">
-        <v>2359</v>
+        <v>2360</v>
       </c>
       <c r="G512" s="7"/>
       <c r="H512" s="5" t="s">
-        <v>2360</v>
+        <v>2361</v>
       </c>
       <c r="I512" s="5" t="s">
-        <v>2361</v>
+        <v>2362</v>
       </c>
       <c r="J512" s="5" t="s">
         <v>485</v>
@@ -25463,26 +25496,26 @@
         <v>1472</v>
       </c>
       <c r="D513" s="5" t="s">
-        <v>2362</v>
+        <v>2363</v>
       </c>
       <c r="E513" s="5" t="s">
-        <v>2363</v>
+        <v>2364</v>
       </c>
       <c r="F513" s="5" t="s">
-        <v>2364</v>
+        <v>2365</v>
       </c>
       <c r="G513" s="7"/>
       <c r="H513" s="5" t="s">
-        <v>2365</v>
+        <v>2366</v>
       </c>
       <c r="I513" s="5" t="s">
-        <v>2365</v>
+        <v>2366</v>
       </c>
       <c r="J513" s="5" t="s">
-        <v>2366</v>
+        <v>2367</v>
       </c>
       <c r="K513" s="8" t="s">
-        <v>2367</v>
+        <v>2368</v>
       </c>
     </row>
     <row r="514" spans="1:11" x14ac:dyDescent="0.2">
@@ -25496,26 +25529,26 @@
         <v>67</v>
       </c>
       <c r="D514" s="5" t="s">
-        <v>2368</v>
+        <v>2369</v>
       </c>
       <c r="E514" s="5" t="s">
-        <v>2369</v>
+        <v>2370</v>
       </c>
       <c r="F514" s="5" t="s">
-        <v>2370</v>
+        <v>2371</v>
       </c>
       <c r="G514" s="7"/>
       <c r="H514" s="5" t="s">
-        <v>2371</v>
+        <v>2372</v>
       </c>
       <c r="I514" s="5" t="s">
-        <v>2372</v>
+        <v>2373</v>
       </c>
       <c r="J514" s="5" t="s">
         <v>223</v>
       </c>
       <c r="K514" s="8" t="s">
-        <v>2373</v>
+        <v>2374</v>
       </c>
     </row>
     <row r="515" spans="1:11" x14ac:dyDescent="0.2">
@@ -25529,26 +25562,26 @@
         <v>67</v>
       </c>
       <c r="D515" s="5" t="s">
-        <v>2374</v>
+        <v>2375</v>
       </c>
       <c r="E515" s="5" t="s">
-        <v>2375</v>
+        <v>2376</v>
       </c>
       <c r="F515" s="5" t="s">
-        <v>2376</v>
+        <v>2377</v>
       </c>
       <c r="G515" s="7"/>
       <c r="H515" s="5" t="s">
-        <v>2377</v>
+        <v>2378</v>
       </c>
       <c r="I515" s="5" t="s">
-        <v>2378</v>
+        <v>2379</v>
       </c>
       <c r="J515" s="5" t="s">
         <v>223</v>
       </c>
       <c r="K515" s="8" t="s">
-        <v>2379</v>
+        <v>2380</v>
       </c>
     </row>
     <row r="516" spans="1:11" x14ac:dyDescent="0.2">
@@ -25568,18 +25601,18 @@
         <v>1637</v>
       </c>
       <c r="F516" s="5" t="s">
-        <v>2380</v>
+        <v>2381</v>
       </c>
       <c r="G516" s="7"/>
       <c r="H516" s="5" t="s">
-        <v>2381</v>
+        <v>2382</v>
       </c>
       <c r="I516" s="7"/>
       <c r="J516" s="5" t="s">
         <v>1669</v>
       </c>
       <c r="K516" s="8" t="s">
-        <v>2382</v>
+        <v>2383</v>
       </c>
     </row>
     <row r="517" spans="1:11" x14ac:dyDescent="0.2">
@@ -25593,24 +25626,24 @@
         <v>1472</v>
       </c>
       <c r="D517" s="5" t="s">
-        <v>2353</v>
+        <v>2354</v>
       </c>
       <c r="E517" s="5" t="s">
-        <v>2354</v>
+        <v>2355</v>
       </c>
       <c r="F517" s="5" t="s">
-        <v>2383</v>
+        <v>2384</v>
       </c>
       <c r="G517" s="7"/>
       <c r="H517" s="5" t="s">
-        <v>2384</v>
+        <v>2385</v>
       </c>
       <c r="I517" s="7"/>
       <c r="J517" s="5" t="s">
         <v>1669</v>
       </c>
       <c r="K517" s="8" t="s">
-        <v>2219</v>
+        <v>2220</v>
       </c>
     </row>
     <row r="518" spans="1:11" x14ac:dyDescent="0.2">
@@ -25630,20 +25663,20 @@
         <v>1637</v>
       </c>
       <c r="F518" s="5" t="s">
-        <v>2385</v>
+        <v>2386</v>
       </c>
       <c r="G518" s="7"/>
       <c r="H518" s="5" t="s">
-        <v>2386</v>
+        <v>2387</v>
       </c>
       <c r="I518" s="5" t="s">
-        <v>2387</v>
+        <v>2388</v>
       </c>
       <c r="J518" s="5" t="s">
         <v>1524</v>
       </c>
       <c r="K518" s="8" t="s">
-        <v>2388</v>
+        <v>2389</v>
       </c>
     </row>
     <row r="519" spans="1:11" x14ac:dyDescent="0.2">
@@ -25657,26 +25690,26 @@
         <v>1472</v>
       </c>
       <c r="D519" s="5" t="s">
-        <v>2389</v>
+        <v>2390</v>
       </c>
       <c r="E519" s="5" t="s">
-        <v>2390</v>
+        <v>2391</v>
       </c>
       <c r="F519" s="5" t="s">
-        <v>2391</v>
+        <v>2392</v>
       </c>
       <c r="G519" s="7"/>
       <c r="H519" s="5" t="s">
-        <v>2392</v>
+        <v>2393</v>
       </c>
       <c r="I519" s="5" t="s">
-        <v>2393</v>
+        <v>2394</v>
       </c>
       <c r="J519" s="5" t="s">
         <v>1524</v>
       </c>
       <c r="K519" s="8" t="s">
-        <v>2394</v>
+        <v>2395</v>
       </c>
     </row>
     <row r="520" spans="1:11" x14ac:dyDescent="0.2">
@@ -25690,26 +25723,26 @@
         <v>1472</v>
       </c>
       <c r="D520" s="5" t="s">
-        <v>2395</v>
+        <v>2396</v>
       </c>
       <c r="E520" s="5" t="s">
-        <v>2396</v>
+        <v>2397</v>
       </c>
       <c r="F520" s="5" t="s">
-        <v>2397</v>
+        <v>2398</v>
       </c>
       <c r="G520" s="7"/>
       <c r="H520" s="5" t="s">
-        <v>2398</v>
+        <v>2399</v>
       </c>
       <c r="I520" s="5" t="s">
-        <v>2399</v>
+        <v>2400</v>
       </c>
       <c r="J520" s="5" t="s">
         <v>1524</v>
       </c>
       <c r="K520" s="8" t="s">
-        <v>2400</v>
+        <v>2401</v>
       </c>
     </row>
     <row r="521" spans="1:11" x14ac:dyDescent="0.2">
@@ -25723,26 +25756,26 @@
         <v>1472</v>
       </c>
       <c r="D521" s="5" t="s">
-        <v>2104</v>
+        <v>2105</v>
       </c>
       <c r="E521" s="5" t="s">
-        <v>2105</v>
+        <v>2106</v>
       </c>
       <c r="F521" s="5" t="s">
-        <v>2401</v>
+        <v>2402</v>
       </c>
       <c r="G521" s="7"/>
       <c r="H521" s="5" t="s">
-        <v>2402</v>
+        <v>2403</v>
       </c>
       <c r="I521" s="5" t="s">
-        <v>2403</v>
+        <v>2404</v>
       </c>
       <c r="J521" s="5" t="s">
         <v>1524</v>
       </c>
       <c r="K521" s="8" t="s">
-        <v>2404</v>
+        <v>2405</v>
       </c>
     </row>
     <row r="522" spans="1:11" x14ac:dyDescent="0.2">
@@ -25754,24 +25787,24 @@
         <v>1472</v>
       </c>
       <c r="D522" s="5" t="s">
-        <v>2171</v>
+        <v>2172</v>
       </c>
       <c r="E522" s="5" t="s">
-        <v>2172</v>
+        <v>2173</v>
       </c>
       <c r="F522" s="5" t="s">
-        <v>2405</v>
+        <v>2406</v>
       </c>
       <c r="G522" s="7"/>
       <c r="H522" s="5" t="s">
-        <v>2406</v>
+        <v>2407</v>
       </c>
       <c r="I522" s="7"/>
       <c r="J522" s="5" t="s">
         <v>1669</v>
       </c>
       <c r="K522" s="8" t="s">
-        <v>2407</v>
+        <v>2408</v>
       </c>
     </row>
     <row r="523" spans="1:11" x14ac:dyDescent="0.2">
@@ -25789,18 +25822,18 @@
         <v>1637</v>
       </c>
       <c r="F523" s="5" t="s">
-        <v>2408</v>
+        <v>2409</v>
       </c>
       <c r="G523" s="7"/>
       <c r="H523" s="5" t="s">
-        <v>2409</v>
+        <v>2410</v>
       </c>
       <c r="I523" s="7"/>
       <c r="J523" s="5" t="s">
         <v>1669</v>
       </c>
       <c r="K523" s="8" t="s">
-        <v>2410</v>
+        <v>2411</v>
       </c>
     </row>
     <row r="524" spans="1:11" x14ac:dyDescent="0.2">
@@ -25814,26 +25847,26 @@
         <v>1472</v>
       </c>
       <c r="D524" s="5" t="s">
-        <v>2395</v>
+        <v>2396</v>
       </c>
       <c r="E524" s="5" t="s">
-        <v>2396</v>
+        <v>2397</v>
       </c>
       <c r="F524" s="5" t="s">
-        <v>2411</v>
+        <v>2412</v>
       </c>
       <c r="G524" s="7"/>
       <c r="H524" s="5" t="s">
-        <v>2412</v>
+        <v>2413</v>
       </c>
       <c r="I524" s="5" t="s">
-        <v>2399</v>
+        <v>2400</v>
       </c>
       <c r="J524" s="5" t="s">
         <v>1524</v>
       </c>
       <c r="K524" s="8" t="s">
-        <v>2413</v>
+        <v>2414</v>
       </c>
     </row>
     <row r="525" spans="1:11" x14ac:dyDescent="0.2">
@@ -25853,20 +25886,20 @@
         <v>1554</v>
       </c>
       <c r="F525" s="5" t="s">
-        <v>2414</v>
+        <v>2415</v>
       </c>
       <c r="G525" s="7"/>
       <c r="H525" s="5" t="s">
-        <v>2415</v>
+        <v>2416</v>
       </c>
       <c r="I525" s="5" t="s">
-        <v>2416</v>
+        <v>2417</v>
       </c>
       <c r="J525" s="5" t="s">
         <v>1524</v>
       </c>
       <c r="K525" s="8" t="s">
-        <v>2417</v>
+        <v>2418</v>
       </c>
     </row>
     <row r="526" spans="1:11" x14ac:dyDescent="0.2">
@@ -25880,26 +25913,26 @@
         <v>1472</v>
       </c>
       <c r="D526" s="5" t="s">
-        <v>2418</v>
+        <v>2419</v>
       </c>
       <c r="E526" s="5" t="s">
-        <v>2419</v>
+        <v>2420</v>
       </c>
       <c r="F526" s="5" t="s">
-        <v>2420</v>
+        <v>2421</v>
       </c>
       <c r="G526" s="7"/>
       <c r="H526" s="5" t="s">
-        <v>2421</v>
+        <v>2422</v>
       </c>
       <c r="I526" s="5" t="s">
-        <v>2422</v>
+        <v>2423</v>
       </c>
       <c r="J526" s="5" t="s">
         <v>1786</v>
       </c>
       <c r="K526" s="8" t="s">
-        <v>2423</v>
+        <v>2424</v>
       </c>
     </row>
     <row r="527" spans="1:11" x14ac:dyDescent="0.2">
@@ -25913,24 +25946,24 @@
         <v>588</v>
       </c>
       <c r="D527" s="5" t="s">
-        <v>2424</v>
+        <v>2425</v>
       </c>
       <c r="E527" s="5" t="s">
-        <v>2425</v>
+        <v>2426</v>
       </c>
       <c r="F527" s="5" t="s">
-        <v>2426</v>
+        <v>2427</v>
       </c>
       <c r="G527" s="7"/>
       <c r="H527" s="5" t="s">
-        <v>2427</v>
+        <v>2428</v>
       </c>
       <c r="I527" s="7"/>
       <c r="J527" s="5" t="s">
         <v>619</v>
       </c>
       <c r="K527" s="8" t="s">
-        <v>2428</v>
+        <v>2429</v>
       </c>
     </row>
     <row r="528" spans="1:11" x14ac:dyDescent="0.2">
@@ -25950,20 +25983,20 @@
         <v>1637</v>
       </c>
       <c r="F528" s="5" t="s">
-        <v>2429</v>
+        <v>2430</v>
       </c>
       <c r="G528" s="7"/>
       <c r="H528" s="5" t="s">
-        <v>2430</v>
+        <v>2431</v>
       </c>
       <c r="I528" s="5" t="s">
-        <v>2431</v>
+        <v>2432</v>
       </c>
       <c r="J528" s="5" t="s">
         <v>1669</v>
       </c>
       <c r="K528" s="8" t="s">
-        <v>2432</v>
+        <v>2433</v>
       </c>
     </row>
     <row r="529" spans="1:11" x14ac:dyDescent="0.2">
@@ -25975,60 +26008,119 @@
         <v>67</v>
       </c>
       <c r="D529" s="5" t="s">
-        <v>2433</v>
+        <v>2434</v>
       </c>
       <c r="E529" s="5" t="s">
-        <v>2434</v>
+        <v>2435</v>
       </c>
       <c r="F529" s="5" t="s">
-        <v>2435</v>
+        <v>2436</v>
       </c>
       <c r="G529" s="7"/>
       <c r="H529" s="5" t="s">
-        <v>2436</v>
+        <v>2437</v>
       </c>
       <c r="I529" s="5" t="s">
-        <v>2437</v>
+        <v>2438</v>
       </c>
       <c r="J529" s="5" t="s">
         <v>223</v>
       </c>
       <c r="K529" s="8" t="s">
-        <v>2407</v>
+        <v>2408</v>
       </c>
     </row>
     <row r="530" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A530" s="9">
+      <c r="A530" s="4">
         <v>530</v>
       </c>
-      <c r="B530" s="10" t="s">
-        <v>11</v>
-      </c>
-      <c r="C530" s="10" t="s">
+      <c r="B530" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C530" s="5" t="s">
         <v>277</v>
       </c>
-      <c r="D530" s="10" t="s">
-        <v>2438</v>
-      </c>
-      <c r="E530" s="10" t="s">
+      <c r="D530" s="5" t="s">
         <v>2439</v>
       </c>
-      <c r="F530" s="10" t="s">
+      <c r="E530" s="5" t="s">
         <v>2440</v>
       </c>
-      <c r="G530" s="11"/>
-      <c r="H530" s="10" t="s">
+      <c r="F530" s="5" t="s">
         <v>2441</v>
       </c>
-      <c r="I530" s="10" t="s">
+      <c r="G530" s="7"/>
+      <c r="H530" s="5" t="s">
         <v>2442</v>
       </c>
-      <c r="J530" s="10" t="s">
+      <c r="I530" s="5" t="s">
+        <v>2443</v>
+      </c>
+      <c r="J530" s="5" t="s">
         <v>283</v>
       </c>
-      <c r="K530" s="12"/>
+      <c r="K530" s="6"/>
+    </row>
+    <row r="531" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A531" s="4">
+        <v>531</v>
+      </c>
+      <c r="B531" s="7"/>
+      <c r="C531" s="5" t="s">
+        <v>1472</v>
+      </c>
+      <c r="D531" s="5" t="s">
+        <v>2118</v>
+      </c>
+      <c r="E531" s="5" t="s">
+        <v>2119</v>
+      </c>
+      <c r="F531" s="5" t="s">
+        <v>2444</v>
+      </c>
+      <c r="G531" s="7"/>
+      <c r="H531" s="5" t="s">
+        <v>2445</v>
+      </c>
+      <c r="I531" s="7"/>
+      <c r="J531" s="7"/>
+      <c r="K531" s="8" t="s">
+        <v>2446</v>
+      </c>
+    </row>
+    <row r="532" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A532" s="9">
+        <v>532</v>
+      </c>
+      <c r="B532" s="10"/>
+      <c r="C532" s="11" t="s">
+        <v>12</v>
+      </c>
+      <c r="D532" s="11" t="s">
+        <v>1827</v>
+      </c>
+      <c r="E532" s="11" t="s">
+        <v>1828</v>
+      </c>
+      <c r="F532" s="11" t="s">
+        <v>2447</v>
+      </c>
+      <c r="G532" s="10"/>
+      <c r="H532" s="11" t="s">
+        <v>2448</v>
+      </c>
+      <c r="I532" s="11" t="s">
+        <v>2449</v>
+      </c>
+      <c r="J532" s="11" t="s">
+        <v>2450</v>
+      </c>
+      <c r="K532" s="12" t="s">
+        <v>2451</v>
+      </c>
     </row>
   </sheetData>
+  <sheetProtection algorithmName="SHA-512" hashValue="mHoihxJsEa4VaItwbQ6SgYoVof8uQapwkp3ypMoLN0zjEv3VyTJVqJ9sCusk51ySPmb3ufW/BGPVFra2ZYqC+w==" saltValue="1+fXPmTJnpmvWsK5Fiux/A==" spinCount="100000" sheet="1" objects="1" scenarios="1" sort="0" autoFilter="0"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <tableParts count="1">
     <tablePart r:id="rId1"/>

--- a/RM.xlsx
+++ b/RM.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\MPCI QC\Desktop\FG &amp; RMPM LIST\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{21759D3C-DC17-4F84-9815-5B393A21BFFC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3C9A2609-4361-45D9-A231-0634BFC64B8C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="20490" windowHeight="10920" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -778,10 +778,10 @@
     <t>R440MB</t>
   </si>
   <si>
-    <t>Toyo Matte Pink Colour MTI/RMB-23001</t>
-  </si>
-  <si>
-    <t>PET Color Opaque Pink MTI/RMB-23001</t>
+    <t>Toyo Matte Pink Colour MTI/RBM-23001</t>
+  </si>
+  <si>
+    <t>PET Color Opaque Pink MTI/RBM-23001</t>
   </si>
   <si>
     <t>RM010.2</t>
@@ -8363,20 +8363,20 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{1F039EC9-6C81-44BF-BDD8-BD030429FA22}" name="Table1" displayName="Table1" ref="A1:K532" totalsRowShown="0" headerRowDxfId="0" dataDxfId="15" headerRowBorderDxfId="13" tableBorderDxfId="14" totalsRowBorderDxfId="12">
-  <autoFilter ref="A1:K532" xr:uid="{1F039EC9-6C81-44BF-BDD8-BD030429FA22}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{E3B5AEDA-707A-47AD-8C41-A4475E42D34E}" name="Table1" displayName="Table1" ref="A1:K532" totalsRowShown="0" headerRowDxfId="0" dataDxfId="15" headerRowBorderDxfId="13" tableBorderDxfId="14" totalsRowBorderDxfId="12">
+  <autoFilter ref="A1:K532" xr:uid="{E3B5AEDA-707A-47AD-8C41-A4475E42D34E}"/>
   <tableColumns count="11">
-    <tableColumn id="1" xr3:uid="{43BA8B2C-B61B-49ED-BA93-161E3E1035A8}" name="ID" dataDxfId="11"/>
-    <tableColumn id="2" xr3:uid="{9A3FF523-352E-426D-8D5D-F42138B81F77}" name="Status" dataDxfId="10"/>
-    <tableColumn id="3" xr3:uid="{5BFA5739-57D6-4002-8ACE-AD5C74E58B24}" name="Material List::Material_Detail" dataDxfId="9"/>
-    <tableColumn id="4" xr3:uid="{2ED2B048-9943-499F-BA4F-AEACF77A4585}" name="Product_Code" dataDxfId="8"/>
-    <tableColumn id="5" xr3:uid="{2D1987A0-21E0-4788-A8D1-B539DBE80A15}" name="RM PM Product List 2::Product_Detail" dataDxfId="7"/>
-    <tableColumn id="6" xr3:uid="{66D4A25C-A235-477C-B076-4DBCF1DE4BEE}" name="Item_Code" dataDxfId="6"/>
-    <tableColumn id="7" xr3:uid="{AA9E07D4-BB89-4C4D-95A7-1B2F020E5B6C}" name="Old_Item_Code" dataDxfId="5"/>
-    <tableColumn id="8" xr3:uid="{643E3A94-3A50-4C27-A96C-7D799DA3CEA5}" name="Item_Name" dataDxfId="4"/>
-    <tableColumn id="9" xr3:uid="{AF523473-BCF4-47DF-9B1E-9038856C6061}" name="Item_Detail_by_Vendor" dataDxfId="3"/>
-    <tableColumn id="10" xr3:uid="{FDC3D2FC-88BF-41F0-B6E1-A4CA470807F0}" name="Vendor List 2::Vendor_Name" dataDxfId="2"/>
-    <tableColumn id="11" xr3:uid="{BBD06216-3437-4CB7-B10D-B81BF109BDB1}" name="Remarks" dataDxfId="1"/>
+    <tableColumn id="1" xr3:uid="{C3D128A2-65D5-422D-88E6-95FFBD5EF1CD}" name="ID" dataDxfId="11"/>
+    <tableColumn id="2" xr3:uid="{E98BF5B1-024E-4E6A-8C75-9208A0E7535F}" name="Status" dataDxfId="10"/>
+    <tableColumn id="3" xr3:uid="{EF9BF6C0-FF52-4FFE-A781-8CEB0A1B5ACB}" name="Material List::Material_Detail" dataDxfId="9"/>
+    <tableColumn id="4" xr3:uid="{BDD840C7-E025-4661-AB00-D5AABD5CEA14}" name="Product_Code" dataDxfId="8"/>
+    <tableColumn id="5" xr3:uid="{3D232217-20F8-43C0-849E-832998FD76FC}" name="RM PM Product List 2::Product_Detail" dataDxfId="7"/>
+    <tableColumn id="6" xr3:uid="{8356FBEA-B221-4C7E-BE80-16BE54A43442}" name="Item_Code" dataDxfId="6"/>
+    <tableColumn id="7" xr3:uid="{541DDC80-66AA-451B-A38F-294F5F2FC53E}" name="Old_Item_Code" dataDxfId="5"/>
+    <tableColumn id="8" xr3:uid="{0E5FE7DC-5670-415E-8C22-9940205C9DB5}" name="Item_Name" dataDxfId="4"/>
+    <tableColumn id="9" xr3:uid="{8E9F812C-5325-4A7D-A0D9-FA3A551967FF}" name="Item_Detail_by_Vendor" dataDxfId="3"/>
+    <tableColumn id="10" xr3:uid="{DB805BC5-A8EA-4ECF-B5CD-1C893603790E}" name="Vendor List 2::Vendor_Name" dataDxfId="2"/>
+    <tableColumn id="11" xr3:uid="{1CF9D566-2984-470D-8349-BA7AA7710A66}" name="Remarks" dataDxfId="1"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -26120,7 +26120,7 @@
       </c>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="mHoihxJsEa4VaItwbQ6SgYoVof8uQapwkp3ypMoLN0zjEv3VyTJVqJ9sCusk51ySPmb3ufW/BGPVFra2ZYqC+w==" saltValue="1+fXPmTJnpmvWsK5Fiux/A==" spinCount="100000" sheet="1" objects="1" scenarios="1" sort="0" autoFilter="0"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="1YZ7r2ip7JVa0U/myZNfHTIOEzUWG+1iNA8z6ZxB063A7GigqMS/pyZfGZ9M0+uV4nQvwVEQLrNQS8jXs87atA==" saltValue="8HEEtiL6dTE7tplAWF7QUg==" spinCount="100000" sheet="1" objects="1" scenarios="1" sort="0" autoFilter="0"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <tableParts count="1">
     <tablePart r:id="rId1"/>

--- a/RM.xlsx
+++ b/RM.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\MPCI QC\Desktop\FG &amp; RMPM LIST\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3C9A2609-4361-45D9-A231-0634BFC64B8C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E5CB6B3B-343B-47A4-8018-CAFDD2338A0C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="20490" windowHeight="10920" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4723" uniqueCount="2452">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4741" uniqueCount="2463">
   <si>
     <t>ID</t>
   </si>
@@ -589,7 +589,7 @@
     <t>Toyo Golden Colour 2NA628(PET)</t>
   </si>
   <si>
-    <t>Master Batch 2NA68 PET Gold</t>
+    <t>Master Batch 2NA628 PET Gold</t>
   </si>
   <si>
     <t>RM017</t>
@@ -7364,7 +7364,8 @@
 OD w/o thread: 25.05 mm
 Neck Size(collar): 27.65 mm
 Wall Thickness: 2.10 mm to 3.65 mm
-Used for: MP0360.1
+Used for: 
+MP0360.1, MP0424.1
 Brand Name not available on LIP</t>
   </si>
   <si>
@@ -7835,6 +7836,46 @@
     <t>Billed to: Dabur
 Shipped to: MPCI
 Trial not done yet</t>
+  </si>
+  <si>
+    <t>RM116.3</t>
+  </si>
+  <si>
+    <t>Tape Roll BOPP 48mmx300mtrx42micron (Print) PI</t>
+  </si>
+  <si>
+    <t>BOPP TAPE 48MM 42MIC TPT 300MTR</t>
+  </si>
+  <si>
+    <t>Packro Industries Pvt. Ltd.</t>
+  </si>
+  <si>
+    <t>Quality Issue: Email attached</t>
+  </si>
+  <si>
+    <t>RM267</t>
+  </si>
+  <si>
+    <t>FTC 25mm (3.90mm) Without Plug H=23.70, OD=26.80, W=2.70</t>
+  </si>
+  <si>
+    <t>RM267.1</t>
+  </si>
+  <si>
+    <t>FTC 25mm Milky White Without Plug LP</t>
+  </si>
+  <si>
+    <t>25MM FTC WITHOUT PLUG</t>
+  </si>
+  <si>
+    <t>Vendor: RITU PLASTIC
+(Procured on: 20 March 2026)
+Height: 23.74 mm
+Weight: 2.69 gm
+OD: 26.82 mm
+ID without thread: 25.30 mm
+ID with thread: 23.05 mm
+Depth: 18.70 mm</t>
   </si>
 </sst>
 </file>
@@ -8014,10 +8055,10 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
@@ -8274,6 +8315,8 @@
       </border>
     </dxf>
     <dxf>
+      <numFmt numFmtId="30" formatCode="@"/>
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <border diagonalUp="0" diagonalDown="0">
         <left style="thin">
           <color indexed="64"/>
@@ -8363,20 +8406,20 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{E3B5AEDA-707A-47AD-8C41-A4475E42D34E}" name="Table1" displayName="Table1" ref="A1:K532" totalsRowShown="0" headerRowDxfId="0" dataDxfId="15" headerRowBorderDxfId="13" tableBorderDxfId="14" totalsRowBorderDxfId="12">
-  <autoFilter ref="A1:K532" xr:uid="{E3B5AEDA-707A-47AD-8C41-A4475E42D34E}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{03EE533D-708C-4AEB-9D0D-2E3195DE5812}" name="Table1" displayName="Table1" ref="A1:K534" totalsRowShown="0" headerRowDxfId="0" dataDxfId="15" headerRowBorderDxfId="13" tableBorderDxfId="14" totalsRowBorderDxfId="12">
+  <autoFilter ref="A1:K534" xr:uid="{03EE533D-708C-4AEB-9D0D-2E3195DE5812}"/>
   <tableColumns count="11">
-    <tableColumn id="1" xr3:uid="{C3D128A2-65D5-422D-88E6-95FFBD5EF1CD}" name="ID" dataDxfId="11"/>
-    <tableColumn id="2" xr3:uid="{E98BF5B1-024E-4E6A-8C75-9208A0E7535F}" name="Status" dataDxfId="10"/>
-    <tableColumn id="3" xr3:uid="{EF9BF6C0-FF52-4FFE-A781-8CEB0A1B5ACB}" name="Material List::Material_Detail" dataDxfId="9"/>
-    <tableColumn id="4" xr3:uid="{BDD840C7-E025-4661-AB00-D5AABD5CEA14}" name="Product_Code" dataDxfId="8"/>
-    <tableColumn id="5" xr3:uid="{3D232217-20F8-43C0-849E-832998FD76FC}" name="RM PM Product List 2::Product_Detail" dataDxfId="7"/>
-    <tableColumn id="6" xr3:uid="{8356FBEA-B221-4C7E-BE80-16BE54A43442}" name="Item_Code" dataDxfId="6"/>
-    <tableColumn id="7" xr3:uid="{541DDC80-66AA-451B-A38F-294F5F2FC53E}" name="Old_Item_Code" dataDxfId="5"/>
-    <tableColumn id="8" xr3:uid="{0E5FE7DC-5670-415E-8C22-9940205C9DB5}" name="Item_Name" dataDxfId="4"/>
-    <tableColumn id="9" xr3:uid="{8E9F812C-5325-4A7D-A0D9-FA3A551967FF}" name="Item_Detail_by_Vendor" dataDxfId="3"/>
-    <tableColumn id="10" xr3:uid="{DB805BC5-A8EA-4ECF-B5CD-1C893603790E}" name="Vendor List 2::Vendor_Name" dataDxfId="2"/>
-    <tableColumn id="11" xr3:uid="{1CF9D566-2984-470D-8349-BA7AA7710A66}" name="Remarks" dataDxfId="1"/>
+    <tableColumn id="1" xr3:uid="{8468CDF2-DB87-447F-8CE6-3C981FAE775A}" name="ID" dataDxfId="11"/>
+    <tableColumn id="2" xr3:uid="{865C5089-FB9E-4253-9987-6D732953DB70}" name="Status" dataDxfId="10"/>
+    <tableColumn id="3" xr3:uid="{572F8903-F152-474E-8A8B-9DFD76326929}" name="Material List::Material_Detail" dataDxfId="9"/>
+    <tableColumn id="4" xr3:uid="{0EB650E1-C722-426F-AE64-DD0AC9405178}" name="Product_Code" dataDxfId="8"/>
+    <tableColumn id="5" xr3:uid="{CAD66990-BF5A-4356-91DC-496DF0DB6706}" name="RM PM Product List 2::Product_Detail" dataDxfId="7"/>
+    <tableColumn id="6" xr3:uid="{2BFC3698-BD50-4441-BBC8-68B71ED5FCF5}" name="Item_Code" dataDxfId="6"/>
+    <tableColumn id="7" xr3:uid="{21AE0DEC-9493-4534-BACF-E074CE0AF4AC}" name="Old_Item_Code" dataDxfId="5"/>
+    <tableColumn id="8" xr3:uid="{76ABFD0A-3271-4FAD-9795-A9045A64FD22}" name="Item_Name" dataDxfId="4"/>
+    <tableColumn id="9" xr3:uid="{29DF494E-C337-47C0-9FBF-14FE9B873076}" name="Item_Detail_by_Vendor" dataDxfId="3"/>
+    <tableColumn id="10" xr3:uid="{0E38AF1C-A4B5-4AB2-81CD-C06F23A1A6E9}" name="Vendor List 2::Vendor_Name" dataDxfId="2"/>
+    <tableColumn id="11" xr3:uid="{78CA8D49-1230-4AE9-BB51-0FF1938A1D04}" name="Remarks" dataDxfId="1"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -8679,7 +8722,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:K532"/>
+  <dimension ref="A1:K534"/>
   <sheetFormatPr defaultColWidth="21.7109375" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.140625" bestFit="1" customWidth="1"/>
@@ -26089,38 +26132,104 @@
       </c>
     </row>
     <row r="532" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A532" s="9">
+      <c r="A532" s="4">
         <v>532</v>
       </c>
-      <c r="B532" s="10"/>
-      <c r="C532" s="11" t="s">
+      <c r="B532" s="7"/>
+      <c r="C532" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="D532" s="11" t="s">
+      <c r="D532" s="5" t="s">
         <v>1827</v>
       </c>
-      <c r="E532" s="11" t="s">
+      <c r="E532" s="5" t="s">
         <v>1828</v>
       </c>
-      <c r="F532" s="11" t="s">
+      <c r="F532" s="5" t="s">
         <v>2447</v>
       </c>
-      <c r="G532" s="10"/>
-      <c r="H532" s="11" t="s">
+      <c r="G532" s="7"/>
+      <c r="H532" s="5" t="s">
         <v>2448</v>
       </c>
-      <c r="I532" s="11" t="s">
+      <c r="I532" s="5" t="s">
         <v>2449</v>
       </c>
-      <c r="J532" s="11" t="s">
+      <c r="J532" s="5" t="s">
         <v>2450</v>
       </c>
-      <c r="K532" s="12" t="s">
+      <c r="K532" s="8" t="s">
         <v>2451</v>
       </c>
     </row>
+    <row r="533" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A533" s="4">
+        <v>533</v>
+      </c>
+      <c r="B533" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C533" s="5" t="s">
+        <v>969</v>
+      </c>
+      <c r="D533" s="5" t="s">
+        <v>976</v>
+      </c>
+      <c r="E533" s="5" t="s">
+        <v>977</v>
+      </c>
+      <c r="F533" s="5" t="s">
+        <v>2452</v>
+      </c>
+      <c r="G533" s="7"/>
+      <c r="H533" s="5" t="s">
+        <v>2453</v>
+      </c>
+      <c r="I533" s="5" t="s">
+        <v>2454</v>
+      </c>
+      <c r="J533" s="5" t="s">
+        <v>2455</v>
+      </c>
+      <c r="K533" s="8" t="s">
+        <v>2456</v>
+      </c>
+    </row>
+    <row r="534" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A534" s="9">
+        <v>534</v>
+      </c>
+      <c r="B534" s="10" t="s">
+        <v>11</v>
+      </c>
+      <c r="C534" s="10" t="s">
+        <v>1472</v>
+      </c>
+      <c r="D534" s="10" t="s">
+        <v>2457</v>
+      </c>
+      <c r="E534" s="10" t="s">
+        <v>2458</v>
+      </c>
+      <c r="F534" s="10" t="s">
+        <v>2459</v>
+      </c>
+      <c r="G534" s="11"/>
+      <c r="H534" s="10" t="s">
+        <v>2460</v>
+      </c>
+      <c r="I534" s="10" t="s">
+        <v>2461</v>
+      </c>
+      <c r="J534" s="10" t="s">
+        <v>1524</v>
+      </c>
+      <c r="K534" s="12" t="s">
+        <v>2462</v>
+      </c>
+    </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="1YZ7r2ip7JVa0U/myZNfHTIOEzUWG+1iNA8z6ZxB063A7GigqMS/pyZfGZ9M0+uV4nQvwVEQLrNQS8jXs87atA==" saltValue="8HEEtiL6dTE7tplAWF7QUg==" spinCount="100000" sheet="1" objects="1" scenarios="1" sort="0" autoFilter="0"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="5av31vnnFljIfOAuHPPC6zsrmODCUei6w4Et9paNfN9tBWhnJdn3Rf3fjwwFEZK+0F+NNnRs/amW3rQOhl2E0Q==" saltValue="6NzH6u9itqoL9XbNFr4t2w==" spinCount="100000" sheet="1" objects="1" scenarios="1" sort="0" autoFilter="0"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <tableParts count="1">
     <tablePart r:id="rId1"/>

--- a/RM.xlsx
+++ b/RM.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\MPCI QC\Desktop\FG &amp; RMPM LIST\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E5CB6B3B-343B-47A4-8018-CAFDD2338A0C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{362E5F14-1DA5-4ACB-8AA4-1F6DA58E6273}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="20490" windowHeight="10920" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4741" uniqueCount="2463">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4750" uniqueCount="2467">
   <si>
     <t>ID</t>
   </si>
@@ -6402,7 +6402,7 @@
     <t>Wad 23.75mmX1.0mm Golden 8Layer 25mm PET</t>
   </si>
   <si>
-    <t>2211/063/BC/23.75</t>
+    <t>2211/080/BC/23.75</t>
   </si>
   <si>
     <t>Approved for : Screw 25mm Glass Bottle Cap</t>
@@ -7876,6 +7876,21 @@
 ID without thread: 25.30 mm
 ID with thread: 23.05 mm
 Depth: 18.70 mm</t>
+  </si>
+  <si>
+    <t>RM202.5</t>
+  </si>
+  <si>
+    <t>PET Resin Recycled GB801 - 1150Kgs</t>
+  </si>
+  <si>
+    <t>RPET RESIN</t>
+  </si>
+  <si>
+    <t>TDS &amp; COA: NA
+Planned Trial on 3rd April 2026: 
+mc-07 - MP0024.1
+mc-10 - MP0045.1</t>
   </si>
 </sst>
 </file>
@@ -8406,20 +8421,20 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{03EE533D-708C-4AEB-9D0D-2E3195DE5812}" name="Table1" displayName="Table1" ref="A1:K534" totalsRowShown="0" headerRowDxfId="0" dataDxfId="15" headerRowBorderDxfId="13" tableBorderDxfId="14" totalsRowBorderDxfId="12">
-  <autoFilter ref="A1:K534" xr:uid="{03EE533D-708C-4AEB-9D0D-2E3195DE5812}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{F331C5FA-3C12-4A27-9B9C-DEB5B2DAFE13}" name="Table1" displayName="Table1" ref="A1:K535" totalsRowShown="0" headerRowDxfId="0" dataDxfId="15" headerRowBorderDxfId="13" tableBorderDxfId="14" totalsRowBorderDxfId="12">
+  <autoFilter ref="A1:K535" xr:uid="{F331C5FA-3C12-4A27-9B9C-DEB5B2DAFE13}"/>
   <tableColumns count="11">
-    <tableColumn id="1" xr3:uid="{8468CDF2-DB87-447F-8CE6-3C981FAE775A}" name="ID" dataDxfId="11"/>
-    <tableColumn id="2" xr3:uid="{865C5089-FB9E-4253-9987-6D732953DB70}" name="Status" dataDxfId="10"/>
-    <tableColumn id="3" xr3:uid="{572F8903-F152-474E-8A8B-9DFD76326929}" name="Material List::Material_Detail" dataDxfId="9"/>
-    <tableColumn id="4" xr3:uid="{0EB650E1-C722-426F-AE64-DD0AC9405178}" name="Product_Code" dataDxfId="8"/>
-    <tableColumn id="5" xr3:uid="{CAD66990-BF5A-4356-91DC-496DF0DB6706}" name="RM PM Product List 2::Product_Detail" dataDxfId="7"/>
-    <tableColumn id="6" xr3:uid="{2BFC3698-BD50-4441-BBC8-68B71ED5FCF5}" name="Item_Code" dataDxfId="6"/>
-    <tableColumn id="7" xr3:uid="{21AE0DEC-9493-4534-BACF-E074CE0AF4AC}" name="Old_Item_Code" dataDxfId="5"/>
-    <tableColumn id="8" xr3:uid="{76ABFD0A-3271-4FAD-9795-A9045A64FD22}" name="Item_Name" dataDxfId="4"/>
-    <tableColumn id="9" xr3:uid="{29DF494E-C337-47C0-9FBF-14FE9B873076}" name="Item_Detail_by_Vendor" dataDxfId="3"/>
-    <tableColumn id="10" xr3:uid="{0E38AF1C-A4B5-4AB2-81CD-C06F23A1A6E9}" name="Vendor List 2::Vendor_Name" dataDxfId="2"/>
-    <tableColumn id="11" xr3:uid="{78CA8D49-1230-4AE9-BB51-0FF1938A1D04}" name="Remarks" dataDxfId="1"/>
+    <tableColumn id="1" xr3:uid="{7714AD47-3BF0-4E4B-A3C4-C595BBCF808C}" name="ID" dataDxfId="11"/>
+    <tableColumn id="2" xr3:uid="{FCB7D981-EE57-4C04-95C3-8163C3AFAFE8}" name="Status" dataDxfId="10"/>
+    <tableColumn id="3" xr3:uid="{EFD5CBDD-86E9-497F-860F-3ECB05C2D333}" name="Material List::Material_Detail" dataDxfId="9"/>
+    <tableColumn id="4" xr3:uid="{8B1DFC98-513A-4DBA-93C0-417405C75FDC}" name="Product_Code" dataDxfId="8"/>
+    <tableColumn id="5" xr3:uid="{7218CA50-EA3D-4E7C-88C2-937C48805B7D}" name="RM PM Product List 2::Product_Detail" dataDxfId="7"/>
+    <tableColumn id="6" xr3:uid="{799C31B7-1830-41B6-B14E-5CA7C840328A}" name="Item_Code" dataDxfId="6"/>
+    <tableColumn id="7" xr3:uid="{AC64CD68-8AE1-45B7-B1C1-BFEA7EC64AF4}" name="Old_Item_Code" dataDxfId="5"/>
+    <tableColumn id="8" xr3:uid="{9E890DB5-24DD-43E9-9C12-6A131337B712}" name="Item_Name" dataDxfId="4"/>
+    <tableColumn id="9" xr3:uid="{49EA27FB-FADB-4493-96C5-0084B39B4B2C}" name="Item_Detail_by_Vendor" dataDxfId="3"/>
+    <tableColumn id="10" xr3:uid="{C228BC38-B18F-4977-94C9-9D6A28CA10E2}" name="Vendor List 2::Vendor_Name" dataDxfId="2"/>
+    <tableColumn id="11" xr3:uid="{D5DC21E0-C262-42BB-B1E8-7FE5B70BDD1C}" name="Remarks" dataDxfId="1"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -8722,7 +8737,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:K534"/>
+  <dimension ref="A1:K535"/>
   <sheetFormatPr defaultColWidth="21.7109375" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.140625" bestFit="1" customWidth="1"/>
@@ -26196,40 +26211,73 @@
       </c>
     </row>
     <row r="534" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A534" s="9">
+      <c r="A534" s="4">
         <v>534</v>
       </c>
-      <c r="B534" s="10" t="s">
-        <v>11</v>
-      </c>
-      <c r="C534" s="10" t="s">
+      <c r="B534" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C534" s="5" t="s">
         <v>1472</v>
       </c>
-      <c r="D534" s="10" t="s">
+      <c r="D534" s="5" t="s">
         <v>2457</v>
       </c>
-      <c r="E534" s="10" t="s">
+      <c r="E534" s="5" t="s">
         <v>2458</v>
       </c>
-      <c r="F534" s="10" t="s">
+      <c r="F534" s="5" t="s">
         <v>2459</v>
       </c>
-      <c r="G534" s="11"/>
-      <c r="H534" s="10" t="s">
+      <c r="G534" s="7"/>
+      <c r="H534" s="5" t="s">
         <v>2460</v>
       </c>
-      <c r="I534" s="10" t="s">
+      <c r="I534" s="5" t="s">
         <v>2461</v>
       </c>
-      <c r="J534" s="10" t="s">
+      <c r="J534" s="5" t="s">
         <v>1524</v>
       </c>
-      <c r="K534" s="12" t="s">
+      <c r="K534" s="8" t="s">
         <v>2462</v>
       </c>
     </row>
+    <row r="535" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A535" s="9">
+        <v>535</v>
+      </c>
+      <c r="B535" s="10" t="s">
+        <v>11</v>
+      </c>
+      <c r="C535" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="D535" s="10" t="s">
+        <v>1827</v>
+      </c>
+      <c r="E535" s="10" t="s">
+        <v>1828</v>
+      </c>
+      <c r="F535" s="10" t="s">
+        <v>2463</v>
+      </c>
+      <c r="G535" s="11"/>
+      <c r="H535" s="10" t="s">
+        <v>2464</v>
+      </c>
+      <c r="I535" s="10" t="s">
+        <v>2465</v>
+      </c>
+      <c r="J535" s="10" t="s">
+        <v>2367</v>
+      </c>
+      <c r="K535" s="12" t="s">
+        <v>2466</v>
+      </c>
+    </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="5av31vnnFljIfOAuHPPC6zsrmODCUei6w4Et9paNfN9tBWhnJdn3Rf3fjwwFEZK+0F+NNnRs/amW3rQOhl2E0Q==" saltValue="6NzH6u9itqoL9XbNFr4t2w==" spinCount="100000" sheet="1" objects="1" scenarios="1" sort="0" autoFilter="0"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="8Fvownv+2MXvy0uCoQxN6EiZIJk9ZWE+KHMNz85MFUQI36Q33tiMOjNrCCj8VSox0ToTtd3oUpryQchcarQ+sQ==" saltValue="J4bars0Jx/nh2ERJxo0U3w==" spinCount="100000" sheet="1" objects="1" scenarios="1" sort="0" autoFilter="0"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <tableParts count="1">
     <tablePart r:id="rId1"/>

--- a/RM.xlsx
+++ b/RM.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="25330"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\MPCI QC\Desktop\FG &amp; RMPM LIST\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\FG &amp; RMPM LIST\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{362E5F14-1DA5-4ACB-8AA4-1F6DA58E6273}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EAEAA9AC-7881-4050-ACE8-14246F7000B5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4750" uniqueCount="2467">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4782" uniqueCount="2486">
   <si>
     <t>ID</t>
   </si>
@@ -7888,9 +7888,85 @@
   </si>
   <si>
     <t>TDS &amp; COA: NA
-Planned Trial on 3rd April 2026: 
+Trial on 3rd April 2026: 
 mc-07 - MP0024.1
+Trial on 4th April 2026:
+mc-03 - MP0370.1
 mc-10 - MP0045.1</t>
+  </si>
+  <si>
+    <t>RM257.3</t>
+  </si>
+  <si>
+    <t>FTC 38mm Tablet Metallic Gold (MATTE)</t>
+  </si>
+  <si>
+    <t>38mm Golden Metallic Fliptop</t>
+  </si>
+  <si>
+    <t>Procured from: RITU PLASTIC
+HEIGHT: 18.74 MM
+OD: 40.20 MM
+WEIGHT: 5.30 GM</t>
+  </si>
+  <si>
+    <t>RM269</t>
+  </si>
+  <si>
+    <t>INNER PLUG 46mm U Cup H=15.40, OD=39.65, W=3.30</t>
+  </si>
+  <si>
+    <t>RM269.1</t>
+  </si>
+  <si>
+    <t>Inner Plug 46mm U Cup Clear</t>
+  </si>
+  <si>
+    <t>Latest Packaging Karnal</t>
+  </si>
+  <si>
+    <t>TO BE PROCURED..
+Codification based on sample Piece
+Weight:3.30 GM
+Height: 15.40 MM
+OD (Mouth): 39.65 MM
+OD (Head): 38.15 MM
+Depth: 13.30 MM</t>
+  </si>
+  <si>
+    <t>RM268</t>
+  </si>
+  <si>
+    <t>Measuring Cup 50ml 46mm H=29.00, OD=52.00, W=5.85</t>
+  </si>
+  <si>
+    <t>RM268.1</t>
+  </si>
+  <si>
+    <t>Measuring Cup Clear 50ml 46mm</t>
+  </si>
+  <si>
+    <t>Measuring Cup 46mm</t>
+  </si>
+  <si>
+    <t>TO BE PROCURED..
+Codification based on sample Piece
+Procured on: 4th May 2026
+Observation: Some Cups loose fit on 46mm Screw Caps, Cups would fall off on their own if Bottle is inverted. Accepted only for this consignment.
+Weight: 5.87 gm
+Height: 29.00 mm
+OD (Mouth): 52.00 mm
+OD (Head): 49.00 mm
+Depth: 27.90 mm</t>
+  </si>
+  <si>
+    <t>RM114.3</t>
+  </si>
+  <si>
+    <t>Tape Roll BOPP 48mmx300mtrx42micron (Tpt) PIPL</t>
+  </si>
+  <si>
+    <t>Codification done on PO basis....</t>
   </si>
 </sst>
 </file>
@@ -8070,10 +8146,10 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
@@ -8421,20 +8497,20 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{F331C5FA-3C12-4A27-9B9C-DEB5B2DAFE13}" name="Table1" displayName="Table1" ref="A1:K535" totalsRowShown="0" headerRowDxfId="0" dataDxfId="15" headerRowBorderDxfId="13" tableBorderDxfId="14" totalsRowBorderDxfId="12">
-  <autoFilter ref="A1:K535" xr:uid="{F331C5FA-3C12-4A27-9B9C-DEB5B2DAFE13}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{621D8861-5843-4820-8599-C0841FFE000A}" name="Table1" displayName="Table1" ref="A1:K539" totalsRowShown="0" headerRowDxfId="0" dataDxfId="15" headerRowBorderDxfId="13" tableBorderDxfId="14" totalsRowBorderDxfId="12">
+  <autoFilter ref="A1:K539" xr:uid="{621D8861-5843-4820-8599-C0841FFE000A}"/>
   <tableColumns count="11">
-    <tableColumn id="1" xr3:uid="{7714AD47-3BF0-4E4B-A3C4-C595BBCF808C}" name="ID" dataDxfId="11"/>
-    <tableColumn id="2" xr3:uid="{FCB7D981-EE57-4C04-95C3-8163C3AFAFE8}" name="Status" dataDxfId="10"/>
-    <tableColumn id="3" xr3:uid="{EFD5CBDD-86E9-497F-860F-3ECB05C2D333}" name="Material List::Material_Detail" dataDxfId="9"/>
-    <tableColumn id="4" xr3:uid="{8B1DFC98-513A-4DBA-93C0-417405C75FDC}" name="Product_Code" dataDxfId="8"/>
-    <tableColumn id="5" xr3:uid="{7218CA50-EA3D-4E7C-88C2-937C48805B7D}" name="RM PM Product List 2::Product_Detail" dataDxfId="7"/>
-    <tableColumn id="6" xr3:uid="{799C31B7-1830-41B6-B14E-5CA7C840328A}" name="Item_Code" dataDxfId="6"/>
-    <tableColumn id="7" xr3:uid="{AC64CD68-8AE1-45B7-B1C1-BFEA7EC64AF4}" name="Old_Item_Code" dataDxfId="5"/>
-    <tableColumn id="8" xr3:uid="{9E890DB5-24DD-43E9-9C12-6A131337B712}" name="Item_Name" dataDxfId="4"/>
-    <tableColumn id="9" xr3:uid="{49EA27FB-FADB-4493-96C5-0084B39B4B2C}" name="Item_Detail_by_Vendor" dataDxfId="3"/>
-    <tableColumn id="10" xr3:uid="{C228BC38-B18F-4977-94C9-9D6A28CA10E2}" name="Vendor List 2::Vendor_Name" dataDxfId="2"/>
-    <tableColumn id="11" xr3:uid="{D5DC21E0-C262-42BB-B1E8-7FE5B70BDD1C}" name="Remarks" dataDxfId="1"/>
+    <tableColumn id="1" xr3:uid="{2F23AE1D-29A2-4A1D-8238-C2F52E35C357}" name="ID" dataDxfId="11"/>
+    <tableColumn id="2" xr3:uid="{9C43327E-0145-437B-BE49-473D4BFD19C4}" name="Status" dataDxfId="10"/>
+    <tableColumn id="3" xr3:uid="{9542BAAC-1E59-4F7E-AB6E-55127EFAAB3F}" name="Material List::Material_Detail" dataDxfId="9"/>
+    <tableColumn id="4" xr3:uid="{F1F0D5EA-904F-4DFD-97CD-2E3F36BED7CA}" name="Product_Code" dataDxfId="8"/>
+    <tableColumn id="5" xr3:uid="{08E1270D-67D7-4AF5-AFBE-91F675782A6E}" name="RM PM Product List 2::Product_Detail" dataDxfId="7"/>
+    <tableColumn id="6" xr3:uid="{911ADD1F-25BA-4BE6-B975-CED4C0AEA3D1}" name="Item_Code" dataDxfId="6"/>
+    <tableColumn id="7" xr3:uid="{A4FC3FDC-7F57-41BE-92EB-9502802E2DD7}" name="Old_Item_Code" dataDxfId="5"/>
+    <tableColumn id="8" xr3:uid="{9C7EA96C-9209-463A-979D-059A103A44FE}" name="Item_Name" dataDxfId="4"/>
+    <tableColumn id="9" xr3:uid="{12837EAC-E6EF-4308-836B-8A65CA774133}" name="Item_Detail_by_Vendor" dataDxfId="3"/>
+    <tableColumn id="10" xr3:uid="{E804ADA3-C580-4AD2-B6FD-2EE44341324D}" name="Vendor List 2::Vendor_Name" dataDxfId="2"/>
+    <tableColumn id="11" xr3:uid="{DC3E43BE-70BD-4AEB-B7DB-EE6F07BC3DF0}" name="Remarks" dataDxfId="1"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -8737,7 +8813,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:K535"/>
+  <dimension ref="A1:K539"/>
   <sheetFormatPr defaultColWidth="21.7109375" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.140625" bestFit="1" customWidth="1"/>
@@ -26244,40 +26320,164 @@
       </c>
     </row>
     <row r="535" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A535" s="9">
+      <c r="A535" s="4">
         <v>535</v>
       </c>
-      <c r="B535" s="10" t="s">
-        <v>11</v>
-      </c>
-      <c r="C535" s="10" t="s">
+      <c r="B535" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C535" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="D535" s="10" t="s">
+      <c r="D535" s="5" t="s">
         <v>1827</v>
       </c>
-      <c r="E535" s="10" t="s">
+      <c r="E535" s="5" t="s">
         <v>1828</v>
       </c>
-      <c r="F535" s="10" t="s">
+      <c r="F535" s="5" t="s">
         <v>2463</v>
       </c>
-      <c r="G535" s="11"/>
-      <c r="H535" s="10" t="s">
+      <c r="G535" s="7"/>
+      <c r="H535" s="5" t="s">
         <v>2464</v>
       </c>
-      <c r="I535" s="10" t="s">
+      <c r="I535" s="5" t="s">
         <v>2465</v>
       </c>
-      <c r="J535" s="10" t="s">
+      <c r="J535" s="5" t="s">
         <v>2367</v>
       </c>
-      <c r="K535" s="12" t="s">
+      <c r="K535" s="8" t="s">
         <v>2466</v>
       </c>
     </row>
+    <row r="536" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A536" s="4">
+        <v>536</v>
+      </c>
+      <c r="B536" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C536" s="5" t="s">
+        <v>1472</v>
+      </c>
+      <c r="D536" s="5" t="s">
+        <v>2354</v>
+      </c>
+      <c r="E536" s="5" t="s">
+        <v>2355</v>
+      </c>
+      <c r="F536" s="5" t="s">
+        <v>2467</v>
+      </c>
+      <c r="G536" s="7"/>
+      <c r="H536" s="5" t="s">
+        <v>2468</v>
+      </c>
+      <c r="I536" s="5" t="s">
+        <v>2469</v>
+      </c>
+      <c r="J536" s="5" t="s">
+        <v>1524</v>
+      </c>
+      <c r="K536" s="8" t="s">
+        <v>2470</v>
+      </c>
+    </row>
+    <row r="537" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A537" s="4">
+        <v>537</v>
+      </c>
+      <c r="B537" s="7"/>
+      <c r="C537" s="5" t="s">
+        <v>1472</v>
+      </c>
+      <c r="D537" s="5" t="s">
+        <v>2471</v>
+      </c>
+      <c r="E537" s="5" t="s">
+        <v>2472</v>
+      </c>
+      <c r="F537" s="5" t="s">
+        <v>2473</v>
+      </c>
+      <c r="G537" s="7"/>
+      <c r="H537" s="5" t="s">
+        <v>2474</v>
+      </c>
+      <c r="I537" s="7"/>
+      <c r="J537" s="5" t="s">
+        <v>2475</v>
+      </c>
+      <c r="K537" s="8" t="s">
+        <v>2476</v>
+      </c>
+    </row>
+    <row r="538" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A538" s="4">
+        <v>538</v>
+      </c>
+      <c r="B538" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C538" s="5" t="s">
+        <v>1472</v>
+      </c>
+      <c r="D538" s="5" t="s">
+        <v>2477</v>
+      </c>
+      <c r="E538" s="5" t="s">
+        <v>2478</v>
+      </c>
+      <c r="F538" s="5" t="s">
+        <v>2479</v>
+      </c>
+      <c r="G538" s="7"/>
+      <c r="H538" s="5" t="s">
+        <v>2480</v>
+      </c>
+      <c r="I538" s="5" t="s">
+        <v>2481</v>
+      </c>
+      <c r="J538" s="5" t="s">
+        <v>2475</v>
+      </c>
+      <c r="K538" s="8" t="s">
+        <v>2482</v>
+      </c>
+    </row>
+    <row r="539" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A539" s="9">
+        <v>539</v>
+      </c>
+      <c r="B539" s="10"/>
+      <c r="C539" s="11" t="s">
+        <v>969</v>
+      </c>
+      <c r="D539" s="11" t="s">
+        <v>970</v>
+      </c>
+      <c r="E539" s="11" t="s">
+        <v>971</v>
+      </c>
+      <c r="F539" s="11" t="s">
+        <v>2483</v>
+      </c>
+      <c r="G539" s="10"/>
+      <c r="H539" s="11" t="s">
+        <v>2484</v>
+      </c>
+      <c r="I539" s="10"/>
+      <c r="J539" s="11" t="s">
+        <v>2455</v>
+      </c>
+      <c r="K539" s="12" t="s">
+        <v>2485</v>
+      </c>
+    </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="8Fvownv+2MXvy0uCoQxN6EiZIJk9ZWE+KHMNz85MFUQI36Q33tiMOjNrCCj8VSox0ToTtd3oUpryQchcarQ+sQ==" saltValue="J4bars0Jx/nh2ERJxo0U3w==" spinCount="100000" sheet="1" objects="1" scenarios="1" sort="0" autoFilter="0"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="Wgq/fhdgpOShr3bLMbDcz6Kc0Zi+G8f+nzxM765mEu/aLD25la43nrcu+Re0Yr0OwK2L+qzwfmskyfJwLgYVXA==" saltValue="xn8lSsyZQqz2lQhcHkQ1dw==" spinCount="100000" sheet="1" objects="1" scenarios="1" sort="0" autoFilter="0"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <tableParts count="1">
     <tablePart r:id="rId1"/>

--- a/RM.xlsx
+++ b/RM.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\FG &amp; RMPM LIST\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EAEAA9AC-7881-4050-ACE8-14246F7000B5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E61582AB-D049-46D3-A736-70E7997B1A7A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4782" uniqueCount="2486">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4817" uniqueCount="2500">
   <si>
     <t>ID</t>
   </si>
@@ -7967,6 +7967,51 @@
   </si>
   <si>
     <t>Codification done on PO basis....</t>
+  </si>
+  <si>
+    <t>RM111.14</t>
+  </si>
+  <si>
+    <t>FTC Short 19mm Purple (3mm) ACE H=23.3, OD=22.4, W=2.4</t>
+  </si>
+  <si>
+    <t>19mm Short Fliptop Cap Purple</t>
+  </si>
+  <si>
+    <t>RM084.5</t>
+  </si>
+  <si>
+    <t>BMW 25mm Black Cap H=21.0, OD=29.3, W=2.6</t>
+  </si>
+  <si>
+    <t>25mm BMW Caps Black</t>
+  </si>
+  <si>
+    <t>RM202.6</t>
+  </si>
+  <si>
+    <t>PET Resin Recycled RPET B2B  - 1000Kgs</t>
+  </si>
+  <si>
+    <t>RPET B2B RESIN</t>
+  </si>
+  <si>
+    <t>Plain Bag, No information/artwork available on bag. Bill Image attached</t>
+  </si>
+  <si>
+    <t>RM085.6</t>
+  </si>
+  <si>
+    <t>Screw 28mm BMW Black Cap VP H=21.10, OD=33.7, W=3.4</t>
+  </si>
+  <si>
+    <t>PP CAP 28MM BLACK WITH SEAL D0066</t>
+  </si>
+  <si>
+    <t>Procured on: 18-05-2026
+Height: 21.00 mm
+OD: 33.50 mm
+Weight: 3.70 gm</t>
   </si>
 </sst>
 </file>
@@ -8146,10 +8191,10 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
@@ -8497,20 +8542,20 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{621D8861-5843-4820-8599-C0841FFE000A}" name="Table1" displayName="Table1" ref="A1:K539" totalsRowShown="0" headerRowDxfId="0" dataDxfId="15" headerRowBorderDxfId="13" tableBorderDxfId="14" totalsRowBorderDxfId="12">
-  <autoFilter ref="A1:K539" xr:uid="{621D8861-5843-4820-8599-C0841FFE000A}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{C1A0CD41-9604-4120-AF13-B36509CA7BAB}" name="Table1" displayName="Table1" ref="A1:K543" totalsRowShown="0" headerRowDxfId="0" dataDxfId="15" headerRowBorderDxfId="13" tableBorderDxfId="14" totalsRowBorderDxfId="12">
+  <autoFilter ref="A1:K543" xr:uid="{C1A0CD41-9604-4120-AF13-B36509CA7BAB}"/>
   <tableColumns count="11">
-    <tableColumn id="1" xr3:uid="{2F23AE1D-29A2-4A1D-8238-C2F52E35C357}" name="ID" dataDxfId="11"/>
-    <tableColumn id="2" xr3:uid="{9C43327E-0145-437B-BE49-473D4BFD19C4}" name="Status" dataDxfId="10"/>
-    <tableColumn id="3" xr3:uid="{9542BAAC-1E59-4F7E-AB6E-55127EFAAB3F}" name="Material List::Material_Detail" dataDxfId="9"/>
-    <tableColumn id="4" xr3:uid="{F1F0D5EA-904F-4DFD-97CD-2E3F36BED7CA}" name="Product_Code" dataDxfId="8"/>
-    <tableColumn id="5" xr3:uid="{08E1270D-67D7-4AF5-AFBE-91F675782A6E}" name="RM PM Product List 2::Product_Detail" dataDxfId="7"/>
-    <tableColumn id="6" xr3:uid="{911ADD1F-25BA-4BE6-B975-CED4C0AEA3D1}" name="Item_Code" dataDxfId="6"/>
-    <tableColumn id="7" xr3:uid="{A4FC3FDC-7F57-41BE-92EB-9502802E2DD7}" name="Old_Item_Code" dataDxfId="5"/>
-    <tableColumn id="8" xr3:uid="{9C7EA96C-9209-463A-979D-059A103A44FE}" name="Item_Name" dataDxfId="4"/>
-    <tableColumn id="9" xr3:uid="{12837EAC-E6EF-4308-836B-8A65CA774133}" name="Item_Detail_by_Vendor" dataDxfId="3"/>
-    <tableColumn id="10" xr3:uid="{E804ADA3-C580-4AD2-B6FD-2EE44341324D}" name="Vendor List 2::Vendor_Name" dataDxfId="2"/>
-    <tableColumn id="11" xr3:uid="{DC3E43BE-70BD-4AEB-B7DB-EE6F07BC3DF0}" name="Remarks" dataDxfId="1"/>
+    <tableColumn id="1" xr3:uid="{106A661A-32B8-4192-9145-1E8FC4875709}" name="ID" dataDxfId="11"/>
+    <tableColumn id="2" xr3:uid="{DCC04206-9405-4B11-89DC-8369FA4E1672}" name="Status" dataDxfId="10"/>
+    <tableColumn id="3" xr3:uid="{651ED718-66F2-476E-85ED-9F10F289EF82}" name="Material List::Material_Detail" dataDxfId="9"/>
+    <tableColumn id="4" xr3:uid="{B4042D24-F4F4-4412-9622-CF06B69C188D}" name="Product_Code" dataDxfId="8"/>
+    <tableColumn id="5" xr3:uid="{FC9A498A-CEA7-499D-A9FF-5A3CAF76EBB2}" name="RM PM Product List 2::Product_Detail" dataDxfId="7"/>
+    <tableColumn id="6" xr3:uid="{B120EBA3-B7B5-4A0D-8F1D-975668789538}" name="Item_Code" dataDxfId="6"/>
+    <tableColumn id="7" xr3:uid="{9847C85B-3993-4F58-B8C5-23D1EC660B04}" name="Old_Item_Code" dataDxfId="5"/>
+    <tableColumn id="8" xr3:uid="{48C29934-43C5-4753-8B35-E5451B09ED0A}" name="Item_Name" dataDxfId="4"/>
+    <tableColumn id="9" xr3:uid="{C5F1E75E-651C-4141-AC9D-43E5494F473E}" name="Item_Detail_by_Vendor" dataDxfId="3"/>
+    <tableColumn id="10" xr3:uid="{0FE43CEF-B42B-4074-AAE8-F183BB65E25B}" name="Vendor List 2::Vendor_Name" dataDxfId="2"/>
+    <tableColumn id="11" xr3:uid="{1D11E7C3-A86D-45D8-84DB-403FB80313E7}" name="Remarks" dataDxfId="1"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -8813,7 +8858,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:K539"/>
+  <dimension ref="A1:K543"/>
   <sheetFormatPr defaultColWidth="21.7109375" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.140625" bestFit="1" customWidth="1"/>
@@ -26448,36 +26493,166 @@
       </c>
     </row>
     <row r="539" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A539" s="9">
+      <c r="A539" s="4">
         <v>539</v>
       </c>
-      <c r="B539" s="10"/>
-      <c r="C539" s="11" t="s">
+      <c r="B539" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C539" s="5" t="s">
         <v>969</v>
       </c>
-      <c r="D539" s="11" t="s">
+      <c r="D539" s="5" t="s">
         <v>970</v>
       </c>
-      <c r="E539" s="11" t="s">
+      <c r="E539" s="5" t="s">
         <v>971</v>
       </c>
-      <c r="F539" s="11" t="s">
+      <c r="F539" s="5" t="s">
         <v>2483</v>
       </c>
-      <c r="G539" s="10"/>
-      <c r="H539" s="11" t="s">
+      <c r="G539" s="7"/>
+      <c r="H539" s="5" t="s">
         <v>2484</v>
       </c>
-      <c r="I539" s="10"/>
-      <c r="J539" s="11" t="s">
+      <c r="I539" s="7"/>
+      <c r="J539" s="5" t="s">
         <v>2455</v>
       </c>
-      <c r="K539" s="12" t="s">
+      <c r="K539" s="8" t="s">
         <v>2485</v>
       </c>
     </row>
+    <row r="540" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A540" s="4">
+        <v>540</v>
+      </c>
+      <c r="B540" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C540" s="5" t="s">
+        <v>1472</v>
+      </c>
+      <c r="D540" s="5" t="s">
+        <v>1636</v>
+      </c>
+      <c r="E540" s="5" t="s">
+        <v>1637</v>
+      </c>
+      <c r="F540" s="5" t="s">
+        <v>2486</v>
+      </c>
+      <c r="G540" s="7"/>
+      <c r="H540" s="5" t="s">
+        <v>2487</v>
+      </c>
+      <c r="I540" s="5" t="s">
+        <v>2488</v>
+      </c>
+      <c r="J540" s="5" t="s">
+        <v>1669</v>
+      </c>
+      <c r="K540" s="6"/>
+    </row>
+    <row r="541" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A541" s="4">
+        <v>541</v>
+      </c>
+      <c r="B541" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C541" s="5" t="s">
+        <v>1472</v>
+      </c>
+      <c r="D541" s="5" t="s">
+        <v>1518</v>
+      </c>
+      <c r="E541" s="5" t="s">
+        <v>1519</v>
+      </c>
+      <c r="F541" s="5" t="s">
+        <v>2489</v>
+      </c>
+      <c r="G541" s="7"/>
+      <c r="H541" s="5" t="s">
+        <v>2490</v>
+      </c>
+      <c r="I541" s="5" t="s">
+        <v>2491</v>
+      </c>
+      <c r="J541" s="5" t="s">
+        <v>1524</v>
+      </c>
+      <c r="K541" s="6"/>
+    </row>
+    <row r="542" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A542" s="4">
+        <v>542</v>
+      </c>
+      <c r="B542" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C542" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="D542" s="5" t="s">
+        <v>1827</v>
+      </c>
+      <c r="E542" s="5" t="s">
+        <v>1828</v>
+      </c>
+      <c r="F542" s="5" t="s">
+        <v>2492</v>
+      </c>
+      <c r="G542" s="7"/>
+      <c r="H542" s="5" t="s">
+        <v>2493</v>
+      </c>
+      <c r="I542" s="5" t="s">
+        <v>2494</v>
+      </c>
+      <c r="J542" s="5" t="s">
+        <v>555</v>
+      </c>
+      <c r="K542" s="8" t="s">
+        <v>2495</v>
+      </c>
+    </row>
+    <row r="543" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A543" s="9">
+        <v>543</v>
+      </c>
+      <c r="B543" s="10" t="s">
+        <v>11</v>
+      </c>
+      <c r="C543" s="10" t="s">
+        <v>1472</v>
+      </c>
+      <c r="D543" s="10" t="s">
+        <v>1553</v>
+      </c>
+      <c r="E543" s="10" t="s">
+        <v>1554</v>
+      </c>
+      <c r="F543" s="10" t="s">
+        <v>2496</v>
+      </c>
+      <c r="G543" s="11"/>
+      <c r="H543" s="10" t="s">
+        <v>2497</v>
+      </c>
+      <c r="I543" s="10" t="s">
+        <v>2498</v>
+      </c>
+      <c r="J543" s="10" t="s">
+        <v>1786</v>
+      </c>
+      <c r="K543" s="12" t="s">
+        <v>2499</v>
+      </c>
+    </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="Wgq/fhdgpOShr3bLMbDcz6Kc0Zi+G8f+nzxM765mEu/aLD25la43nrcu+Re0Yr0OwK2L+qzwfmskyfJwLgYVXA==" saltValue="xn8lSsyZQqz2lQhcHkQ1dw==" spinCount="100000" sheet="1" objects="1" scenarios="1" sort="0" autoFilter="0"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="DUiIXvtfF7dwMToDoPOnaG5X8HiwDoTknbZp5EAlHgtT7YeJ8D1ZBQvsOx+wAhrlgYqP2e1v3nSTcg4TZF1Thg==" saltValue="99Ow8nbpnTPt5Cy/25J6Dg==" spinCount="100000" sheet="1" objects="1" scenarios="1" sort="0" autoFilter="0"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <tableParts count="1">
     <tablePart r:id="rId1"/>

--- a/RM.xlsx
+++ b/RM.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\FG &amp; RMPM LIST\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E61582AB-D049-46D3-A736-70E7997B1A7A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{23845A59-CF8B-42A3-A71A-F7C22B9C10E5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4817" uniqueCount="2500">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4835" uniqueCount="2507">
   <si>
     <t>ID</t>
   </si>
@@ -7833,9 +7833,9 @@
     <t>Rungta Eco Extrusions Private Limited</t>
   </si>
   <si>
-    <t>Billed to: Dabur
+    <t xml:space="preserve">Billed to: Dabur
 Shipped to: MPCI
-Trial not done yet</t>
+</t>
   </si>
   <si>
     <t>RM116.3</t>
@@ -8012,6 +8012,30 @@
 Height: 21.00 mm
 OD: 33.50 mm
 Weight: 3.70 gm</t>
+  </si>
+  <si>
+    <t>RM202.7</t>
+  </si>
+  <si>
+    <t>PET Resin Recycled RPET 0.84 IV (PETOLOOP084)  - 1150Kgs</t>
+  </si>
+  <si>
+    <t>1222111269 r-PET Resin 0.84 IV</t>
+  </si>
+  <si>
+    <t>Received another rPET Resin from Dabur (Biller, name of Dodhia not mentioned anywhere on Bill except the Resin Bags)
+Mfr.: DODHIA Company
+On 23rd and 25th May 2026
+PETOLOOP084- 1150KG</t>
+  </si>
+  <si>
+    <t>RM007.8</t>
+  </si>
+  <si>
+    <t>Amber (NB83-MON-0I BROWN 407592 23-0442)  Colour PET</t>
+  </si>
+  <si>
+    <t>NB83-MON-0I BROWN 407592 23-0442</t>
   </si>
 </sst>
 </file>
@@ -8195,9 +8219,7 @@
       <alignment vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1"/>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -8542,20 +8564,20 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{C1A0CD41-9604-4120-AF13-B36509CA7BAB}" name="Table1" displayName="Table1" ref="A1:K543" totalsRowShown="0" headerRowDxfId="0" dataDxfId="15" headerRowBorderDxfId="13" tableBorderDxfId="14" totalsRowBorderDxfId="12">
-  <autoFilter ref="A1:K543" xr:uid="{C1A0CD41-9604-4120-AF13-B36509CA7BAB}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{1830319C-9417-47AE-9107-B778F23861D8}" name="Table1" displayName="Table1" ref="A1:K545" totalsRowShown="0" headerRowDxfId="0" dataDxfId="15" headerRowBorderDxfId="13" tableBorderDxfId="14" totalsRowBorderDxfId="12">
+  <autoFilter ref="A1:K545" xr:uid="{1830319C-9417-47AE-9107-B778F23861D8}"/>
   <tableColumns count="11">
-    <tableColumn id="1" xr3:uid="{106A661A-32B8-4192-9145-1E8FC4875709}" name="ID" dataDxfId="11"/>
-    <tableColumn id="2" xr3:uid="{DCC04206-9405-4B11-89DC-8369FA4E1672}" name="Status" dataDxfId="10"/>
-    <tableColumn id="3" xr3:uid="{651ED718-66F2-476E-85ED-9F10F289EF82}" name="Material List::Material_Detail" dataDxfId="9"/>
-    <tableColumn id="4" xr3:uid="{B4042D24-F4F4-4412-9622-CF06B69C188D}" name="Product_Code" dataDxfId="8"/>
-    <tableColumn id="5" xr3:uid="{FC9A498A-CEA7-499D-A9FF-5A3CAF76EBB2}" name="RM PM Product List 2::Product_Detail" dataDxfId="7"/>
-    <tableColumn id="6" xr3:uid="{B120EBA3-B7B5-4A0D-8F1D-975668789538}" name="Item_Code" dataDxfId="6"/>
-    <tableColumn id="7" xr3:uid="{9847C85B-3993-4F58-B8C5-23D1EC660B04}" name="Old_Item_Code" dataDxfId="5"/>
-    <tableColumn id="8" xr3:uid="{48C29934-43C5-4753-8B35-E5451B09ED0A}" name="Item_Name" dataDxfId="4"/>
-    <tableColumn id="9" xr3:uid="{C5F1E75E-651C-4141-AC9D-43E5494F473E}" name="Item_Detail_by_Vendor" dataDxfId="3"/>
-    <tableColumn id="10" xr3:uid="{0FE43CEF-B42B-4074-AAE8-F183BB65E25B}" name="Vendor List 2::Vendor_Name" dataDxfId="2"/>
-    <tableColumn id="11" xr3:uid="{1D11E7C3-A86D-45D8-84DB-403FB80313E7}" name="Remarks" dataDxfId="1"/>
+    <tableColumn id="1" xr3:uid="{C5A021E0-45BA-4ED4-923D-9AECE517E903}" name="ID" dataDxfId="11"/>
+    <tableColumn id="2" xr3:uid="{205DA61C-F3FB-4412-9D43-AA0087F0D28F}" name="Status" dataDxfId="10"/>
+    <tableColumn id="3" xr3:uid="{2BFD3825-8061-45E2-9AE4-E806E3718ABB}" name="Material List::Material_Detail" dataDxfId="9"/>
+    <tableColumn id="4" xr3:uid="{347A3BD7-08A7-4950-82E1-5996624AB870}" name="Product_Code" dataDxfId="8"/>
+    <tableColumn id="5" xr3:uid="{A13D2F54-9290-46A4-BC05-C0BBD0D21574}" name="RM PM Product List 2::Product_Detail" dataDxfId="7"/>
+    <tableColumn id="6" xr3:uid="{40AC261D-4621-49F8-AD18-6177C552A164}" name="Item_Code" dataDxfId="6"/>
+    <tableColumn id="7" xr3:uid="{576C5F22-863A-4E9C-A460-06D3896D58A3}" name="Old_Item_Code" dataDxfId="5"/>
+    <tableColumn id="8" xr3:uid="{00617C07-3289-4C5C-904D-AB33DB377F0A}" name="Item_Name" dataDxfId="4"/>
+    <tableColumn id="9" xr3:uid="{684C0F31-F18A-4999-8CD9-35320391F821}" name="Item_Detail_by_Vendor" dataDxfId="3"/>
+    <tableColumn id="10" xr3:uid="{F860F7BC-E20A-4D22-86C9-B767ECFFB173}" name="Vendor List 2::Vendor_Name" dataDxfId="2"/>
+    <tableColumn id="11" xr3:uid="{FAC1FB00-8FFC-4993-97E7-371587FB7EC6}" name="Remarks" dataDxfId="1"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -8858,7 +8880,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:K543"/>
+  <dimension ref="A1:K545"/>
   <sheetFormatPr defaultColWidth="21.7109375" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.140625" bestFit="1" customWidth="1"/>
@@ -26271,7 +26293,9 @@
       <c r="A532" s="4">
         <v>532</v>
       </c>
-      <c r="B532" s="7"/>
+      <c r="B532" s="5" t="s">
+        <v>11</v>
+      </c>
       <c r="C532" s="5" t="s">
         <v>12</v>
       </c>
@@ -26619,40 +26643,104 @@
       </c>
     </row>
     <row r="543" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A543" s="9">
+      <c r="A543" s="4">
         <v>543</v>
       </c>
-      <c r="B543" s="10" t="s">
-        <v>11</v>
-      </c>
-      <c r="C543" s="10" t="s">
+      <c r="B543" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C543" s="5" t="s">
         <v>1472</v>
       </c>
-      <c r="D543" s="10" t="s">
+      <c r="D543" s="5" t="s">
         <v>1553</v>
       </c>
-      <c r="E543" s="10" t="s">
+      <c r="E543" s="5" t="s">
         <v>1554</v>
       </c>
-      <c r="F543" s="10" t="s">
+      <c r="F543" s="5" t="s">
         <v>2496</v>
       </c>
-      <c r="G543" s="11"/>
-      <c r="H543" s="10" t="s">
+      <c r="G543" s="7"/>
+      <c r="H543" s="5" t="s">
         <v>2497</v>
       </c>
-      <c r="I543" s="10" t="s">
+      <c r="I543" s="5" t="s">
         <v>2498</v>
       </c>
-      <c r="J543" s="10" t="s">
+      <c r="J543" s="5" t="s">
         <v>1786</v>
       </c>
-      <c r="K543" s="12" t="s">
+      <c r="K543" s="8" t="s">
         <v>2499</v>
       </c>
     </row>
+    <row r="544" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A544" s="4">
+        <v>544</v>
+      </c>
+      <c r="B544" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C544" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="D544" s="5" t="s">
+        <v>1827</v>
+      </c>
+      <c r="E544" s="5" t="s">
+        <v>1828</v>
+      </c>
+      <c r="F544" s="5" t="s">
+        <v>2500</v>
+      </c>
+      <c r="G544" s="7"/>
+      <c r="H544" s="5" t="s">
+        <v>2501</v>
+      </c>
+      <c r="I544" s="5" t="s">
+        <v>2502</v>
+      </c>
+      <c r="J544" s="5" t="s">
+        <v>2200</v>
+      </c>
+      <c r="K544" s="8" t="s">
+        <v>2503</v>
+      </c>
+    </row>
+    <row r="545" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A545" s="9">
+        <v>545</v>
+      </c>
+      <c r="B545" s="10" t="s">
+        <v>11</v>
+      </c>
+      <c r="C545" s="10" t="s">
+        <v>67</v>
+      </c>
+      <c r="D545" s="10" t="s">
+        <v>68</v>
+      </c>
+      <c r="E545" s="10" t="s">
+        <v>69</v>
+      </c>
+      <c r="F545" s="10" t="s">
+        <v>2504</v>
+      </c>
+      <c r="G545" s="11"/>
+      <c r="H545" s="10" t="s">
+        <v>2505</v>
+      </c>
+      <c r="I545" s="10" t="s">
+        <v>2506</v>
+      </c>
+      <c r="J545" s="10" t="s">
+        <v>104</v>
+      </c>
+      <c r="K545" s="12"/>
+    </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="DUiIXvtfF7dwMToDoPOnaG5X8HiwDoTknbZp5EAlHgtT7YeJ8D1ZBQvsOx+wAhrlgYqP2e1v3nSTcg4TZF1Thg==" saltValue="99Ow8nbpnTPt5Cy/25J6Dg==" spinCount="100000" sheet="1" objects="1" scenarios="1" sort="0" autoFilter="0"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="8TXEK1U+Mu4KjKf0quQGAcR8kH+pLjdbwPS1AhlMu/UVW096cfuD6fcj3O4JFi2R8Q6daQOzwjinCMk6cTWeSg==" saltValue="sVaMAd4BDOGN1povQxCU0g==" spinCount="100000" sheet="1" objects="1" scenarios="1" sort="0" autoFilter="0"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <tableParts count="1">
     <tablePart r:id="rId1"/>

--- a/RM.xlsx
+++ b/RM.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\FG &amp; RMPM LIST\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{23845A59-CF8B-42A3-A71A-F7C22B9C10E5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F1764060-4106-4DA8-BC55-46DF612EA311}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4835" uniqueCount="2507">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4862" uniqueCount="2519">
   <si>
     <t>ID</t>
   </si>
@@ -8036,6 +8036,58 @@
   </si>
   <si>
     <t>NB83-MON-0I BROWN 407592 23-0442</t>
+  </si>
+  <si>
+    <t>RM087.5</t>
+  </si>
+  <si>
+    <t>Screw 53mm Plain Milky White Cap LP H=14.00, OD=54.50, W=4.20</t>
+  </si>
+  <si>
+    <t>53MM WHITE SCREW CAP</t>
+  </si>
+  <si>
+    <t>Procured from RITU PLASTICS
+This screw cap features a wad lock for an induction liner/wad.
+Height: 14.00 mm
+Weight: 4.20 gm
+ID (w/o thread): 52.40 mm
+ID (w/ thread): 50.60 mm
+OD: 54.50 mm</t>
+  </si>
+  <si>
+    <t>RM087.6</t>
+  </si>
+  <si>
+    <t>Screw 53mm Plain Black Cap LP H=14.00, OD=54.50, W=4.20</t>
+  </si>
+  <si>
+    <t>53MM BLACK SCREW CAP</t>
+  </si>
+  <si>
+    <t>Procured from RITU PLASTICS
+This screw cap features a wad lock for an induction liner/wad.
+Height: 14.15 mm
+Weight: 4.24 gm
+ID (w/o thread): 52.45 mm
+ID (w/ thread): 50.62 mm
+OD: 54.50 mm</t>
+  </si>
+  <si>
+    <t>RM189.2</t>
+  </si>
+  <si>
+    <t>53mm Silver PET Wad, 51.55mm X 0.70mm</t>
+  </si>
+  <si>
+    <t>53MM PET INDUCTION WAD</t>
+  </si>
+  <si>
+    <t>To be used with:
+RM087.5 &amp; RM087.6
+Seal Dia.: 51.55 mm
+Thickness: 0.68 mm
+Weight: 0.90 gm</t>
   </si>
 </sst>
 </file>
@@ -8219,7 +8271,9 @@
       <alignment vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -8564,20 +8618,20 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{1830319C-9417-47AE-9107-B778F23861D8}" name="Table1" displayName="Table1" ref="A1:K545" totalsRowShown="0" headerRowDxfId="0" dataDxfId="15" headerRowBorderDxfId="13" tableBorderDxfId="14" totalsRowBorderDxfId="12">
-  <autoFilter ref="A1:K545" xr:uid="{1830319C-9417-47AE-9107-B778F23861D8}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{DC9902EA-C51C-44F7-A5A0-093160012CE8}" name="Table1" displayName="Table1" ref="A1:K548" totalsRowShown="0" headerRowDxfId="0" dataDxfId="15" headerRowBorderDxfId="13" tableBorderDxfId="14" totalsRowBorderDxfId="12">
+  <autoFilter ref="A1:K548" xr:uid="{DC9902EA-C51C-44F7-A5A0-093160012CE8}"/>
   <tableColumns count="11">
-    <tableColumn id="1" xr3:uid="{C5A021E0-45BA-4ED4-923D-9AECE517E903}" name="ID" dataDxfId="11"/>
-    <tableColumn id="2" xr3:uid="{205DA61C-F3FB-4412-9D43-AA0087F0D28F}" name="Status" dataDxfId="10"/>
-    <tableColumn id="3" xr3:uid="{2BFD3825-8061-45E2-9AE4-E806E3718ABB}" name="Material List::Material_Detail" dataDxfId="9"/>
-    <tableColumn id="4" xr3:uid="{347A3BD7-08A7-4950-82E1-5996624AB870}" name="Product_Code" dataDxfId="8"/>
-    <tableColumn id="5" xr3:uid="{A13D2F54-9290-46A4-BC05-C0BBD0D21574}" name="RM PM Product List 2::Product_Detail" dataDxfId="7"/>
-    <tableColumn id="6" xr3:uid="{40AC261D-4621-49F8-AD18-6177C552A164}" name="Item_Code" dataDxfId="6"/>
-    <tableColumn id="7" xr3:uid="{576C5F22-863A-4E9C-A460-06D3896D58A3}" name="Old_Item_Code" dataDxfId="5"/>
-    <tableColumn id="8" xr3:uid="{00617C07-3289-4C5C-904D-AB33DB377F0A}" name="Item_Name" dataDxfId="4"/>
-    <tableColumn id="9" xr3:uid="{684C0F31-F18A-4999-8CD9-35320391F821}" name="Item_Detail_by_Vendor" dataDxfId="3"/>
-    <tableColumn id="10" xr3:uid="{F860F7BC-E20A-4D22-86C9-B767ECFFB173}" name="Vendor List 2::Vendor_Name" dataDxfId="2"/>
-    <tableColumn id="11" xr3:uid="{FAC1FB00-8FFC-4993-97E7-371587FB7EC6}" name="Remarks" dataDxfId="1"/>
+    <tableColumn id="1" xr3:uid="{7490F8BC-9714-4C54-BB67-D6B73B4533F3}" name="ID" dataDxfId="11"/>
+    <tableColumn id="2" xr3:uid="{7AE6CBA6-4BF2-4762-8ED3-A920E4B0E73B}" name="Status" dataDxfId="10"/>
+    <tableColumn id="3" xr3:uid="{E1F998D9-5EEB-4AA9-9809-D6C255796CA0}" name="Material List::Material_Detail" dataDxfId="9"/>
+    <tableColumn id="4" xr3:uid="{CBB19B08-E329-490D-BDD4-55337C809F15}" name="Product_Code" dataDxfId="8"/>
+    <tableColumn id="5" xr3:uid="{E29E9C00-4751-405E-9C92-B625B97CC54F}" name="RM PM Product List 2::Product_Detail" dataDxfId="7"/>
+    <tableColumn id="6" xr3:uid="{860841A9-F8B2-4A1C-92EF-CB8EF51A38A7}" name="Item_Code" dataDxfId="6"/>
+    <tableColumn id="7" xr3:uid="{96AD8F8B-DAFA-4E0B-A332-29AAE39C4071}" name="Old_Item_Code" dataDxfId="5"/>
+    <tableColumn id="8" xr3:uid="{AD069BC0-2E1F-4634-8C58-FD547CE4B0F2}" name="Item_Name" dataDxfId="4"/>
+    <tableColumn id="9" xr3:uid="{3D25D03D-4E1A-47D2-9711-9356A10E57B4}" name="Item_Detail_by_Vendor" dataDxfId="3"/>
+    <tableColumn id="10" xr3:uid="{84169D8E-0651-42E3-89C8-8FAB3A9DAA08}" name="Vendor List 2::Vendor_Name" dataDxfId="2"/>
+    <tableColumn id="11" xr3:uid="{75A68619-730A-48E6-A090-18F3D633A23C}" name="Remarks" dataDxfId="1"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -8880,7 +8934,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:K545"/>
+  <dimension ref="A1:K548"/>
   <sheetFormatPr defaultColWidth="21.7109375" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.140625" bestFit="1" customWidth="1"/>
@@ -26709,38 +26763,137 @@
       </c>
     </row>
     <row r="545" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A545" s="9">
+      <c r="A545" s="4">
         <v>545</v>
       </c>
-      <c r="B545" s="10" t="s">
-        <v>11</v>
-      </c>
-      <c r="C545" s="10" t="s">
+      <c r="B545" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C545" s="5" t="s">
         <v>67</v>
       </c>
-      <c r="D545" s="10" t="s">
+      <c r="D545" s="5" t="s">
         <v>68</v>
       </c>
-      <c r="E545" s="10" t="s">
+      <c r="E545" s="5" t="s">
         <v>69</v>
       </c>
-      <c r="F545" s="10" t="s">
+      <c r="F545" s="5" t="s">
         <v>2504</v>
       </c>
-      <c r="G545" s="11"/>
-      <c r="H545" s="10" t="s">
+      <c r="G545" s="7"/>
+      <c r="H545" s="5" t="s">
         <v>2505</v>
       </c>
-      <c r="I545" s="10" t="s">
+      <c r="I545" s="5" t="s">
         <v>2506</v>
       </c>
-      <c r="J545" s="10" t="s">
+      <c r="J545" s="5" t="s">
         <v>104</v>
       </c>
-      <c r="K545" s="12"/>
+      <c r="K545" s="6"/>
+    </row>
+    <row r="546" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A546" s="4">
+        <v>546</v>
+      </c>
+      <c r="B546" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C546" s="5" t="s">
+        <v>1472</v>
+      </c>
+      <c r="D546" s="5" t="s">
+        <v>1575</v>
+      </c>
+      <c r="E546" s="5" t="s">
+        <v>1576</v>
+      </c>
+      <c r="F546" s="5" t="s">
+        <v>2507</v>
+      </c>
+      <c r="G546" s="7"/>
+      <c r="H546" s="5" t="s">
+        <v>2508</v>
+      </c>
+      <c r="I546" s="5" t="s">
+        <v>2509</v>
+      </c>
+      <c r="J546" s="5" t="s">
+        <v>1524</v>
+      </c>
+      <c r="K546" s="8" t="s">
+        <v>2510</v>
+      </c>
+    </row>
+    <row r="547" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A547" s="4">
+        <v>547</v>
+      </c>
+      <c r="B547" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C547" s="5" t="s">
+        <v>1472</v>
+      </c>
+      <c r="D547" s="5" t="s">
+        <v>1575</v>
+      </c>
+      <c r="E547" s="5" t="s">
+        <v>1576</v>
+      </c>
+      <c r="F547" s="5" t="s">
+        <v>2511</v>
+      </c>
+      <c r="G547" s="7"/>
+      <c r="H547" s="5" t="s">
+        <v>2512</v>
+      </c>
+      <c r="I547" s="5" t="s">
+        <v>2513</v>
+      </c>
+      <c r="J547" s="5" t="s">
+        <v>1524</v>
+      </c>
+      <c r="K547" s="8" t="s">
+        <v>2514</v>
+      </c>
+    </row>
+    <row r="548" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A548" s="9">
+        <v>548</v>
+      </c>
+      <c r="B548" s="10" t="s">
+        <v>11</v>
+      </c>
+      <c r="C548" s="10" t="s">
+        <v>765</v>
+      </c>
+      <c r="D548" s="10" t="s">
+        <v>1755</v>
+      </c>
+      <c r="E548" s="10" t="s">
+        <v>1756</v>
+      </c>
+      <c r="F548" s="10" t="s">
+        <v>2515</v>
+      </c>
+      <c r="G548" s="11"/>
+      <c r="H548" s="10" t="s">
+        <v>2516</v>
+      </c>
+      <c r="I548" s="10" t="s">
+        <v>2517</v>
+      </c>
+      <c r="J548" s="10" t="s">
+        <v>1524</v>
+      </c>
+      <c r="K548" s="12" t="s">
+        <v>2518</v>
+      </c>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="8TXEK1U+Mu4KjKf0quQGAcR8kH+pLjdbwPS1AhlMu/UVW096cfuD6fcj3O4JFi2R8Q6daQOzwjinCMk6cTWeSg==" saltValue="sVaMAd4BDOGN1povQxCU0g==" spinCount="100000" sheet="1" objects="1" scenarios="1" sort="0" autoFilter="0"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="Mhra6HIeZA1v2C7C5fqMLaX8Inuwp0m9/OvRp/Ld02qSMhHpYZjJ7e5PROtRtAGf0GwbMhbs3XBwWdfkRN1gyw==" saltValue="n57MPx1dGZYysEbzSPpofQ==" spinCount="100000" sheet="1" objects="1" scenarios="1" sort="0" autoFilter="0"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <tableParts count="1">
     <tablePart r:id="rId1"/>

--- a/RM.xlsx
+++ b/RM.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\FG &amp; RMPM LIST\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F1764060-4106-4DA8-BC55-46DF612EA311}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5FE8A54E-84C3-42BC-B0B6-B4F386CB77F4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4862" uniqueCount="2519">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4879" uniqueCount="2526">
   <si>
     <t>ID</t>
   </si>
@@ -5635,7 +5635,7 @@
     <t>Mist Pump 19mm Short Milky LP</t>
   </si>
   <si>
-    <t>Pipe Length= 19.4cm</t>
+    <t>Pipe Length= 126.50 mm</t>
   </si>
   <si>
     <t>RM205</t>
@@ -8032,10 +8032,10 @@
     <t>RM007.8</t>
   </si>
   <si>
-    <t>Amber (NB83-MON-0I BROWN 407592 23-0442)  Colour PET</t>
-  </si>
-  <si>
-    <t>NB83-MON-0I BROWN 407592 23-0442</t>
+    <t>Amber (NB83-M0N-0I BROWN 407592 23-0442)  Colour PET</t>
+  </si>
+  <si>
+    <t>NB83-M0N-0I BROWN 407592 23-0442</t>
   </si>
   <si>
     <t>RM087.5</t>
@@ -8088,6 +8088,33 @@
 Seal Dia.: 51.55 mm
 Thickness: 0.68 mm
 Weight: 0.90 gm</t>
+  </si>
+  <si>
+    <t>RM098.6</t>
+  </si>
+  <si>
+    <t>Mist Pump 19mm Short Milky XL-ND Tube LP</t>
+  </si>
+  <si>
+    <t>20MM WHITE MIST</t>
+  </si>
+  <si>
+    <t>Procured from RITU PLASTICS:
+Total Weight: 5.45 gm
+Pump + Overcap Weight: 5.08 gm
+Pipe Weight: 0.37 gm
+Pipe Length: 160.00 mm
+Pipe OD: 2.15 mm
+Dip Tube length is extra large, dia. is narrower than regular pumps..</t>
+  </si>
+  <si>
+    <t>RM202.8</t>
+  </si>
+  <si>
+    <t>PET Resin Recycled RPET B2B 080 IV  - 1100Kgs</t>
+  </si>
+  <si>
+    <t>PET RESIN CHIPS</t>
   </si>
 </sst>
 </file>
@@ -8271,9 +8298,7 @@
       <alignment vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1"/>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -8618,20 +8643,20 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{DC9902EA-C51C-44F7-A5A0-093160012CE8}" name="Table1" displayName="Table1" ref="A1:K548" totalsRowShown="0" headerRowDxfId="0" dataDxfId="15" headerRowBorderDxfId="13" tableBorderDxfId="14" totalsRowBorderDxfId="12">
-  <autoFilter ref="A1:K548" xr:uid="{DC9902EA-C51C-44F7-A5A0-093160012CE8}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{C623A0C7-0452-4FA7-ACFA-2343099BB6BA}" name="Table1" displayName="Table1" ref="A1:K550" totalsRowShown="0" headerRowDxfId="0" dataDxfId="15" headerRowBorderDxfId="13" tableBorderDxfId="14" totalsRowBorderDxfId="12">
+  <autoFilter ref="A1:K550" xr:uid="{C623A0C7-0452-4FA7-ACFA-2343099BB6BA}"/>
   <tableColumns count="11">
-    <tableColumn id="1" xr3:uid="{7490F8BC-9714-4C54-BB67-D6B73B4533F3}" name="ID" dataDxfId="11"/>
-    <tableColumn id="2" xr3:uid="{7AE6CBA6-4BF2-4762-8ED3-A920E4B0E73B}" name="Status" dataDxfId="10"/>
-    <tableColumn id="3" xr3:uid="{E1F998D9-5EEB-4AA9-9809-D6C255796CA0}" name="Material List::Material_Detail" dataDxfId="9"/>
-    <tableColumn id="4" xr3:uid="{CBB19B08-E329-490D-BDD4-55337C809F15}" name="Product_Code" dataDxfId="8"/>
-    <tableColumn id="5" xr3:uid="{E29E9C00-4751-405E-9C92-B625B97CC54F}" name="RM PM Product List 2::Product_Detail" dataDxfId="7"/>
-    <tableColumn id="6" xr3:uid="{860841A9-F8B2-4A1C-92EF-CB8EF51A38A7}" name="Item_Code" dataDxfId="6"/>
-    <tableColumn id="7" xr3:uid="{96AD8F8B-DAFA-4E0B-A332-29AAE39C4071}" name="Old_Item_Code" dataDxfId="5"/>
-    <tableColumn id="8" xr3:uid="{AD069BC0-2E1F-4634-8C58-FD547CE4B0F2}" name="Item_Name" dataDxfId="4"/>
-    <tableColumn id="9" xr3:uid="{3D25D03D-4E1A-47D2-9711-9356A10E57B4}" name="Item_Detail_by_Vendor" dataDxfId="3"/>
-    <tableColumn id="10" xr3:uid="{84169D8E-0651-42E3-89C8-8FAB3A9DAA08}" name="Vendor List 2::Vendor_Name" dataDxfId="2"/>
-    <tableColumn id="11" xr3:uid="{75A68619-730A-48E6-A090-18F3D633A23C}" name="Remarks" dataDxfId="1"/>
+    <tableColumn id="1" xr3:uid="{E2127E8A-184B-4531-985C-E85D24F86501}" name="ID" dataDxfId="11"/>
+    <tableColumn id="2" xr3:uid="{88A155D0-BF10-48AD-8F4A-7F9D2C01B4EC}" name="Status" dataDxfId="10"/>
+    <tableColumn id="3" xr3:uid="{1DB7F052-4DBF-4817-A95C-E58FEC6D70AE}" name="Material List::Material_Detail" dataDxfId="9"/>
+    <tableColumn id="4" xr3:uid="{CCEFC485-091A-4ACC-BC42-BE0BD1C3E403}" name="Product_Code" dataDxfId="8"/>
+    <tableColumn id="5" xr3:uid="{C4E9E881-40E7-4447-AFC0-29C34747C71D}" name="RM PM Product List 2::Product_Detail" dataDxfId="7"/>
+    <tableColumn id="6" xr3:uid="{A0299F15-EC2B-4433-B468-CCC6C7B5E5FA}" name="Item_Code" dataDxfId="6"/>
+    <tableColumn id="7" xr3:uid="{798394BA-A5D1-42E9-A326-44EA348C4F00}" name="Old_Item_Code" dataDxfId="5"/>
+    <tableColumn id="8" xr3:uid="{521C2471-C201-4D98-85BA-B7BB8B0661C5}" name="Item_Name" dataDxfId="4"/>
+    <tableColumn id="9" xr3:uid="{D33568F0-A200-4A3E-873D-FCA11FED0C5E}" name="Item_Detail_by_Vendor" dataDxfId="3"/>
+    <tableColumn id="10" xr3:uid="{16AC3A69-6F9F-40F8-AF98-FF697C76D81D}" name="Vendor List 2::Vendor_Name" dataDxfId="2"/>
+    <tableColumn id="11" xr3:uid="{2DE08438-63B2-49C0-B964-3978A67431E6}" name="Remarks" dataDxfId="1"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -8934,7 +8959,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:K548"/>
+  <dimension ref="A1:K550"/>
   <sheetFormatPr defaultColWidth="21.7109375" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.140625" bestFit="1" customWidth="1"/>
@@ -26860,40 +26885,104 @@
       </c>
     </row>
     <row r="548" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A548" s="9">
+      <c r="A548" s="4">
         <v>548</v>
       </c>
-      <c r="B548" s="10" t="s">
-        <v>11</v>
-      </c>
-      <c r="C548" s="10" t="s">
+      <c r="B548" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C548" s="5" t="s">
         <v>765</v>
       </c>
-      <c r="D548" s="10" t="s">
+      <c r="D548" s="5" t="s">
         <v>1755</v>
       </c>
-      <c r="E548" s="10" t="s">
+      <c r="E548" s="5" t="s">
         <v>1756</v>
       </c>
-      <c r="F548" s="10" t="s">
+      <c r="F548" s="5" t="s">
         <v>2515</v>
       </c>
-      <c r="G548" s="11"/>
-      <c r="H548" s="10" t="s">
+      <c r="G548" s="7"/>
+      <c r="H548" s="5" t="s">
         <v>2516</v>
       </c>
-      <c r="I548" s="10" t="s">
+      <c r="I548" s="5" t="s">
         <v>2517</v>
       </c>
-      <c r="J548" s="10" t="s">
+      <c r="J548" s="5" t="s">
         <v>1524</v>
       </c>
-      <c r="K548" s="12" t="s">
+      <c r="K548" s="8" t="s">
         <v>2518</v>
       </c>
     </row>
+    <row r="549" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A549" s="4">
+        <v>549</v>
+      </c>
+      <c r="B549" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C549" s="5" t="s">
+        <v>1472</v>
+      </c>
+      <c r="D549" s="5" t="s">
+        <v>1647</v>
+      </c>
+      <c r="E549" s="5" t="s">
+        <v>1648</v>
+      </c>
+      <c r="F549" s="5" t="s">
+        <v>2519</v>
+      </c>
+      <c r="G549" s="7"/>
+      <c r="H549" s="5" t="s">
+        <v>2520</v>
+      </c>
+      <c r="I549" s="5" t="s">
+        <v>2521</v>
+      </c>
+      <c r="J549" s="5" t="s">
+        <v>1524</v>
+      </c>
+      <c r="K549" s="8" t="s">
+        <v>2522</v>
+      </c>
+    </row>
+    <row r="550" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A550" s="9">
+        <v>550</v>
+      </c>
+      <c r="B550" s="10" t="s">
+        <v>11</v>
+      </c>
+      <c r="C550" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="D550" s="10" t="s">
+        <v>1827</v>
+      </c>
+      <c r="E550" s="10" t="s">
+        <v>1828</v>
+      </c>
+      <c r="F550" s="10" t="s">
+        <v>2523</v>
+      </c>
+      <c r="G550" s="11"/>
+      <c r="H550" s="10" t="s">
+        <v>2524</v>
+      </c>
+      <c r="I550" s="10" t="s">
+        <v>2525</v>
+      </c>
+      <c r="J550" s="10" t="s">
+        <v>555</v>
+      </c>
+      <c r="K550" s="12"/>
+    </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="Mhra6HIeZA1v2C7C5fqMLaX8Inuwp0m9/OvRp/Ld02qSMhHpYZjJ7e5PROtRtAGf0GwbMhbs3XBwWdfkRN1gyw==" saltValue="n57MPx1dGZYysEbzSPpofQ==" spinCount="100000" sheet="1" objects="1" scenarios="1" sort="0" autoFilter="0"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="0ad3LqVbpEGZ/INUH1N97M0KM5i8hCmEH46nvA7cBu7xE2bYFrNYmWoKWM3H0lZ4dgvp5If5Iom9v9F3i1htxw==" saltValue="LsSqe1DYO0vcs7dt+t35nQ==" spinCount="100000" sheet="1" objects="1" scenarios="1" sort="0" autoFilter="0"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <tableParts count="1">
     <tablePart r:id="rId1"/>

--- a/RM.xlsx
+++ b/RM.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\FG &amp; RMPM LIST\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5FE8A54E-84C3-42BC-B0B6-B4F386CB77F4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5DDD2934-3062-4E58-9C29-BC955F4534EC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4879" uniqueCount="2526">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4903" uniqueCount="2536">
   <si>
     <t>ID</t>
   </si>
@@ -8115,6 +8115,36 @@
   </si>
   <si>
     <t>PET RESIN CHIPS</t>
+  </si>
+  <si>
+    <t>RM008.3</t>
+  </si>
+  <si>
+    <t>SCJ Nice TR Red 5115333529 PET</t>
+  </si>
+  <si>
+    <t>5115333529 PET RED</t>
+  </si>
+  <si>
+    <t>SCJ Masterbatches Pvt. Ltd.</t>
+  </si>
+  <si>
+    <t>RM010.3</t>
+  </si>
+  <si>
+    <t>SCJ Nice TR Yellow 2115314091 PET</t>
+  </si>
+  <si>
+    <t>2115314091 PET YELLOW</t>
+  </si>
+  <si>
+    <t>RM013.3</t>
+  </si>
+  <si>
+    <t>SCJ Nice TR PINK 8115334610 PET</t>
+  </si>
+  <si>
+    <t>8115334610 PET PINK</t>
   </si>
 </sst>
 </file>
@@ -8340,8 +8370,6 @@
       </border>
     </dxf>
     <dxf>
-      <numFmt numFmtId="30" formatCode="@"/>
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <border diagonalUp="0" diagonalDown="0">
         <left style="thin">
           <color indexed="64"/>
@@ -8643,20 +8671,20 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{C623A0C7-0452-4FA7-ACFA-2343099BB6BA}" name="Table1" displayName="Table1" ref="A1:K550" totalsRowShown="0" headerRowDxfId="0" dataDxfId="15" headerRowBorderDxfId="13" tableBorderDxfId="14" totalsRowBorderDxfId="12">
-  <autoFilter ref="A1:K550" xr:uid="{C623A0C7-0452-4FA7-ACFA-2343099BB6BA}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{5EF4CDBD-2741-4381-A6ED-5BA64E2DE130}" name="Table1" displayName="Table1" ref="A1:K553" totalsRowShown="0" headerRowDxfId="0" dataDxfId="15" headerRowBorderDxfId="13" tableBorderDxfId="14" totalsRowBorderDxfId="12">
+  <autoFilter ref="A1:K553" xr:uid="{5EF4CDBD-2741-4381-A6ED-5BA64E2DE130}"/>
   <tableColumns count="11">
-    <tableColumn id="1" xr3:uid="{E2127E8A-184B-4531-985C-E85D24F86501}" name="ID" dataDxfId="11"/>
-    <tableColumn id="2" xr3:uid="{88A155D0-BF10-48AD-8F4A-7F9D2C01B4EC}" name="Status" dataDxfId="10"/>
-    <tableColumn id="3" xr3:uid="{1DB7F052-4DBF-4817-A95C-E58FEC6D70AE}" name="Material List::Material_Detail" dataDxfId="9"/>
-    <tableColumn id="4" xr3:uid="{CCEFC485-091A-4ACC-BC42-BE0BD1C3E403}" name="Product_Code" dataDxfId="8"/>
-    <tableColumn id="5" xr3:uid="{C4E9E881-40E7-4447-AFC0-29C34747C71D}" name="RM PM Product List 2::Product_Detail" dataDxfId="7"/>
-    <tableColumn id="6" xr3:uid="{A0299F15-EC2B-4433-B468-CCC6C7B5E5FA}" name="Item_Code" dataDxfId="6"/>
-    <tableColumn id="7" xr3:uid="{798394BA-A5D1-42E9-A326-44EA348C4F00}" name="Old_Item_Code" dataDxfId="5"/>
-    <tableColumn id="8" xr3:uid="{521C2471-C201-4D98-85BA-B7BB8B0661C5}" name="Item_Name" dataDxfId="4"/>
-    <tableColumn id="9" xr3:uid="{D33568F0-A200-4A3E-873D-FCA11FED0C5E}" name="Item_Detail_by_Vendor" dataDxfId="3"/>
-    <tableColumn id="10" xr3:uid="{16AC3A69-6F9F-40F8-AF98-FF697C76D81D}" name="Vendor List 2::Vendor_Name" dataDxfId="2"/>
-    <tableColumn id="11" xr3:uid="{2DE08438-63B2-49C0-B964-3978A67431E6}" name="Remarks" dataDxfId="1"/>
+    <tableColumn id="1" xr3:uid="{82EAA91B-8C1E-4C71-BB4B-308AA86BB770}" name="ID" dataDxfId="11"/>
+    <tableColumn id="2" xr3:uid="{F764F742-028F-4C19-93E5-17ED7EDFC0C5}" name="Status" dataDxfId="10"/>
+    <tableColumn id="3" xr3:uid="{D31764ED-A362-4226-A00F-7C6521ADB3A8}" name="Material List::Material_Detail" dataDxfId="9"/>
+    <tableColumn id="4" xr3:uid="{2C3DBFA0-F620-4E8F-A570-F1A357066887}" name="Product_Code" dataDxfId="8"/>
+    <tableColumn id="5" xr3:uid="{D11B53A2-FF94-4D22-B6ED-FD141A44FBC3}" name="RM PM Product List 2::Product_Detail" dataDxfId="7"/>
+    <tableColumn id="6" xr3:uid="{A0F79D99-6051-443C-B340-FB847F066091}" name="Item_Code" dataDxfId="6"/>
+    <tableColumn id="7" xr3:uid="{47F1A256-C1DE-4D1B-B67C-83D3C1029A95}" name="Old_Item_Code" dataDxfId="5"/>
+    <tableColumn id="8" xr3:uid="{621CB3BE-E9AA-4B43-B627-E20E9B8FC794}" name="Item_Name" dataDxfId="4"/>
+    <tableColumn id="9" xr3:uid="{47DE0A5E-A3E2-40F2-AFE2-140485D41822}" name="Item_Detail_by_Vendor" dataDxfId="3"/>
+    <tableColumn id="10" xr3:uid="{C81830D9-8A7C-4686-9F51-D6A6BEA3BFD3}" name="Vendor List 2::Vendor_Name" dataDxfId="2"/>
+    <tableColumn id="11" xr3:uid="{F1809FBB-B8E3-4309-AAE2-95D439997F5C}" name="Remarks" dataDxfId="1"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -8959,7 +8987,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:K550"/>
+  <dimension ref="A1:K553"/>
   <sheetFormatPr defaultColWidth="21.7109375" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.140625" bestFit="1" customWidth="1"/>
@@ -26951,38 +26979,131 @@
       </c>
     </row>
     <row r="550" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A550" s="9">
+      <c r="A550" s="4">
         <v>550</v>
       </c>
-      <c r="B550" s="10" t="s">
-        <v>11</v>
-      </c>
-      <c r="C550" s="10" t="s">
+      <c r="B550" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C550" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="D550" s="10" t="s">
+      <c r="D550" s="5" t="s">
         <v>1827</v>
       </c>
-      <c r="E550" s="10" t="s">
+      <c r="E550" s="5" t="s">
         <v>1828</v>
       </c>
-      <c r="F550" s="10" t="s">
+      <c r="F550" s="5" t="s">
         <v>2523</v>
       </c>
-      <c r="G550" s="11"/>
-      <c r="H550" s="10" t="s">
+      <c r="G550" s="7"/>
+      <c r="H550" s="5" t="s">
         <v>2524</v>
       </c>
-      <c r="I550" s="10" t="s">
+      <c r="I550" s="5" t="s">
         <v>2525</v>
       </c>
-      <c r="J550" s="10" t="s">
+      <c r="J550" s="5" t="s">
         <v>555</v>
       </c>
-      <c r="K550" s="12"/>
+      <c r="K550" s="6"/>
+    </row>
+    <row r="551" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A551" s="4">
+        <v>551</v>
+      </c>
+      <c r="B551" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C551" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="D551" s="5" t="s">
+        <v>105</v>
+      </c>
+      <c r="E551" s="5" t="s">
+        <v>106</v>
+      </c>
+      <c r="F551" s="5" t="s">
+        <v>2526</v>
+      </c>
+      <c r="G551" s="7"/>
+      <c r="H551" s="5" t="s">
+        <v>2527</v>
+      </c>
+      <c r="I551" s="5" t="s">
+        <v>2528</v>
+      </c>
+      <c r="J551" s="5" t="s">
+        <v>2529</v>
+      </c>
+      <c r="K551" s="6"/>
+    </row>
+    <row r="552" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A552" s="4">
+        <v>552</v>
+      </c>
+      <c r="B552" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C552" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="D552" s="5" t="s">
+        <v>81</v>
+      </c>
+      <c r="E552" s="5" t="s">
+        <v>82</v>
+      </c>
+      <c r="F552" s="5" t="s">
+        <v>2530</v>
+      </c>
+      <c r="G552" s="7"/>
+      <c r="H552" s="5" t="s">
+        <v>2531</v>
+      </c>
+      <c r="I552" s="5" t="s">
+        <v>2532</v>
+      </c>
+      <c r="J552" s="5" t="s">
+        <v>2529</v>
+      </c>
+      <c r="K552" s="6"/>
+    </row>
+    <row r="553" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A553" s="9">
+        <v>553</v>
+      </c>
+      <c r="B553" s="10" t="s">
+        <v>11</v>
+      </c>
+      <c r="C553" s="10" t="s">
+        <v>67</v>
+      </c>
+      <c r="D553" s="10" t="s">
+        <v>75</v>
+      </c>
+      <c r="E553" s="10" t="s">
+        <v>76</v>
+      </c>
+      <c r="F553" s="10" t="s">
+        <v>2533</v>
+      </c>
+      <c r="G553" s="11"/>
+      <c r="H553" s="10" t="s">
+        <v>2534</v>
+      </c>
+      <c r="I553" s="10" t="s">
+        <v>2535</v>
+      </c>
+      <c r="J553" s="10" t="s">
+        <v>2529</v>
+      </c>
+      <c r="K553" s="12"/>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="0ad3LqVbpEGZ/INUH1N97M0KM5i8hCmEH46nvA7cBu7xE2bYFrNYmWoKWM3H0lZ4dgvp5If5Iom9v9F3i1htxw==" saltValue="LsSqe1DYO0vcs7dt+t35nQ==" spinCount="100000" sheet="1" objects="1" scenarios="1" sort="0" autoFilter="0"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="YPcyN4liITtShvb6Xn6+yHx7Bx8Ivs7lksJfALbJY/4ojXePeNnT2exLoiGUNofh5maUkkr/34GWf1mDpWjB5A==" saltValue="PbntFgwcxC+M6dQsJLQIzw==" spinCount="100000" sheet="1" objects="1" scenarios="1" sort="0" autoFilter="0"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <tableParts count="1">
     <tablePart r:id="rId1"/>

--- a/RM.xlsx
+++ b/RM.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\FG &amp; RMPM LIST\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5DDD2934-3062-4E58-9C29-BC955F4534EC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3EFDA854-53E2-484A-8230-3E3CFD1B4542}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4903" uniqueCount="2536">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4909" uniqueCount="2539">
   <si>
     <t>ID</t>
   </si>
@@ -7502,7 +7502,7 @@
     <t>RM258</t>
   </si>
   <si>
-    <t>Micro Spray Pump 19mm H=59.00, OD=23.50, W=5.00</t>
+    <t>Micro Spray Pump 19mm H=59 - 63, OD=23.50, W=5.00</t>
   </si>
   <si>
     <t>RM258.1</t>
@@ -8145,6 +8145,31 @@
   </si>
   <si>
     <t>8115334610 PET PINK</t>
+  </si>
+  <si>
+    <t>RM258.2</t>
+  </si>
+  <si>
+    <t>Micro Spray Pump 19mm Milky 20/415 Short Tube Broad Pipe</t>
+  </si>
+  <si>
+    <t>To be procured:
+Codification done (on basis of samples) for PO purpose..
+Pump:
+Height: 62.80 mm
+OD: 22.90 mm
+Weight: 5.43 gm
+Lock:
+Weight: 1.40 gm
+Nozzle Cover ID: 7.75 mm
+Pipe:
+Length: 95.20 mm
+OD: 3.80 mm
+ID: 2.70 mm
+Weight: 0.53 gm
+Total Length: 151.00 mm
+Thread Depth (fr. mouth to thread end):
+6.20 mm</t>
   </si>
 </sst>
 </file>
@@ -8324,11 +8349,13 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -8671,20 +8698,20 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{5EF4CDBD-2741-4381-A6ED-5BA64E2DE130}" name="Table1" displayName="Table1" ref="A1:K553" totalsRowShown="0" headerRowDxfId="0" dataDxfId="15" headerRowBorderDxfId="13" tableBorderDxfId="14" totalsRowBorderDxfId="12">
-  <autoFilter ref="A1:K553" xr:uid="{5EF4CDBD-2741-4381-A6ED-5BA64E2DE130}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{E3EC2198-B98B-479D-8117-5EACD13C306C}" name="Table1" displayName="Table1" ref="A1:K554" totalsRowShown="0" headerRowDxfId="0" dataDxfId="15" headerRowBorderDxfId="13" tableBorderDxfId="14" totalsRowBorderDxfId="12">
+  <autoFilter ref="A1:K554" xr:uid="{E3EC2198-B98B-479D-8117-5EACD13C306C}"/>
   <tableColumns count="11">
-    <tableColumn id="1" xr3:uid="{82EAA91B-8C1E-4C71-BB4B-308AA86BB770}" name="ID" dataDxfId="11"/>
-    <tableColumn id="2" xr3:uid="{F764F742-028F-4C19-93E5-17ED7EDFC0C5}" name="Status" dataDxfId="10"/>
-    <tableColumn id="3" xr3:uid="{D31764ED-A362-4226-A00F-7C6521ADB3A8}" name="Material List::Material_Detail" dataDxfId="9"/>
-    <tableColumn id="4" xr3:uid="{2C3DBFA0-F620-4E8F-A570-F1A357066887}" name="Product_Code" dataDxfId="8"/>
-    <tableColumn id="5" xr3:uid="{D11B53A2-FF94-4D22-B6ED-FD141A44FBC3}" name="RM PM Product List 2::Product_Detail" dataDxfId="7"/>
-    <tableColumn id="6" xr3:uid="{A0F79D99-6051-443C-B340-FB847F066091}" name="Item_Code" dataDxfId="6"/>
-    <tableColumn id="7" xr3:uid="{47F1A256-C1DE-4D1B-B67C-83D3C1029A95}" name="Old_Item_Code" dataDxfId="5"/>
-    <tableColumn id="8" xr3:uid="{621CB3BE-E9AA-4B43-B627-E20E9B8FC794}" name="Item_Name" dataDxfId="4"/>
-    <tableColumn id="9" xr3:uid="{47DE0A5E-A3E2-40F2-AFE2-140485D41822}" name="Item_Detail_by_Vendor" dataDxfId="3"/>
-    <tableColumn id="10" xr3:uid="{C81830D9-8A7C-4686-9F51-D6A6BEA3BFD3}" name="Vendor List 2::Vendor_Name" dataDxfId="2"/>
-    <tableColumn id="11" xr3:uid="{F1809FBB-B8E3-4309-AAE2-95D439997F5C}" name="Remarks" dataDxfId="1"/>
+    <tableColumn id="1" xr3:uid="{EA3AFE59-5BB0-4C77-8125-4A7796089D08}" name="ID" dataDxfId="11"/>
+    <tableColumn id="2" xr3:uid="{AD42EEDC-21EF-46F7-AE51-E8DDFD8C2A91}" name="Status" dataDxfId="10"/>
+    <tableColumn id="3" xr3:uid="{09E54D83-3B31-454B-921F-AA313256F549}" name="Material List::Material_Detail" dataDxfId="9"/>
+    <tableColumn id="4" xr3:uid="{D0800342-E8E9-4C91-9569-A14036D294B2}" name="Product_Code" dataDxfId="8"/>
+    <tableColumn id="5" xr3:uid="{B7988290-172E-4925-8036-279EB0B0B23C}" name="RM PM Product List 2::Product_Detail" dataDxfId="7"/>
+    <tableColumn id="6" xr3:uid="{44624E5F-71D5-4562-9469-43F092240E35}" name="Item_Code" dataDxfId="6"/>
+    <tableColumn id="7" xr3:uid="{3CC2F0C9-4230-46E2-BC61-8AA19CE49811}" name="Old_Item_Code" dataDxfId="5"/>
+    <tableColumn id="8" xr3:uid="{0C46B6E3-99B0-4BD0-860B-65BD924AF7FB}" name="Item_Name" dataDxfId="4"/>
+    <tableColumn id="9" xr3:uid="{898ECF9F-F503-4095-825F-4EF326E68EA7}" name="Item_Detail_by_Vendor" dataDxfId="3"/>
+    <tableColumn id="10" xr3:uid="{85B3FDB9-4328-4190-988B-792D69F2C5B0}" name="Vendor List 2::Vendor_Name" dataDxfId="2"/>
+    <tableColumn id="11" xr3:uid="{80ADA55B-1D1B-4192-9FC9-DFAEB8764C98}" name="Remarks" dataDxfId="1"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -8987,7 +9014,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:K553"/>
+  <dimension ref="A1:K554"/>
   <sheetFormatPr defaultColWidth="21.7109375" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.140625" bestFit="1" customWidth="1"/>
@@ -27072,38 +27099,65 @@
       <c r="K552" s="6"/>
     </row>
     <row r="553" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A553" s="9">
+      <c r="A553" s="4">
         <v>553</v>
       </c>
-      <c r="B553" s="10" t="s">
-        <v>11</v>
-      </c>
-      <c r="C553" s="10" t="s">
+      <c r="B553" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C553" s="5" t="s">
         <v>67</v>
       </c>
-      <c r="D553" s="10" t="s">
+      <c r="D553" s="5" t="s">
         <v>75</v>
       </c>
-      <c r="E553" s="10" t="s">
+      <c r="E553" s="5" t="s">
         <v>76</v>
       </c>
-      <c r="F553" s="10" t="s">
+      <c r="F553" s="5" t="s">
         <v>2533</v>
       </c>
-      <c r="G553" s="11"/>
-      <c r="H553" s="10" t="s">
+      <c r="G553" s="7"/>
+      <c r="H553" s="5" t="s">
         <v>2534</v>
       </c>
-      <c r="I553" s="10" t="s">
+      <c r="I553" s="5" t="s">
         <v>2535</v>
       </c>
-      <c r="J553" s="10" t="s">
+      <c r="J553" s="5" t="s">
         <v>2529</v>
       </c>
-      <c r="K553" s="12"/>
+      <c r="K553" s="6"/>
+    </row>
+    <row r="554" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A554" s="9">
+        <v>554</v>
+      </c>
+      <c r="B554" s="10"/>
+      <c r="C554" s="11" t="s">
+        <v>1472</v>
+      </c>
+      <c r="D554" s="11" t="s">
+        <v>2363</v>
+      </c>
+      <c r="E554" s="11" t="s">
+        <v>2364</v>
+      </c>
+      <c r="F554" s="11" t="s">
+        <v>2536</v>
+      </c>
+      <c r="G554" s="10"/>
+      <c r="H554" s="11" t="s">
+        <v>2537</v>
+      </c>
+      <c r="I554" s="10"/>
+      <c r="J554" s="10"/>
+      <c r="K554" s="12" t="s">
+        <v>2538</v>
+      </c>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="YPcyN4liITtShvb6Xn6+yHx7Bx8Ivs7lksJfALbJY/4ojXePeNnT2exLoiGUNofh5maUkkr/34GWf1mDpWjB5A==" saltValue="PbntFgwcxC+M6dQsJLQIzw==" spinCount="100000" sheet="1" objects="1" scenarios="1" sort="0" autoFilter="0"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="JWGJNqi8VkThRjA0ImB2mXBXfktNPHS+4Z4u3s4HcdV+jzs0zFSoW/oI7CcJDaw9Y1pWaVFUYrj1I/hWpX9lEA==" saltValue="99YPCLwdL0XY1d3euyE1qA==" spinCount="100000" sheet="1" objects="1" scenarios="1" sort="0" autoFilter="0"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <tableParts count="1">
     <tablePart r:id="rId1"/>

--- a/RM.xlsx
+++ b/RM.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\FG &amp; RMPM LIST\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3EFDA854-53E2-484A-8230-3E3CFD1B4542}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{069B8BF7-463C-4E5E-881B-7A3D3F8DDFB3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4909" uniqueCount="2539">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4911" uniqueCount="2540">
   <si>
     <t>ID</t>
   </si>
@@ -8150,7 +8150,10 @@
     <t>RM258.2</t>
   </si>
   <si>
-    <t>Micro Spray Pump 19mm Milky 20/415 Short Tube Broad Pipe</t>
+    <t>Micro Spray Pump 19mm Milky 20/410 Short Tube Broad Pipe</t>
+  </si>
+  <si>
+    <t>JL-A293 20/410 Plastic Sprayer White</t>
   </si>
   <si>
     <t>To be procured:
@@ -8698,20 +8701,20 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{E3EC2198-B98B-479D-8117-5EACD13C306C}" name="Table1" displayName="Table1" ref="A1:K554" totalsRowShown="0" headerRowDxfId="0" dataDxfId="15" headerRowBorderDxfId="13" tableBorderDxfId="14" totalsRowBorderDxfId="12">
-  <autoFilter ref="A1:K554" xr:uid="{E3EC2198-B98B-479D-8117-5EACD13C306C}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{BF390089-4454-4B6C-97FC-E5967AEB7E19}" name="Table1" displayName="Table1" ref="A1:K554" totalsRowShown="0" headerRowDxfId="0" dataDxfId="15" headerRowBorderDxfId="13" tableBorderDxfId="14" totalsRowBorderDxfId="12">
+  <autoFilter ref="A1:K554" xr:uid="{BF390089-4454-4B6C-97FC-E5967AEB7E19}"/>
   <tableColumns count="11">
-    <tableColumn id="1" xr3:uid="{EA3AFE59-5BB0-4C77-8125-4A7796089D08}" name="ID" dataDxfId="11"/>
-    <tableColumn id="2" xr3:uid="{AD42EEDC-21EF-46F7-AE51-E8DDFD8C2A91}" name="Status" dataDxfId="10"/>
-    <tableColumn id="3" xr3:uid="{09E54D83-3B31-454B-921F-AA313256F549}" name="Material List::Material_Detail" dataDxfId="9"/>
-    <tableColumn id="4" xr3:uid="{D0800342-E8E9-4C91-9569-A14036D294B2}" name="Product_Code" dataDxfId="8"/>
-    <tableColumn id="5" xr3:uid="{B7988290-172E-4925-8036-279EB0B0B23C}" name="RM PM Product List 2::Product_Detail" dataDxfId="7"/>
-    <tableColumn id="6" xr3:uid="{44624E5F-71D5-4562-9469-43F092240E35}" name="Item_Code" dataDxfId="6"/>
-    <tableColumn id="7" xr3:uid="{3CC2F0C9-4230-46E2-BC61-8AA19CE49811}" name="Old_Item_Code" dataDxfId="5"/>
-    <tableColumn id="8" xr3:uid="{0C46B6E3-99B0-4BD0-860B-65BD924AF7FB}" name="Item_Name" dataDxfId="4"/>
-    <tableColumn id="9" xr3:uid="{898ECF9F-F503-4095-825F-4EF326E68EA7}" name="Item_Detail_by_Vendor" dataDxfId="3"/>
-    <tableColumn id="10" xr3:uid="{85B3FDB9-4328-4190-988B-792D69F2C5B0}" name="Vendor List 2::Vendor_Name" dataDxfId="2"/>
-    <tableColumn id="11" xr3:uid="{80ADA55B-1D1B-4192-9FC9-DFAEB8764C98}" name="Remarks" dataDxfId="1"/>
+    <tableColumn id="1" xr3:uid="{8BA5CF18-411F-42BC-AEB9-E45C7EE09EA5}" name="ID" dataDxfId="11"/>
+    <tableColumn id="2" xr3:uid="{EB618F5A-A87F-47C8-AA50-4936625746C3}" name="Status" dataDxfId="10"/>
+    <tableColumn id="3" xr3:uid="{98529247-6C02-4EA6-B84A-BA1294ED2B18}" name="Material List::Material_Detail" dataDxfId="9"/>
+    <tableColumn id="4" xr3:uid="{84F6CF45-4BA3-4AD7-BDA8-D82AC8D9ADF8}" name="Product_Code" dataDxfId="8"/>
+    <tableColumn id="5" xr3:uid="{A564C5BC-6270-421E-9942-F51A5B04BC93}" name="RM PM Product List 2::Product_Detail" dataDxfId="7"/>
+    <tableColumn id="6" xr3:uid="{6948DCD0-72B6-4F86-8509-A8F0670AA130}" name="Item_Code" dataDxfId="6"/>
+    <tableColumn id="7" xr3:uid="{52CC81C7-BACC-4202-A5F5-21631C4D6032}" name="Old_Item_Code" dataDxfId="5"/>
+    <tableColumn id="8" xr3:uid="{EDF32E78-EFD1-4376-8600-791202D965F7}" name="Item_Name" dataDxfId="4"/>
+    <tableColumn id="9" xr3:uid="{7F7A6741-8447-4562-9BC2-8466D7ED6934}" name="Item_Detail_by_Vendor" dataDxfId="3"/>
+    <tableColumn id="10" xr3:uid="{04E7C606-80DD-4C34-9962-6989F35A580C}" name="Vendor List 2::Vendor_Name" dataDxfId="2"/>
+    <tableColumn id="11" xr3:uid="{CBBF0F75-6177-42AD-8159-0FFF57A2A6FB}" name="Remarks" dataDxfId="1"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -27150,14 +27153,18 @@
       <c r="H554" s="11" t="s">
         <v>2537</v>
       </c>
-      <c r="I554" s="10"/>
-      <c r="J554" s="10"/>
+      <c r="I554" s="11" t="s">
+        <v>2538</v>
+      </c>
+      <c r="J554" s="11" t="s">
+        <v>2367</v>
+      </c>
       <c r="K554" s="12" t="s">
-        <v>2538</v>
+        <v>2539</v>
       </c>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="JWGJNqi8VkThRjA0ImB2mXBXfktNPHS+4Z4u3s4HcdV+jzs0zFSoW/oI7CcJDaw9Y1pWaVFUYrj1I/hWpX9lEA==" saltValue="99YPCLwdL0XY1d3euyE1qA==" spinCount="100000" sheet="1" objects="1" scenarios="1" sort="0" autoFilter="0"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="OaElohfNMtKYqImKCH9d366+Oq7/7aN4YDNHFG+LUxMsnaVW3ey78m1Q2yFs93dMzIHS73aOfP7JjnpmRZXw0Q==" saltValue="lP4Va5ni1/88NdEqJ0075Q==" spinCount="100000" sheet="1" objects="1" scenarios="1" sort="0" autoFilter="0"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <tableParts count="1">
     <tablePart r:id="rId1"/>

--- a/RM.xlsx
+++ b/RM.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\FG &amp; RMPM LIST\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{069B8BF7-463C-4E5E-881B-7A3D3F8DDFB3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B7FC8B20-52CA-435C-B66A-C6F4EC9B202A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4911" uniqueCount="2540">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4919" uniqueCount="2543">
   <si>
     <t>ID</t>
   </si>
@@ -8173,6 +8173,15 @@
 Total Length: 151.00 mm
 Thread Depth (fr. mouth to thread end):
 6.20 mm</t>
+  </si>
+  <si>
+    <t>RM015.4</t>
+  </si>
+  <si>
+    <t>Renol BLACK NB93407096-MN Colour PET</t>
+  </si>
+  <si>
+    <t>NB93-M0N-0B BLACK 407096 23-0629</t>
   </si>
 </sst>
 </file>
@@ -8352,13 +8361,11 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -8701,20 +8708,20 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{BF390089-4454-4B6C-97FC-E5967AEB7E19}" name="Table1" displayName="Table1" ref="A1:K554" totalsRowShown="0" headerRowDxfId="0" dataDxfId="15" headerRowBorderDxfId="13" tableBorderDxfId="14" totalsRowBorderDxfId="12">
-  <autoFilter ref="A1:K554" xr:uid="{BF390089-4454-4B6C-97FC-E5967AEB7E19}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{2F794530-73D2-4D79-A636-B43A35081188}" name="Table1" displayName="Table1" ref="A1:K555" totalsRowShown="0" headerRowDxfId="0" dataDxfId="15" headerRowBorderDxfId="13" tableBorderDxfId="14" totalsRowBorderDxfId="12">
+  <autoFilter ref="A1:K555" xr:uid="{2F794530-73D2-4D79-A636-B43A35081188}"/>
   <tableColumns count="11">
-    <tableColumn id="1" xr3:uid="{8BA5CF18-411F-42BC-AEB9-E45C7EE09EA5}" name="ID" dataDxfId="11"/>
-    <tableColumn id="2" xr3:uid="{EB618F5A-A87F-47C8-AA50-4936625746C3}" name="Status" dataDxfId="10"/>
-    <tableColumn id="3" xr3:uid="{98529247-6C02-4EA6-B84A-BA1294ED2B18}" name="Material List::Material_Detail" dataDxfId="9"/>
-    <tableColumn id="4" xr3:uid="{84F6CF45-4BA3-4AD7-BDA8-D82AC8D9ADF8}" name="Product_Code" dataDxfId="8"/>
-    <tableColumn id="5" xr3:uid="{A564C5BC-6270-421E-9942-F51A5B04BC93}" name="RM PM Product List 2::Product_Detail" dataDxfId="7"/>
-    <tableColumn id="6" xr3:uid="{6948DCD0-72B6-4F86-8509-A8F0670AA130}" name="Item_Code" dataDxfId="6"/>
-    <tableColumn id="7" xr3:uid="{52CC81C7-BACC-4202-A5F5-21631C4D6032}" name="Old_Item_Code" dataDxfId="5"/>
-    <tableColumn id="8" xr3:uid="{EDF32E78-EFD1-4376-8600-791202D965F7}" name="Item_Name" dataDxfId="4"/>
-    <tableColumn id="9" xr3:uid="{7F7A6741-8447-4562-9BC2-8466D7ED6934}" name="Item_Detail_by_Vendor" dataDxfId="3"/>
-    <tableColumn id="10" xr3:uid="{04E7C606-80DD-4C34-9962-6989F35A580C}" name="Vendor List 2::Vendor_Name" dataDxfId="2"/>
-    <tableColumn id="11" xr3:uid="{CBBF0F75-6177-42AD-8159-0FFF57A2A6FB}" name="Remarks" dataDxfId="1"/>
+    <tableColumn id="1" xr3:uid="{8DF184B9-7EC7-4A87-90F0-76329B878289}" name="ID" dataDxfId="11"/>
+    <tableColumn id="2" xr3:uid="{B49F4738-DCD5-4FA5-8C50-9F47338651DE}" name="Status" dataDxfId="10"/>
+    <tableColumn id="3" xr3:uid="{EECCA0A1-30DB-4CCB-AF52-1A321EC551EC}" name="Material List::Material_Detail" dataDxfId="9"/>
+    <tableColumn id="4" xr3:uid="{3B336718-F8ED-434F-B3C0-7A2ECD03D46F}" name="Product_Code" dataDxfId="8"/>
+    <tableColumn id="5" xr3:uid="{53EF6FBF-3285-4F9B-8FC5-3A90B7980A7E}" name="RM PM Product List 2::Product_Detail" dataDxfId="7"/>
+    <tableColumn id="6" xr3:uid="{761B7DED-800C-40A3-98DE-7564A5F3730F}" name="Item_Code" dataDxfId="6"/>
+    <tableColumn id="7" xr3:uid="{988B58A1-D3BC-4563-90A6-B4BE2BFD6465}" name="Old_Item_Code" dataDxfId="5"/>
+    <tableColumn id="8" xr3:uid="{4B41C686-DF34-41D3-971F-0E20E0257CF2}" name="Item_Name" dataDxfId="4"/>
+    <tableColumn id="9" xr3:uid="{D0FA98FE-D248-4DAF-A4BD-166B35C49E13}" name="Item_Detail_by_Vendor" dataDxfId="3"/>
+    <tableColumn id="10" xr3:uid="{BC94AC55-2ED9-4E84-8B0A-5D496A914A6B}" name="Vendor List 2::Vendor_Name" dataDxfId="2"/>
+    <tableColumn id="11" xr3:uid="{64748745-57DE-4B62-814E-2AA47993BBEF}" name="Remarks" dataDxfId="1"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -9017,7 +9024,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:K554"/>
+  <dimension ref="A1:K555"/>
   <sheetFormatPr defaultColWidth="21.7109375" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.140625" bestFit="1" customWidth="1"/>
@@ -27133,38 +27140,69 @@
       <c r="K553" s="6"/>
     </row>
     <row r="554" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A554" s="9">
+      <c r="A554" s="4">
         <v>554</v>
       </c>
-      <c r="B554" s="10"/>
-      <c r="C554" s="11" t="s">
+      <c r="B554" s="7"/>
+      <c r="C554" s="5" t="s">
         <v>1472</v>
       </c>
-      <c r="D554" s="11" t="s">
+      <c r="D554" s="5" t="s">
         <v>2363</v>
       </c>
-      <c r="E554" s="11" t="s">
+      <c r="E554" s="5" t="s">
         <v>2364</v>
       </c>
-      <c r="F554" s="11" t="s">
+      <c r="F554" s="5" t="s">
         <v>2536</v>
       </c>
-      <c r="G554" s="10"/>
-      <c r="H554" s="11" t="s">
+      <c r="G554" s="7"/>
+      <c r="H554" s="5" t="s">
         <v>2537</v>
       </c>
-      <c r="I554" s="11" t="s">
+      <c r="I554" s="5" t="s">
         <v>2538</v>
       </c>
-      <c r="J554" s="11" t="s">
+      <c r="J554" s="5" t="s">
         <v>2367</v>
       </c>
-      <c r="K554" s="12" t="s">
+      <c r="K554" s="8" t="s">
         <v>2539</v>
       </c>
     </row>
+    <row r="555" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A555" s="9">
+        <v>555</v>
+      </c>
+      <c r="B555" s="10" t="s">
+        <v>11</v>
+      </c>
+      <c r="C555" s="10" t="s">
+        <v>67</v>
+      </c>
+      <c r="D555" s="10" t="s">
+        <v>163</v>
+      </c>
+      <c r="E555" s="10" t="s">
+        <v>164</v>
+      </c>
+      <c r="F555" s="10" t="s">
+        <v>2540</v>
+      </c>
+      <c r="G555" s="11"/>
+      <c r="H555" s="10" t="s">
+        <v>2541</v>
+      </c>
+      <c r="I555" s="10" t="s">
+        <v>2542</v>
+      </c>
+      <c r="J555" s="10" t="s">
+        <v>104</v>
+      </c>
+      <c r="K555" s="12"/>
+    </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="OaElohfNMtKYqImKCH9d366+Oq7/7aN4YDNHFG+LUxMsnaVW3ey78m1Q2yFs93dMzIHS73aOfP7JjnpmRZXw0Q==" saltValue="lP4Va5ni1/88NdEqJ0075Q==" spinCount="100000" sheet="1" objects="1" scenarios="1" sort="0" autoFilter="0"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="Iuf/o3ZQAdJBNv8Eee/WXqqwwi8WSdag47x3ofIic52qzodKHXsqGwO38oPl9ADSWsPKWpo2A5HaqTyDDiPQUw==" saltValue="xKOQg6tW9NM1Wl5GiUhzHQ==" spinCount="100000" sheet="1" objects="1" scenarios="1" sort="0" autoFilter="0"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <tableParts count="1">
     <tablePart r:id="rId1"/>

--- a/RM.xlsx
+++ b/RM.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\FG &amp; RMPM LIST\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\My Algos\My Apps\RmPmApp\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B7FC8B20-52CA-435C-B66A-C6F4EC9B202A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7F734E54-B150-4DCC-8727-788DBAB0A013}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -8371,41 +8371,6 @@
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="16">
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <alignment horizontal="center" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top/>
-        <bottom/>
-        <vertical style="thin">
-          <color indexed="64"/>
-        </vertical>
-        <horizontal style="thin">
-          <color indexed="64"/>
-        </horizontal>
-      </border>
-    </dxf>
     <dxf>
       <border diagonalUp="0" diagonalDown="0">
         <left style="thin">
@@ -8669,13 +8634,6 @@
       </border>
     </dxf>
     <dxf>
-      <border>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
       <border diagonalUp="0" diagonalDown="0">
         <left style="thin">
           <color indexed="64"/>
@@ -8694,6 +8652,48 @@
     <dxf>
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
+    <dxf>
+      <border>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="center" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top/>
+        <bottom/>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
@@ -8708,20 +8708,20 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{2F794530-73D2-4D79-A636-B43A35081188}" name="Table1" displayName="Table1" ref="A1:K555" totalsRowShown="0" headerRowDxfId="0" dataDxfId="15" headerRowBorderDxfId="13" tableBorderDxfId="14" totalsRowBorderDxfId="12">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{2F794530-73D2-4D79-A636-B43A35081188}" name="Table1" displayName="Table1" ref="A1:K555" totalsRowShown="0" headerRowDxfId="15" dataDxfId="13" headerRowBorderDxfId="14" tableBorderDxfId="12" totalsRowBorderDxfId="11">
   <autoFilter ref="A1:K555" xr:uid="{2F794530-73D2-4D79-A636-B43A35081188}"/>
   <tableColumns count="11">
-    <tableColumn id="1" xr3:uid="{8DF184B9-7EC7-4A87-90F0-76329B878289}" name="ID" dataDxfId="11"/>
-    <tableColumn id="2" xr3:uid="{B49F4738-DCD5-4FA5-8C50-9F47338651DE}" name="Status" dataDxfId="10"/>
-    <tableColumn id="3" xr3:uid="{EECCA0A1-30DB-4CCB-AF52-1A321EC551EC}" name="Material List::Material_Detail" dataDxfId="9"/>
-    <tableColumn id="4" xr3:uid="{3B336718-F8ED-434F-B3C0-7A2ECD03D46F}" name="Product_Code" dataDxfId="8"/>
-    <tableColumn id="5" xr3:uid="{53EF6FBF-3285-4F9B-8FC5-3A90B7980A7E}" name="RM PM Product List 2::Product_Detail" dataDxfId="7"/>
-    <tableColumn id="6" xr3:uid="{761B7DED-800C-40A3-98DE-7564A5F3730F}" name="Item_Code" dataDxfId="6"/>
-    <tableColumn id="7" xr3:uid="{988B58A1-D3BC-4563-90A6-B4BE2BFD6465}" name="Old_Item_Code" dataDxfId="5"/>
-    <tableColumn id="8" xr3:uid="{4B41C686-DF34-41D3-971F-0E20E0257CF2}" name="Item_Name" dataDxfId="4"/>
-    <tableColumn id="9" xr3:uid="{D0FA98FE-D248-4DAF-A4BD-166B35C49E13}" name="Item_Detail_by_Vendor" dataDxfId="3"/>
-    <tableColumn id="10" xr3:uid="{BC94AC55-2ED9-4E84-8B0A-5D496A914A6B}" name="Vendor List 2::Vendor_Name" dataDxfId="2"/>
-    <tableColumn id="11" xr3:uid="{64748745-57DE-4B62-814E-2AA47993BBEF}" name="Remarks" dataDxfId="1"/>
+    <tableColumn id="1" xr3:uid="{8DF184B9-7EC7-4A87-90F0-76329B878289}" name="ID" dataDxfId="10"/>
+    <tableColumn id="2" xr3:uid="{B49F4738-DCD5-4FA5-8C50-9F47338651DE}" name="Status" dataDxfId="9"/>
+    <tableColumn id="3" xr3:uid="{EECCA0A1-30DB-4CCB-AF52-1A321EC551EC}" name="Material List::Material_Detail" dataDxfId="8"/>
+    <tableColumn id="4" xr3:uid="{3B336718-F8ED-434F-B3C0-7A2ECD03D46F}" name="Product_Code" dataDxfId="7"/>
+    <tableColumn id="5" xr3:uid="{53EF6FBF-3285-4F9B-8FC5-3A90B7980A7E}" name="RM PM Product List 2::Product_Detail" dataDxfId="6"/>
+    <tableColumn id="6" xr3:uid="{761B7DED-800C-40A3-98DE-7564A5F3730F}" name="Item_Code" dataDxfId="5"/>
+    <tableColumn id="7" xr3:uid="{988B58A1-D3BC-4563-90A6-B4BE2BFD6465}" name="Old_Item_Code" dataDxfId="4"/>
+    <tableColumn id="8" xr3:uid="{4B41C686-DF34-41D3-971F-0E20E0257CF2}" name="Item_Name" dataDxfId="3"/>
+    <tableColumn id="9" xr3:uid="{D0FA98FE-D248-4DAF-A4BD-166B35C49E13}" name="Item_Detail_by_Vendor" dataDxfId="2"/>
+    <tableColumn id="10" xr3:uid="{BC94AC55-2ED9-4E84-8B0A-5D496A914A6B}" name="Vendor List 2::Vendor_Name" dataDxfId="1"/>
+    <tableColumn id="11" xr3:uid="{64748745-57DE-4B62-814E-2AA47993BBEF}" name="Remarks" dataDxfId="0"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -27202,7 +27202,7 @@
       <c r="K555" s="12"/>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="Iuf/o3ZQAdJBNv8Eee/WXqqwwi8WSdag47x3ofIic52qzodKHXsqGwO38oPl9ADSWsPKWpo2A5HaqTyDDiPQUw==" saltValue="xKOQg6tW9NM1Wl5GiUhzHQ==" spinCount="100000" sheet="1" objects="1" scenarios="1" sort="0" autoFilter="0"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="O+/sV4BeLitDd3N2CChQurjHWzlF96NdRD0trqSdNiSe/feIfy5/ClANr5iaoh2mtd4J6mncYg6X1xWCSleCtQ==" saltValue="ApdT06SDR0JSlXO5HKTZwg==" spinCount="100000" sheet="1" objects="1" scenarios="1" sort="0" autoFilter="0"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <tableParts count="1">
     <tablePart r:id="rId1"/>

--- a/RM.xlsx
+++ b/RM.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\My Algos\My Apps\RmPmApp\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7F734E54-B150-4DCC-8727-788DBAB0A013}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AD2E5B0C-AF4D-44A5-A5AE-8843D169D187}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -27202,7 +27202,7 @@
       <c r="K555" s="12"/>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="O+/sV4BeLitDd3N2CChQurjHWzlF96NdRD0trqSdNiSe/feIfy5/ClANr5iaoh2mtd4J6mncYg6X1xWCSleCtQ==" saltValue="ApdT06SDR0JSlXO5HKTZwg==" spinCount="100000" sheet="1" objects="1" scenarios="1" sort="0" autoFilter="0"/>
+  <sheetProtection sort="0" autoFilter="0"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <tableParts count="1">
     <tablePart r:id="rId1"/>

--- a/RM.xlsx
+++ b/RM.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\My Algos\My Apps\RmPmApp\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\FG &amp; RMPM LIST\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AD2E5B0C-AF4D-44A5-A5AE-8843D169D187}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{39EC97A0-D819-477D-B5E0-6ABEE0F4C277}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4919" uniqueCount="2543">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4928" uniqueCount="2549">
   <si>
     <t>ID</t>
   </si>
@@ -8182,6 +8182,31 @@
   </si>
   <si>
     <t>NB93-M0N-0B BLACK 407096 23-0629</t>
+  </si>
+  <si>
+    <t>RM270</t>
+  </si>
+  <si>
+    <t>63mm 4Layer DABUR TREE LOGO IN GREEN REV D PRINT IN GREEN PE Wad</t>
+  </si>
+  <si>
+    <t>RM270.1</t>
+  </si>
+  <si>
+    <t>Wad 62.05mm X 0.70mm SS108 025 DABUR TREE LOGO 4L 63mm HDPE</t>
+  </si>
+  <si>
+    <t>SS108 025 62.05MM DABUR TREE LOGO IN GREEN REV. D PRINT IN GREEN</t>
+  </si>
+  <si>
+    <t>4Layer PE Induction Wad:
+Seal Dia.: 62.05 +/- 0.10 mm
+Thickness: 0.70 +/- 0.10 mm
+Weight: 
+1. Heat Seal Layer: 0.038 mm
+2. Al. Foil: 0.025 mm
+3. Wax: 0.016 mm
+4. Board: 0.62 mm</t>
   </si>
 </sst>
 </file>
@@ -8365,12 +8390,49 @@
       <alignment vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="16">
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="center" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top/>
+        <bottom/>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
     <dxf>
       <border diagonalUp="0" diagonalDown="0">
         <left style="thin">
@@ -8634,6 +8696,13 @@
       </border>
     </dxf>
     <dxf>
+      <border>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
       <border diagonalUp="0" diagonalDown="0">
         <left style="thin">
           <color indexed="64"/>
@@ -8652,48 +8721,6 @@
     <dxf>
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
-    <dxf>
-      <border>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <alignment horizontal="center" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top/>
-        <bottom/>
-        <vertical style="thin">
-          <color indexed="64"/>
-        </vertical>
-        <horizontal style="thin">
-          <color indexed="64"/>
-        </horizontal>
-      </border>
-    </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
@@ -8708,20 +8735,20 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{2F794530-73D2-4D79-A636-B43A35081188}" name="Table1" displayName="Table1" ref="A1:K555" totalsRowShown="0" headerRowDxfId="15" dataDxfId="13" headerRowBorderDxfId="14" tableBorderDxfId="12" totalsRowBorderDxfId="11">
-  <autoFilter ref="A1:K555" xr:uid="{2F794530-73D2-4D79-A636-B43A35081188}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{5787C600-C201-42AC-A7E0-742D22149895}" name="Table1" displayName="Table1" ref="A1:K556" totalsRowShown="0" headerRowDxfId="0" dataDxfId="15" headerRowBorderDxfId="13" tableBorderDxfId="14" totalsRowBorderDxfId="12">
+  <autoFilter ref="A1:K556" xr:uid="{5787C600-C201-42AC-A7E0-742D22149895}"/>
   <tableColumns count="11">
-    <tableColumn id="1" xr3:uid="{8DF184B9-7EC7-4A87-90F0-76329B878289}" name="ID" dataDxfId="10"/>
-    <tableColumn id="2" xr3:uid="{B49F4738-DCD5-4FA5-8C50-9F47338651DE}" name="Status" dataDxfId="9"/>
-    <tableColumn id="3" xr3:uid="{EECCA0A1-30DB-4CCB-AF52-1A321EC551EC}" name="Material List::Material_Detail" dataDxfId="8"/>
-    <tableColumn id="4" xr3:uid="{3B336718-F8ED-434F-B3C0-7A2ECD03D46F}" name="Product_Code" dataDxfId="7"/>
-    <tableColumn id="5" xr3:uid="{53EF6FBF-3285-4F9B-8FC5-3A90B7980A7E}" name="RM PM Product List 2::Product_Detail" dataDxfId="6"/>
-    <tableColumn id="6" xr3:uid="{761B7DED-800C-40A3-98DE-7564A5F3730F}" name="Item_Code" dataDxfId="5"/>
-    <tableColumn id="7" xr3:uid="{988B58A1-D3BC-4563-90A6-B4BE2BFD6465}" name="Old_Item_Code" dataDxfId="4"/>
-    <tableColumn id="8" xr3:uid="{4B41C686-DF34-41D3-971F-0E20E0257CF2}" name="Item_Name" dataDxfId="3"/>
-    <tableColumn id="9" xr3:uid="{D0FA98FE-D248-4DAF-A4BD-166B35C49E13}" name="Item_Detail_by_Vendor" dataDxfId="2"/>
-    <tableColumn id="10" xr3:uid="{BC94AC55-2ED9-4E84-8B0A-5D496A914A6B}" name="Vendor List 2::Vendor_Name" dataDxfId="1"/>
-    <tableColumn id="11" xr3:uid="{64748745-57DE-4B62-814E-2AA47993BBEF}" name="Remarks" dataDxfId="0"/>
+    <tableColumn id="1" xr3:uid="{115625EE-1563-4817-B8F7-3CB54CCD79EC}" name="ID" dataDxfId="11"/>
+    <tableColumn id="2" xr3:uid="{F5F4939D-AC43-41B3-884B-14A4F48B9C41}" name="Status" dataDxfId="10"/>
+    <tableColumn id="3" xr3:uid="{9E385B08-91EB-4702-9549-D4E884E20A17}" name="Material List::Material_Detail" dataDxfId="9"/>
+    <tableColumn id="4" xr3:uid="{EDA95D6E-DCB9-4F20-9DB8-CCD4C6885B56}" name="Product_Code" dataDxfId="8"/>
+    <tableColumn id="5" xr3:uid="{D5411C1B-0BA0-4813-B22D-2E0E15C4886D}" name="RM PM Product List 2::Product_Detail" dataDxfId="7"/>
+    <tableColumn id="6" xr3:uid="{CF3500B3-AF29-4222-BA19-9C368ECAB635}" name="Item_Code" dataDxfId="6"/>
+    <tableColumn id="7" xr3:uid="{CEBD9434-5EB9-48C4-A989-5189E10ACD4E}" name="Old_Item_Code" dataDxfId="5"/>
+    <tableColumn id="8" xr3:uid="{DBB56731-786B-4648-AABC-64FB785DF2D1}" name="Item_Name" dataDxfId="4"/>
+    <tableColumn id="9" xr3:uid="{6C4E676C-5C2B-4AD9-91EC-745E8DF1C8BF}" name="Item_Detail_by_Vendor" dataDxfId="3"/>
+    <tableColumn id="10" xr3:uid="{ECB9B568-2DC8-49BE-8416-FC1486AE60FE}" name="Vendor List 2::Vendor_Name" dataDxfId="2"/>
+    <tableColumn id="11" xr3:uid="{15161AAF-EF51-4AA3-A8C6-4CB5C8C0B683}" name="Remarks" dataDxfId="1"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -9024,14 +9051,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:K555"/>
+  <dimension ref="A1:K556"/>
   <sheetFormatPr defaultColWidth="21.7109375" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.140625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="11.42578125" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="28.85546875" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="16.5703125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="58.42578125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="59.140625" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="14.140625" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="17.85546875" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="75" bestFit="1" customWidth="1"/>
@@ -27171,38 +27198,71 @@
       </c>
     </row>
     <row r="555" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A555" s="9">
+      <c r="A555" s="4">
         <v>555</v>
       </c>
-      <c r="B555" s="10" t="s">
-        <v>11</v>
-      </c>
-      <c r="C555" s="10" t="s">
+      <c r="B555" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C555" s="5" t="s">
         <v>67</v>
       </c>
-      <c r="D555" s="10" t="s">
+      <c r="D555" s="5" t="s">
         <v>163</v>
       </c>
-      <c r="E555" s="10" t="s">
+      <c r="E555" s="5" t="s">
         <v>164</v>
       </c>
-      <c r="F555" s="10" t="s">
+      <c r="F555" s="5" t="s">
         <v>2540</v>
       </c>
-      <c r="G555" s="11"/>
-      <c r="H555" s="10" t="s">
+      <c r="G555" s="7"/>
+      <c r="H555" s="5" t="s">
         <v>2541</v>
       </c>
-      <c r="I555" s="10" t="s">
+      <c r="I555" s="5" t="s">
         <v>2542</v>
       </c>
-      <c r="J555" s="10" t="s">
+      <c r="J555" s="5" t="s">
         <v>104</v>
       </c>
-      <c r="K555" s="12"/>
+      <c r="K555" s="6"/>
+    </row>
+    <row r="556" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A556" s="9">
+        <v>556</v>
+      </c>
+      <c r="B556" s="10" t="s">
+        <v>11</v>
+      </c>
+      <c r="C556" s="10" t="s">
+        <v>765</v>
+      </c>
+      <c r="D556" s="10" t="s">
+        <v>2543</v>
+      </c>
+      <c r="E556" s="10" t="s">
+        <v>2544</v>
+      </c>
+      <c r="F556" s="10" t="s">
+        <v>2545</v>
+      </c>
+      <c r="G556" s="11"/>
+      <c r="H556" s="10" t="s">
+        <v>2546</v>
+      </c>
+      <c r="I556" s="10" t="s">
+        <v>2547</v>
+      </c>
+      <c r="J556" s="10" t="s">
+        <v>785</v>
+      </c>
+      <c r="K556" s="12" t="s">
+        <v>2548</v>
+      </c>
     </row>
   </sheetData>
-  <sheetProtection sort="0" autoFilter="0"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="GhXBp6rOfcYCiV+L2MGXW9UQGssw/8mQM0MAUkt4YPZn/w9pd38RRtK6pC6AFEfWUm7sbBiqRyekqN+5zDG//w==" saltValue="xKTQriS5asMLkhfZ0ZCm7Q==" spinCount="100000" sheet="1" objects="1" scenarios="1" sort="0" autoFilter="0"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <tableParts count="1">
     <tablePart r:id="rId1"/>

--- a/RM.xlsx
+++ b/RM.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\FG &amp; RMPM LIST\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{39EC97A0-D819-477D-B5E0-6ABEE0F4C277}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{53C96E39-3796-4BA2-ADBF-C48B5FC2A5F4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4928" uniqueCount="2549">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4936" uniqueCount="2554">
   <si>
     <t>ID</t>
   </si>
@@ -8207,6 +8207,21 @@
 2. Al. Foil: 0.025 mm
 3. Wax: 0.016 mm
 4. Board: 0.62 mm</t>
+  </si>
+  <si>
+    <t>RM271</t>
+  </si>
+  <si>
+    <t>19mm Silver PET Wad</t>
+  </si>
+  <si>
+    <t>RM271.1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SGV 1203/080/Plain/19mm PET </t>
+  </si>
+  <si>
+    <t>To be procured:</t>
   </si>
 </sst>
 </file>
@@ -8386,10 +8401,10 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
@@ -8434,6 +8449,8 @@
       </border>
     </dxf>
     <dxf>
+      <numFmt numFmtId="30" formatCode="@"/>
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <border diagonalUp="0" diagonalDown="0">
         <left style="thin">
           <color indexed="64"/>
@@ -8735,20 +8752,20 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{5787C600-C201-42AC-A7E0-742D22149895}" name="Table1" displayName="Table1" ref="A1:K556" totalsRowShown="0" headerRowDxfId="0" dataDxfId="15" headerRowBorderDxfId="13" tableBorderDxfId="14" totalsRowBorderDxfId="12">
-  <autoFilter ref="A1:K556" xr:uid="{5787C600-C201-42AC-A7E0-742D22149895}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{EA218EF3-C7C5-4868-97A6-EBFF74AF29EA}" name="Table1" displayName="Table1" ref="A1:K557" totalsRowShown="0" headerRowDxfId="0" dataDxfId="15" headerRowBorderDxfId="13" tableBorderDxfId="14" totalsRowBorderDxfId="12">
+  <autoFilter ref="A1:K557" xr:uid="{EA218EF3-C7C5-4868-97A6-EBFF74AF29EA}"/>
   <tableColumns count="11">
-    <tableColumn id="1" xr3:uid="{115625EE-1563-4817-B8F7-3CB54CCD79EC}" name="ID" dataDxfId="11"/>
-    <tableColumn id="2" xr3:uid="{F5F4939D-AC43-41B3-884B-14A4F48B9C41}" name="Status" dataDxfId="10"/>
-    <tableColumn id="3" xr3:uid="{9E385B08-91EB-4702-9549-D4E884E20A17}" name="Material List::Material_Detail" dataDxfId="9"/>
-    <tableColumn id="4" xr3:uid="{EDA95D6E-DCB9-4F20-9DB8-CCD4C6885B56}" name="Product_Code" dataDxfId="8"/>
-    <tableColumn id="5" xr3:uid="{D5411C1B-0BA0-4813-B22D-2E0E15C4886D}" name="RM PM Product List 2::Product_Detail" dataDxfId="7"/>
-    <tableColumn id="6" xr3:uid="{CF3500B3-AF29-4222-BA19-9C368ECAB635}" name="Item_Code" dataDxfId="6"/>
-    <tableColumn id="7" xr3:uid="{CEBD9434-5EB9-48C4-A989-5189E10ACD4E}" name="Old_Item_Code" dataDxfId="5"/>
-    <tableColumn id="8" xr3:uid="{DBB56731-786B-4648-AABC-64FB785DF2D1}" name="Item_Name" dataDxfId="4"/>
-    <tableColumn id="9" xr3:uid="{6C4E676C-5C2B-4AD9-91EC-745E8DF1C8BF}" name="Item_Detail_by_Vendor" dataDxfId="3"/>
-    <tableColumn id="10" xr3:uid="{ECB9B568-2DC8-49BE-8416-FC1486AE60FE}" name="Vendor List 2::Vendor_Name" dataDxfId="2"/>
-    <tableColumn id="11" xr3:uid="{15161AAF-EF51-4AA3-A8C6-4CB5C8C0B683}" name="Remarks" dataDxfId="1"/>
+    <tableColumn id="1" xr3:uid="{FE3EA767-F1D1-46EC-858D-DA4BA36D91DF}" name="ID" dataDxfId="11"/>
+    <tableColumn id="2" xr3:uid="{12BB688A-B75D-4E43-8AB7-1B6F77D86350}" name="Status" dataDxfId="10"/>
+    <tableColumn id="3" xr3:uid="{B28C4F43-CECA-43F8-8A7A-C3AE2921AA93}" name="Material List::Material_Detail" dataDxfId="9"/>
+    <tableColumn id="4" xr3:uid="{6208D84B-EFC1-4EF5-A641-125578036C6C}" name="Product_Code" dataDxfId="8"/>
+    <tableColumn id="5" xr3:uid="{2D3C2076-234E-4330-A808-61F0CE63611C}" name="RM PM Product List 2::Product_Detail" dataDxfId="7"/>
+    <tableColumn id="6" xr3:uid="{79D9EC75-552C-4CF9-B77B-2BE0B2F04261}" name="Item_Code" dataDxfId="6"/>
+    <tableColumn id="7" xr3:uid="{BB16CD64-7FBA-4743-802F-F67193B3594A}" name="Old_Item_Code" dataDxfId="5"/>
+    <tableColumn id="8" xr3:uid="{1CD29457-B7A4-4A80-9B96-181289A75B45}" name="Item_Name" dataDxfId="4"/>
+    <tableColumn id="9" xr3:uid="{EC316AFE-789C-4397-9834-51DCC70650B9}" name="Item_Detail_by_Vendor" dataDxfId="3"/>
+    <tableColumn id="10" xr3:uid="{232F8EF1-8E11-414F-ADE3-C0D6CE1C7A24}" name="Vendor List 2::Vendor_Name" dataDxfId="2"/>
+    <tableColumn id="11" xr3:uid="{B1164C7B-872D-421D-A05F-AC19B8044A7A}" name="Remarks" dataDxfId="1"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -9051,7 +9068,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:K556"/>
+  <dimension ref="A1:K557"/>
   <sheetFormatPr defaultColWidth="21.7109375" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.140625" bestFit="1" customWidth="1"/>
@@ -27229,40 +27246,71 @@
       <c r="K555" s="6"/>
     </row>
     <row r="556" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A556" s="9">
+      <c r="A556" s="4">
         <v>556</v>
       </c>
-      <c r="B556" s="10" t="s">
-        <v>11</v>
-      </c>
-      <c r="C556" s="10" t="s">
+      <c r="B556" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C556" s="5" t="s">
         <v>765</v>
       </c>
-      <c r="D556" s="10" t="s">
+      <c r="D556" s="5" t="s">
         <v>2543</v>
       </c>
-      <c r="E556" s="10" t="s">
+      <c r="E556" s="5" t="s">
         <v>2544</v>
       </c>
-      <c r="F556" s="10" t="s">
+      <c r="F556" s="5" t="s">
         <v>2545</v>
       </c>
-      <c r="G556" s="11"/>
-      <c r="H556" s="10" t="s">
+      <c r="G556" s="7"/>
+      <c r="H556" s="5" t="s">
         <v>2546</v>
       </c>
-      <c r="I556" s="10" t="s">
+      <c r="I556" s="5" t="s">
         <v>2547</v>
       </c>
-      <c r="J556" s="10" t="s">
+      <c r="J556" s="5" t="s">
         <v>785</v>
       </c>
-      <c r="K556" s="12" t="s">
+      <c r="K556" s="8" t="s">
         <v>2548</v>
       </c>
     </row>
+    <row r="557" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A557" s="9">
+        <v>557</v>
+      </c>
+      <c r="B557" s="10"/>
+      <c r="C557" s="11" t="s">
+        <v>765</v>
+      </c>
+      <c r="D557" s="11" t="s">
+        <v>2549</v>
+      </c>
+      <c r="E557" s="11" t="s">
+        <v>2550</v>
+      </c>
+      <c r="F557" s="11" t="s">
+        <v>2551</v>
+      </c>
+      <c r="G557" s="10"/>
+      <c r="H557" s="11" t="s">
+        <v>2550</v>
+      </c>
+      <c r="I557" s="11" t="s">
+        <v>2552</v>
+      </c>
+      <c r="J557" s="11" t="s">
+        <v>797</v>
+      </c>
+      <c r="K557" s="12" t="s">
+        <v>2553</v>
+      </c>
+    </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="GhXBp6rOfcYCiV+L2MGXW9UQGssw/8mQM0MAUkt4YPZn/w9pd38RRtK6pC6AFEfWUm7sbBiqRyekqN+5zDG//w==" saltValue="xKTQriS5asMLkhfZ0ZCm7Q==" spinCount="100000" sheet="1" objects="1" scenarios="1" sort="0" autoFilter="0"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="6XenISJ9yIYEmE00XT+8hM600AvutmOry2hqLA6lsoe5vBMl18PlYOeB/FSq/DnywWpZv5ukslaGyJdh2d0wuQ==" saltValue="OElEAGSs71mQJrSUGJlvKA==" spinCount="100000" sheet="1" objects="1" scenarios="1" sort="0" autoFilter="0"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <tableParts count="1">
     <tablePart r:id="rId1"/>

--- a/RM.xlsx
+++ b/RM.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\FG &amp; RMPM LIST\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{53C96E39-3796-4BA2-ADBF-C48B5FC2A5F4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A34297E1-68BA-4269-85B9-66E8A65EBF34}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4936" uniqueCount="2554">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4945" uniqueCount="2560">
   <si>
     <t>ID</t>
   </si>
@@ -8222,6 +8222,32 @@
   </si>
   <si>
     <t>To be procured:</t>
+  </si>
+  <si>
+    <t>RM272</t>
+  </si>
+  <si>
+    <t>53mm Neck 29gm ROPP</t>
+  </si>
+  <si>
+    <t>RM272.1</t>
+  </si>
+  <si>
+    <t>Pet Preform 53mm 29gm ROPP Clear TPAC</t>
+  </si>
+  <si>
+    <t>PET Preform 29G 53MM SP400 NAT R 980 CB</t>
+  </si>
+  <si>
+    <t>Wall Thickness:  mm to mm
+Weight: 28.49 GM - 28.54 gm
+Height: 77.35 mm
+CRH: 13.45 mm
+ID: 47.30 mm
+OD w/ thread: 52.20 mm
+OD w/o thread: 49.80 mm
+OD (Head): 50.00 mm
+OD Neck Ring (Neck Size): 52.25 mm</t>
   </si>
 </sst>
 </file>
@@ -8401,10 +8427,10 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
@@ -8752,20 +8778,20 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{EA218EF3-C7C5-4868-97A6-EBFF74AF29EA}" name="Table1" displayName="Table1" ref="A1:K557" totalsRowShown="0" headerRowDxfId="0" dataDxfId="15" headerRowBorderDxfId="13" tableBorderDxfId="14" totalsRowBorderDxfId="12">
-  <autoFilter ref="A1:K557" xr:uid="{EA218EF3-C7C5-4868-97A6-EBFF74AF29EA}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{D991BE68-994E-4C3A-AD1A-D16C28ACEA8E}" name="Table1" displayName="Table1" ref="A1:K558" totalsRowShown="0" headerRowDxfId="0" dataDxfId="15" headerRowBorderDxfId="13" tableBorderDxfId="14" totalsRowBorderDxfId="12">
+  <autoFilter ref="A1:K558" xr:uid="{D991BE68-994E-4C3A-AD1A-D16C28ACEA8E}"/>
   <tableColumns count="11">
-    <tableColumn id="1" xr3:uid="{FE3EA767-F1D1-46EC-858D-DA4BA36D91DF}" name="ID" dataDxfId="11"/>
-    <tableColumn id="2" xr3:uid="{12BB688A-B75D-4E43-8AB7-1B6F77D86350}" name="Status" dataDxfId="10"/>
-    <tableColumn id="3" xr3:uid="{B28C4F43-CECA-43F8-8A7A-C3AE2921AA93}" name="Material List::Material_Detail" dataDxfId="9"/>
-    <tableColumn id="4" xr3:uid="{6208D84B-EFC1-4EF5-A641-125578036C6C}" name="Product_Code" dataDxfId="8"/>
-    <tableColumn id="5" xr3:uid="{2D3C2076-234E-4330-A808-61F0CE63611C}" name="RM PM Product List 2::Product_Detail" dataDxfId="7"/>
-    <tableColumn id="6" xr3:uid="{79D9EC75-552C-4CF9-B77B-2BE0B2F04261}" name="Item_Code" dataDxfId="6"/>
-    <tableColumn id="7" xr3:uid="{BB16CD64-7FBA-4743-802F-F67193B3594A}" name="Old_Item_Code" dataDxfId="5"/>
-    <tableColumn id="8" xr3:uid="{1CD29457-B7A4-4A80-9B96-181289A75B45}" name="Item_Name" dataDxfId="4"/>
-    <tableColumn id="9" xr3:uid="{EC316AFE-789C-4397-9834-51DCC70650B9}" name="Item_Detail_by_Vendor" dataDxfId="3"/>
-    <tableColumn id="10" xr3:uid="{232F8EF1-8E11-414F-ADE3-C0D6CE1C7A24}" name="Vendor List 2::Vendor_Name" dataDxfId="2"/>
-    <tableColumn id="11" xr3:uid="{B1164C7B-872D-421D-A05F-AC19B8044A7A}" name="Remarks" dataDxfId="1"/>
+    <tableColumn id="1" xr3:uid="{735891A2-2F05-4E9E-8810-7655801B4E44}" name="ID" dataDxfId="11"/>
+    <tableColumn id="2" xr3:uid="{B13B2CE0-ACA7-42C0-B377-F072717C3B38}" name="Status" dataDxfId="10"/>
+    <tableColumn id="3" xr3:uid="{773EEE8D-2081-4BBD-BEA7-C1575042BA66}" name="Material List::Material_Detail" dataDxfId="9"/>
+    <tableColumn id="4" xr3:uid="{B3F34587-82B7-458D-A0AE-EF40BE88A772}" name="Product_Code" dataDxfId="8"/>
+    <tableColumn id="5" xr3:uid="{BAED11DA-9131-46C7-B7A7-5BBCB0130A81}" name="RM PM Product List 2::Product_Detail" dataDxfId="7"/>
+    <tableColumn id="6" xr3:uid="{4B4C3402-6689-4591-9C39-C4B38407BBCD}" name="Item_Code" dataDxfId="6"/>
+    <tableColumn id="7" xr3:uid="{73AA5F1E-DCF2-4350-817A-30DD3E7A61C8}" name="Old_Item_Code" dataDxfId="5"/>
+    <tableColumn id="8" xr3:uid="{211F0F95-5996-4EF8-8DB9-6DAFC32B1201}" name="Item_Name" dataDxfId="4"/>
+    <tableColumn id="9" xr3:uid="{C1048881-69D2-4CBE-A993-8F20EE68108D}" name="Item_Detail_by_Vendor" dataDxfId="3"/>
+    <tableColumn id="10" xr3:uid="{F09007A0-2908-45EB-9579-8A28239FE555}" name="Vendor List 2::Vendor_Name" dataDxfId="2"/>
+    <tableColumn id="11" xr3:uid="{7669724A-D363-4F1B-9C27-2A5639E78838}" name="Remarks" dataDxfId="1"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -9068,7 +9094,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:K557"/>
+  <dimension ref="A1:K558"/>
   <sheetFormatPr defaultColWidth="21.7109375" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.140625" bestFit="1" customWidth="1"/>
@@ -27279,38 +27305,71 @@
       </c>
     </row>
     <row r="557" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A557" s="9">
+      <c r="A557" s="4">
         <v>557</v>
       </c>
-      <c r="B557" s="10"/>
-      <c r="C557" s="11" t="s">
+      <c r="B557" s="7"/>
+      <c r="C557" s="5" t="s">
         <v>765</v>
       </c>
-      <c r="D557" s="11" t="s">
+      <c r="D557" s="5" t="s">
         <v>2549</v>
       </c>
-      <c r="E557" s="11" t="s">
+      <c r="E557" s="5" t="s">
         <v>2550</v>
       </c>
-      <c r="F557" s="11" t="s">
+      <c r="F557" s="5" t="s">
         <v>2551</v>
       </c>
-      <c r="G557" s="10"/>
-      <c r="H557" s="11" t="s">
+      <c r="G557" s="7"/>
+      <c r="H557" s="5" t="s">
         <v>2550</v>
       </c>
-      <c r="I557" s="11" t="s">
+      <c r="I557" s="5" t="s">
         <v>2552</v>
       </c>
-      <c r="J557" s="11" t="s">
+      <c r="J557" s="5" t="s">
         <v>797</v>
       </c>
-      <c r="K557" s="12" t="s">
+      <c r="K557" s="8" t="s">
         <v>2553</v>
       </c>
     </row>
+    <row r="558" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A558" s="9">
+        <v>558</v>
+      </c>
+      <c r="B558" s="10" t="s">
+        <v>11</v>
+      </c>
+      <c r="C558" s="10" t="s">
+        <v>588</v>
+      </c>
+      <c r="D558" s="10" t="s">
+        <v>2554</v>
+      </c>
+      <c r="E558" s="10" t="s">
+        <v>2555</v>
+      </c>
+      <c r="F558" s="10" t="s">
+        <v>2556</v>
+      </c>
+      <c r="G558" s="11"/>
+      <c r="H558" s="10" t="s">
+        <v>2557</v>
+      </c>
+      <c r="I558" s="10" t="s">
+        <v>2558</v>
+      </c>
+      <c r="J558" s="10" t="s">
+        <v>641</v>
+      </c>
+      <c r="K558" s="12" t="s">
+        <v>2559</v>
+      </c>
+    </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="6XenISJ9yIYEmE00XT+8hM600AvutmOry2hqLA6lsoe5vBMl18PlYOeB/FSq/DnywWpZv5ukslaGyJdh2d0wuQ==" saltValue="OElEAGSs71mQJrSUGJlvKA==" spinCount="100000" sheet="1" objects="1" scenarios="1" sort="0" autoFilter="0"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="jhspqN817QB7Xl9plb3pxavq2iOXGkDKtbiqPfjz/ijYhjDwk1myGHB1uSwfdxelumSlrlyl08+Lj6RcFjmpfg==" saltValue="DigyCWFgMvr96XWL1Vk3sA==" spinCount="100000" sheet="1" objects="1" scenarios="1" sort="0" autoFilter="0"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <tableParts count="1">
     <tablePart r:id="rId1"/>

--- a/RM.xlsx
+++ b/RM.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\FG &amp; RMPM LIST\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A34297E1-68BA-4269-85B9-66E8A65EBF34}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{51F6FD22-5489-409B-9D2E-80117BE167F9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -8239,7 +8239,7 @@
     <t>PET Preform 29G 53MM SP400 NAT R 980 CB</t>
   </si>
   <si>
-    <t>Wall Thickness:  mm to mm
+    <t>Wall Thickness: 1.68 mm to 2.95 mm
 Weight: 28.49 GM - 28.54 gm
 Height: 77.35 mm
 CRH: 13.45 mm
@@ -8778,20 +8778,20 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{D991BE68-994E-4C3A-AD1A-D16C28ACEA8E}" name="Table1" displayName="Table1" ref="A1:K558" totalsRowShown="0" headerRowDxfId="0" dataDxfId="15" headerRowBorderDxfId="13" tableBorderDxfId="14" totalsRowBorderDxfId="12">
-  <autoFilter ref="A1:K558" xr:uid="{D991BE68-994E-4C3A-AD1A-D16C28ACEA8E}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{891823E1-8D2B-4BB9-9E78-07D832355D5E}" name="Table1" displayName="Table1" ref="A1:K558" totalsRowShown="0" headerRowDxfId="0" dataDxfId="15" headerRowBorderDxfId="13" tableBorderDxfId="14" totalsRowBorderDxfId="12">
+  <autoFilter ref="A1:K558" xr:uid="{891823E1-8D2B-4BB9-9E78-07D832355D5E}"/>
   <tableColumns count="11">
-    <tableColumn id="1" xr3:uid="{735891A2-2F05-4E9E-8810-7655801B4E44}" name="ID" dataDxfId="11"/>
-    <tableColumn id="2" xr3:uid="{B13B2CE0-ACA7-42C0-B377-F072717C3B38}" name="Status" dataDxfId="10"/>
-    <tableColumn id="3" xr3:uid="{773EEE8D-2081-4BBD-BEA7-C1575042BA66}" name="Material List::Material_Detail" dataDxfId="9"/>
-    <tableColumn id="4" xr3:uid="{B3F34587-82B7-458D-A0AE-EF40BE88A772}" name="Product_Code" dataDxfId="8"/>
-    <tableColumn id="5" xr3:uid="{BAED11DA-9131-46C7-B7A7-5BBCB0130A81}" name="RM PM Product List 2::Product_Detail" dataDxfId="7"/>
-    <tableColumn id="6" xr3:uid="{4B4C3402-6689-4591-9C39-C4B38407BBCD}" name="Item_Code" dataDxfId="6"/>
-    <tableColumn id="7" xr3:uid="{73AA5F1E-DCF2-4350-817A-30DD3E7A61C8}" name="Old_Item_Code" dataDxfId="5"/>
-    <tableColumn id="8" xr3:uid="{211F0F95-5996-4EF8-8DB9-6DAFC32B1201}" name="Item_Name" dataDxfId="4"/>
-    <tableColumn id="9" xr3:uid="{C1048881-69D2-4CBE-A993-8F20EE68108D}" name="Item_Detail_by_Vendor" dataDxfId="3"/>
-    <tableColumn id="10" xr3:uid="{F09007A0-2908-45EB-9579-8A28239FE555}" name="Vendor List 2::Vendor_Name" dataDxfId="2"/>
-    <tableColumn id="11" xr3:uid="{7669724A-D363-4F1B-9C27-2A5639E78838}" name="Remarks" dataDxfId="1"/>
+    <tableColumn id="1" xr3:uid="{AA3F9463-14BF-4B96-8318-CAEAE05E9DCE}" name="ID" dataDxfId="11"/>
+    <tableColumn id="2" xr3:uid="{9D402485-09F2-41B4-BABE-984613EE4F17}" name="Status" dataDxfId="10"/>
+    <tableColumn id="3" xr3:uid="{0A4D65F3-C688-4342-A331-87165E134443}" name="Material List::Material_Detail" dataDxfId="9"/>
+    <tableColumn id="4" xr3:uid="{912645EA-CA11-4527-9AF4-79812A5C62D8}" name="Product_Code" dataDxfId="8"/>
+    <tableColumn id="5" xr3:uid="{4ADD3E75-5E64-4D8F-A322-97BB9CBC9258}" name="RM PM Product List 2::Product_Detail" dataDxfId="7"/>
+    <tableColumn id="6" xr3:uid="{3359B59E-AC34-4630-9A2C-B0DDB65D5485}" name="Item_Code" dataDxfId="6"/>
+    <tableColumn id="7" xr3:uid="{FB58439F-AA59-46E0-A3EB-AEB1A6493E70}" name="Old_Item_Code" dataDxfId="5"/>
+    <tableColumn id="8" xr3:uid="{FC002BE4-F4A7-4875-9DFB-E327423B08D5}" name="Item_Name" dataDxfId="4"/>
+    <tableColumn id="9" xr3:uid="{34F35ECB-EE51-4224-A624-B38125E5B32D}" name="Item_Detail_by_Vendor" dataDxfId="3"/>
+    <tableColumn id="10" xr3:uid="{8EB1514B-75B7-4719-BD0F-73475402C7E6}" name="Vendor List 2::Vendor_Name" dataDxfId="2"/>
+    <tableColumn id="11" xr3:uid="{A7C7519C-50CB-43CE-9A6A-4F2E2AD0A562}" name="Remarks" dataDxfId="1"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -27369,7 +27369,7 @@
       </c>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="jhspqN817QB7Xl9plb3pxavq2iOXGkDKtbiqPfjz/ijYhjDwk1myGHB1uSwfdxelumSlrlyl08+Lj6RcFjmpfg==" saltValue="DigyCWFgMvr96XWL1Vk3sA==" spinCount="100000" sheet="1" objects="1" scenarios="1" sort="0" autoFilter="0"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="kMK/2boG9D6gdQfuy1rtDB7JU6dhxvPtcZpK8xOoGQdbO2nCyZobap8E2nalBVkrYfyq74lHQ66XrRL7B/wPTg==" saltValue="I794d5o5B42YOE5f9pYgjQ==" spinCount="100000" sheet="1" objects="1" scenarios="1" sort="0" autoFilter="0"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <tableParts count="1">
     <tablePart r:id="rId1"/>

--- a/RM.xlsx
+++ b/RM.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\FG &amp; RMPM LIST\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{51F6FD22-5489-409B-9D2E-80117BE167F9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8F18E441-2861-46F4-8BF8-98D72D4AA6C2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4945" uniqueCount="2560">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4956" uniqueCount="2566">
   <si>
     <t>ID</t>
   </si>
@@ -8129,6 +8129,9 @@
     <t>SCJ Masterbatches Pvt. Ltd.</t>
   </si>
   <si>
+    <t>Issues: Static Charge Problem</t>
+  </si>
+  <si>
     <t>RM010.3</t>
   </si>
   <si>
@@ -8145,6 +8148,11 @@
   </si>
   <si>
     <t>8115334610 PET PINK</t>
+  </si>
+  <si>
+    <t>This color is now called:
+SCJ Nice TR PURPLE ONION 8115334610 PET
+Item Code: RM273.1</t>
   </si>
   <si>
     <t>RM258.2</t>
@@ -8202,7 +8210,7 @@
     <t>4Layer PE Induction Wad:
 Seal Dia.: 62.05 +/- 0.10 mm
 Thickness: 0.70 +/- 0.10 mm
-Weight: 
+Weight: 1.40 gm
 1. Heat Seal Layer: 0.038 mm
 2. Al. Foil: 0.025 mm
 3. Wax: 0.016 mm
@@ -8221,7 +8229,8 @@
     <t xml:space="preserve">SGV 1203/080/Plain/19mm PET </t>
   </si>
   <si>
-    <t>To be procured:</t>
+    <t>To be procured:
+Procured on 11.07.2026</t>
   </si>
   <si>
     <t>RM272</t>
@@ -8248,6 +8257,18 @@
 OD w/o thread: 49.80 mm
 OD (Head): 50.00 mm
 OD Neck Ring (Neck Size): 52.25 mm</t>
+  </si>
+  <si>
+    <t>RM273</t>
+  </si>
+  <si>
+    <t>Pet TR Purple Onion</t>
+  </si>
+  <si>
+    <t>RM273.1</t>
+  </si>
+  <si>
+    <t>SCJ Nice TR PURPLE ONION 8115334610 PET</t>
   </si>
 </sst>
 </file>
@@ -8431,9 +8452,7 @@
       <alignment vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1"/>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -8778,20 +8797,20 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{891823E1-8D2B-4BB9-9E78-07D832355D5E}" name="Table1" displayName="Table1" ref="A1:K558" totalsRowShown="0" headerRowDxfId="0" dataDxfId="15" headerRowBorderDxfId="13" tableBorderDxfId="14" totalsRowBorderDxfId="12">
-  <autoFilter ref="A1:K558" xr:uid="{891823E1-8D2B-4BB9-9E78-07D832355D5E}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{A19D9272-74F0-4140-89F8-AC25124E915C}" name="Table1" displayName="Table1" ref="A1:K559" totalsRowShown="0" headerRowDxfId="0" dataDxfId="15" headerRowBorderDxfId="13" tableBorderDxfId="14" totalsRowBorderDxfId="12">
+  <autoFilter ref="A1:K559" xr:uid="{A19D9272-74F0-4140-89F8-AC25124E915C}"/>
   <tableColumns count="11">
-    <tableColumn id="1" xr3:uid="{AA3F9463-14BF-4B96-8318-CAEAE05E9DCE}" name="ID" dataDxfId="11"/>
-    <tableColumn id="2" xr3:uid="{9D402485-09F2-41B4-BABE-984613EE4F17}" name="Status" dataDxfId="10"/>
-    <tableColumn id="3" xr3:uid="{0A4D65F3-C688-4342-A331-87165E134443}" name="Material List::Material_Detail" dataDxfId="9"/>
-    <tableColumn id="4" xr3:uid="{912645EA-CA11-4527-9AF4-79812A5C62D8}" name="Product_Code" dataDxfId="8"/>
-    <tableColumn id="5" xr3:uid="{4ADD3E75-5E64-4D8F-A322-97BB9CBC9258}" name="RM PM Product List 2::Product_Detail" dataDxfId="7"/>
-    <tableColumn id="6" xr3:uid="{3359B59E-AC34-4630-9A2C-B0DDB65D5485}" name="Item_Code" dataDxfId="6"/>
-    <tableColumn id="7" xr3:uid="{FB58439F-AA59-46E0-A3EB-AEB1A6493E70}" name="Old_Item_Code" dataDxfId="5"/>
-    <tableColumn id="8" xr3:uid="{FC002BE4-F4A7-4875-9DFB-E327423B08D5}" name="Item_Name" dataDxfId="4"/>
-    <tableColumn id="9" xr3:uid="{34F35ECB-EE51-4224-A624-B38125E5B32D}" name="Item_Detail_by_Vendor" dataDxfId="3"/>
-    <tableColumn id="10" xr3:uid="{8EB1514B-75B7-4719-BD0F-73475402C7E6}" name="Vendor List 2::Vendor_Name" dataDxfId="2"/>
-    <tableColumn id="11" xr3:uid="{A7C7519C-50CB-43CE-9A6A-4F2E2AD0A562}" name="Remarks" dataDxfId="1"/>
+    <tableColumn id="1" xr3:uid="{ED2EF6EF-0EB7-4112-A26A-587360A50162}" name="ID" dataDxfId="11"/>
+    <tableColumn id="2" xr3:uid="{FD04631D-D00C-4A85-A2D3-B270D1FE8686}" name="Status" dataDxfId="10"/>
+    <tableColumn id="3" xr3:uid="{452A9C79-F513-4556-9DAA-C4E72A9C9794}" name="Material List::Material_Detail" dataDxfId="9"/>
+    <tableColumn id="4" xr3:uid="{637A1E06-74A7-490F-894F-219A47C183BB}" name="Product_Code" dataDxfId="8"/>
+    <tableColumn id="5" xr3:uid="{2FDB4226-7F15-4C2D-AE55-0449A0BC4802}" name="RM PM Product List 2::Product_Detail" dataDxfId="7"/>
+    <tableColumn id="6" xr3:uid="{B8ECC17F-1531-4404-AFF9-6FD59393FC5C}" name="Item_Code" dataDxfId="6"/>
+    <tableColumn id="7" xr3:uid="{9CDAF27F-B4A2-41DB-B042-54F5483B4C54}" name="Old_Item_Code" dataDxfId="5"/>
+    <tableColumn id="8" xr3:uid="{679FFD2C-0F99-451A-8946-09878C496DEF}" name="Item_Name" dataDxfId="4"/>
+    <tableColumn id="9" xr3:uid="{C363CCC7-2B54-4B87-BB4F-4D4263978256}" name="Item_Detail_by_Vendor" dataDxfId="3"/>
+    <tableColumn id="10" xr3:uid="{16FC478C-37F1-4094-84A3-E55D974BDC77}" name="Vendor List 2::Vendor_Name" dataDxfId="2"/>
+    <tableColumn id="11" xr3:uid="{50C50C0E-3494-45F7-A277-BBBEEB8D1D70}" name="Remarks" dataDxfId="1"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -9094,7 +9113,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:K558"/>
+  <dimension ref="A1:K559"/>
   <sheetFormatPr defaultColWidth="21.7109375" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.140625" bestFit="1" customWidth="1"/>
@@ -27145,7 +27164,9 @@
       <c r="J551" s="5" t="s">
         <v>2529</v>
       </c>
-      <c r="K551" s="6"/>
+      <c r="K551" s="8" t="s">
+        <v>2530</v>
+      </c>
     </row>
     <row r="552" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A552" s="4">
@@ -27164,14 +27185,14 @@
         <v>82</v>
       </c>
       <c r="F552" s="5" t="s">
-        <v>2530</v>
+        <v>2531</v>
       </c>
       <c r="G552" s="7"/>
       <c r="H552" s="5" t="s">
-        <v>2531</v>
+        <v>2532</v>
       </c>
       <c r="I552" s="5" t="s">
-        <v>2532</v>
+        <v>2533</v>
       </c>
       <c r="J552" s="5" t="s">
         <v>2529</v>
@@ -27183,7 +27204,7 @@
         <v>553</v>
       </c>
       <c r="B553" s="5" t="s">
-        <v>11</v>
+        <v>636</v>
       </c>
       <c r="C553" s="5" t="s">
         <v>67</v>
@@ -27195,19 +27216,21 @@
         <v>76</v>
       </c>
       <c r="F553" s="5" t="s">
-        <v>2533</v>
+        <v>2534</v>
       </c>
       <c r="G553" s="7"/>
       <c r="H553" s="5" t="s">
-        <v>2534</v>
+        <v>2535</v>
       </c>
       <c r="I553" s="5" t="s">
-        <v>2535</v>
+        <v>2536</v>
       </c>
       <c r="J553" s="5" t="s">
         <v>2529</v>
       </c>
-      <c r="K553" s="6"/>
+      <c r="K553" s="8" t="s">
+        <v>2537</v>
+      </c>
     </row>
     <row r="554" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A554" s="4">
@@ -27224,20 +27247,20 @@
         <v>2364</v>
       </c>
       <c r="F554" s="5" t="s">
-        <v>2536</v>
+        <v>2538</v>
       </c>
       <c r="G554" s="7"/>
       <c r="H554" s="5" t="s">
-        <v>2537</v>
+        <v>2539</v>
       </c>
       <c r="I554" s="5" t="s">
-        <v>2538</v>
+        <v>2540</v>
       </c>
       <c r="J554" s="5" t="s">
         <v>2367</v>
       </c>
       <c r="K554" s="8" t="s">
-        <v>2539</v>
+        <v>2541</v>
       </c>
     </row>
     <row r="555" spans="1:11" x14ac:dyDescent="0.2">
@@ -27257,14 +27280,14 @@
         <v>164</v>
       </c>
       <c r="F555" s="5" t="s">
-        <v>2540</v>
+        <v>2542</v>
       </c>
       <c r="G555" s="7"/>
       <c r="H555" s="5" t="s">
-        <v>2541</v>
+        <v>2543</v>
       </c>
       <c r="I555" s="5" t="s">
-        <v>2542</v>
+        <v>2544</v>
       </c>
       <c r="J555" s="5" t="s">
         <v>104</v>
@@ -27282,94 +27305,127 @@
         <v>765</v>
       </c>
       <c r="D556" s="5" t="s">
-        <v>2543</v>
+        <v>2545</v>
       </c>
       <c r="E556" s="5" t="s">
-        <v>2544</v>
+        <v>2546</v>
       </c>
       <c r="F556" s="5" t="s">
-        <v>2545</v>
+        <v>2547</v>
       </c>
       <c r="G556" s="7"/>
       <c r="H556" s="5" t="s">
-        <v>2546</v>
+        <v>2548</v>
       </c>
       <c r="I556" s="5" t="s">
-        <v>2547</v>
+        <v>2549</v>
       </c>
       <c r="J556" s="5" t="s">
         <v>785</v>
       </c>
       <c r="K556" s="8" t="s">
-        <v>2548</v>
+        <v>2550</v>
       </c>
     </row>
     <row r="557" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A557" s="4">
         <v>557</v>
       </c>
-      <c r="B557" s="7"/>
+      <c r="B557" s="5" t="s">
+        <v>11</v>
+      </c>
       <c r="C557" s="5" t="s">
         <v>765</v>
       </c>
       <c r="D557" s="5" t="s">
-        <v>2549</v>
+        <v>2551</v>
       </c>
       <c r="E557" s="5" t="s">
-        <v>2550</v>
+        <v>2552</v>
       </c>
       <c r="F557" s="5" t="s">
-        <v>2551</v>
+        <v>2553</v>
       </c>
       <c r="G557" s="7"/>
       <c r="H557" s="5" t="s">
-        <v>2550</v>
+        <v>2552</v>
       </c>
       <c r="I557" s="5" t="s">
-        <v>2552</v>
+        <v>2554</v>
       </c>
       <c r="J557" s="5" t="s">
         <v>797</v>
       </c>
       <c r="K557" s="8" t="s">
-        <v>2553</v>
+        <v>2555</v>
       </c>
     </row>
     <row r="558" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A558" s="9">
+      <c r="A558" s="4">
         <v>558</v>
       </c>
-      <c r="B558" s="10" t="s">
-        <v>11</v>
-      </c>
-      <c r="C558" s="10" t="s">
+      <c r="B558" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C558" s="5" t="s">
         <v>588</v>
       </c>
-      <c r="D558" s="10" t="s">
-        <v>2554</v>
-      </c>
-      <c r="E558" s="10" t="s">
-        <v>2555</v>
-      </c>
-      <c r="F558" s="10" t="s">
+      <c r="D558" s="5" t="s">
         <v>2556</v>
       </c>
-      <c r="G558" s="11"/>
-      <c r="H558" s="10" t="s">
+      <c r="E558" s="5" t="s">
         <v>2557</v>
       </c>
-      <c r="I558" s="10" t="s">
+      <c r="F558" s="5" t="s">
         <v>2558</v>
       </c>
-      <c r="J558" s="10" t="s">
+      <c r="G558" s="7"/>
+      <c r="H558" s="5" t="s">
+        <v>2559</v>
+      </c>
+      <c r="I558" s="5" t="s">
+        <v>2560</v>
+      </c>
+      <c r="J558" s="5" t="s">
         <v>641</v>
       </c>
-      <c r="K558" s="12" t="s">
-        <v>2559</v>
-      </c>
+      <c r="K558" s="8" t="s">
+        <v>2561</v>
+      </c>
+    </row>
+    <row r="559" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A559" s="9">
+        <v>559</v>
+      </c>
+      <c r="B559" s="10" t="s">
+        <v>11</v>
+      </c>
+      <c r="C559" s="10" t="s">
+        <v>67</v>
+      </c>
+      <c r="D559" s="10" t="s">
+        <v>2562</v>
+      </c>
+      <c r="E559" s="10" t="s">
+        <v>2563</v>
+      </c>
+      <c r="F559" s="10" t="s">
+        <v>2564</v>
+      </c>
+      <c r="G559" s="11"/>
+      <c r="H559" s="10" t="s">
+        <v>2565</v>
+      </c>
+      <c r="I559" s="10" t="s">
+        <v>2536</v>
+      </c>
+      <c r="J559" s="10" t="s">
+        <v>2529</v>
+      </c>
+      <c r="K559" s="12"/>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="kMK/2boG9D6gdQfuy1rtDB7JU6dhxvPtcZpK8xOoGQdbO2nCyZobap8E2nalBVkrYfyq74lHQ66XrRL7B/wPTg==" saltValue="I794d5o5B42YOE5f9pYgjQ==" spinCount="100000" sheet="1" objects="1" scenarios="1" sort="0" autoFilter="0"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="blHOPAnLpH79WayCqSNB8zHEmfilVFGj/xCf2DUXiv7v6Clu9L52Kw8Shj0lPNws73ZHJTmM/wxWow5TGTGfxA==" saltValue="vjLWhPuhq7o4w8gXCJVt1w==" spinCount="100000" sheet="1" objects="1" scenarios="1" sort="0" autoFilter="0"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <tableParts count="1">
     <tablePart r:id="rId1"/>
